--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A73970-ACF3-4AA6-9DF2-E6751F7BC552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3417AF8-9660-4976-B5BB-E5A33D5AF2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>4.78</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5075.1363199999996</v>
+        <v>5064.5188799999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4466,14 +4466,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>7.0237431112321742</v>
+        <v>7.3642693066239637</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22813798282757203</v>
+        <v>0.22187622097249027</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>3.3382445740642042</v>
+        <v>3.4769479145113666</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4515,7 +4515,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="302">
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>4.8687220027404132</v>
+        <v>4.8197379854720408</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4534,7 +4534,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="312">
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>6.8384512580908767</v>
+        <v>6.8641356814360206</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4553,7 +4553,7 @@
         <v>438</v>
       </c>
       <c r="F31" s="312">
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>6.1762589337191462</v>
+        <v>6.1469536878205542</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4572,7 +4572,7 @@
         <v>440</v>
       </c>
       <c r="F32" s="312">
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>3817.8456825297781</v>
+        <v>3725.8278691964447</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-1738.1543174702219</v>
+        <v>-1830.1721308035553</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-133595.49547196552</v>
+        <v>-133572.49101863219</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>626261.06678643764</v>
+        <v>626115.72996402986</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>392279.51308745093</v>
+        <v>392210.49972745095</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.7294379569975952E-2</v>
+        <v>7.7442795460059763E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,14 +4873,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.10251046025104602</v>
+        <v>7.5471698113207544E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>1.32623433710651</v>
+        <v>0.9745476989157914</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4900,11 +4900,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C120</f>
-        <v>7.0642585231402863E-2</v>
+        <v>7.0630420943605887E-2</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G120</f>
-        <v>0.10232932303990128</v>
+        <v>0.102310110249777</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4914,11 +4914,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C117</f>
-        <v>9.3055202992623556E-2</v>
+        <v>9.3039179367971361E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G117</f>
-        <v>0.12805536634261894</v>
+        <v>0.12803132337228806</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.6183391793060631</v>
+        <v>4.9253617912598004</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>2315838.5793675557</v>
+        <v>2338843.0327008888</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1811647434480963</v>
+        <v>2.2028314101147628</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>7.76 HKD</v>
+        <v>8.13 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>7.15 HKD</v>
+        <v>7.5 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>7 HKD</v>
+        <v>7.34 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>6.84 HKD</v>
+        <v>7.18 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>6.77 HKD</v>
+        <v>7.1 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>7.0237431112321742</v>
+        <v>7.3642693066239637</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.77857142857142836</v>
+        <v>0.59661335497134915</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>2.5596731454927757</v>
+        <v>2.8803345595400174</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>3.3382445740642042</v>
+        <v>3.4769479145113666</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52472000738099656</v>
+        <v>0.52786247083822091</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>1.0006982963331732</v>
+        <v>0.73814429659137726</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>3.8680237064072402</v>
+        <v>4.0815936888806634</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>4.8687220027404132</v>
+        <v>4.8197379854720408</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30681946568426044</v>
+        <v>0.34552393661964331</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>1.2627775237514614</v>
+        <v>0.93618926635390554</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>5.5756737343394152</v>
+        <v>5.9279464150821148</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>6.8384512580908767</v>
+        <v>6.8641356814360206</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>2.6380784463057028E-2</v>
+        <v>6.7913543674738563E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C170" s="92">
         <f>F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="171" spans="2:4">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>1.1768973214285723</v>
+        <v>0.86853712533791372</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>4.9993616122905742</v>
+        <v>5.27841656248264</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>6.1762589337191462</v>
+        <v>6.1469536878205542</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.12022147767093794</v>
+        <v>0.16491459548843124</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>2315838.5793675557</v>
+        <v>2338843.0327008888</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>226</v>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-477230.71031622222</v>
+        <v>-465728.48364955559</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>353</v>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>6.8526604204348809</v>
+        <v>7.0219024921412929</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>320</v>
@@ -9592,7 +9592,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>954461.42063244444</v>
+        <v>931456.96729911119</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>354</v>
@@ -9724,11 +9724,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>2315838.5793675557</v>
+        <v>2338843.0327008888</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1811647434480963</v>
+        <v>2.2028314101147628</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9758,11 +9758,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>2285442.5793675557</v>
+        <v>2308447.0327008888</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>2.1525363735208822</v>
+        <v>2.1742030401875487</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -10342,24 +10342,24 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-1738.1543174702219</v>
+        <v>-1830.1721308035553</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>474.06678643761552</v>
+        <v>328.7299640298852</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>5344.7997321626699</v>
+        <v>5086.406745496819</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>2692.8696524834195</v>
+        <v>2491.8136988481774</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>4440.0899902686779</v>
+        <v>4172.5312381705007</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
@@ -10397,24 +10397,24 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>534381.98188786209</v>
+        <v>534289.96407452878</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>774079.06678643764</v>
+        <v>773933.72996402986</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1158381.7997321626</v>
+        <v>1158123.4067454969</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>1373621.8696524834</v>
+        <v>1373420.8136988482</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>1160672.0899902687</v>
+        <v>1160404.5312381706</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-133595.49547196552</v>
+        <v>-133572.49101863219</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -10564,26 +10564,26 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>392279.51308745093</v>
+        <v>392210.49972745095</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>626261.06678643764</v>
+        <v>626115.72996402986</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1059581.7997321626</v>
+        <v>1059323.4067454969</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>1207188.8696524834</v>
+        <v>1206987.8136988482</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>969999.08999026869</v>
+        <v>969731.53123817057</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
@@ -10672,26 +10672,26 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>392279.51308745093</v>
+        <v>392210.49972745095</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>626261.06678643764</v>
+        <v>626115.72996402986</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1059581.7997321626</v>
+        <v>1059323.4067454969</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>1207188.8696524834</v>
+        <v>1206987.8136988482</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>969999.08999026869</v>
+        <v>969731.53123817057</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
@@ -11533,19 +11533,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18127734752283906</v>
+        <v>0.18131138955078466</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>7.6711322657647213E-2</v>
+        <v>7.6728437990656748E-2</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.11859522886106481</v>
+        <v>0.11861259009266797</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.15698232220051717</v>
+        <v>0.15701851819346507</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11671,24 +11671,24 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>3817.8456825297781</v>
+        <v>3725.8278691964447</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>6030.0667864376155</v>
+        <v>5884.7299640298852</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>10720.79973216267</v>
+        <v>10462.406745496819</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>8341.8696524834195</v>
+        <v>8140.8136988481774</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>11101.089990268678</v>
+        <v>10833.531238170501</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
@@ -11783,24 +11783,24 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-1738.1543174702219</v>
+        <v>-1830.1721308035553</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>474.06678643761552</v>
+        <v>328.7299640298852</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>5344.7997321626699</v>
+        <v>5086.406745496819</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>2692.8696524834195</v>
+        <v>2491.8136988481774</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>4440.0899902686779</v>
+        <v>4172.5312381705007</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
@@ -12869,26 +12869,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>3.0267544252387976E-4</v>
+        <v>3.1869906717608135E-4</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>7.8424541642960457E-5</v>
+        <v>5.4381571312090199E-5</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>7.966226898809284E-4</v>
+        <v>7.5811016810289965E-4</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.3399096884436752E-4</v>
+        <v>3.0905442106730192E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>6.1702349870645565E-4</v>
+        <v>5.7984181146791369E-4</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12926,26 +12926,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.3055202992623556E-2</v>
+        <v>9.3039179367971361E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12805536634261894</v>
+        <v>0.12803132337228806</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.17265253544651632</v>
+        <v>0.17261402292473829</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1703674363324458</v>
+        <v>0.17034249978466875</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16129446821716184</v>
+        <v>0.1612572865299233</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12983,7 +12983,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.3263800748155889E-2</v>
+        <v>2.325979484199284E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -13098,26 +13098,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>6.831003094685259E-2</v>
+        <v>6.8298013228363444E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.10360193651326588</v>
+        <v>0.10357789354293501</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15792675979460266</v>
+        <v>0.15788824727282463</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.14972510079778259</v>
+        <v>0.14970016425000554</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13479732022540755</v>
+        <v>0.13476013853816901</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -13205,26 +13205,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>6.831003094685259E-2</v>
+        <v>6.8298013228363444E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.10360193651326588</v>
+        <v>0.10357789354293501</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15792675979460266</v>
+        <v>0.15788824727282463</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.14972510079778259</v>
+        <v>0.14970016425000554</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13479732022540755</v>
+        <v>0.13476013853816901</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -13273,8 +13273,7 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C90" s="113">
-        <f>G90</f>
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
@@ -13330,7 +13329,7 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>520254.56</v>
+        <v>382227.84</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
@@ -13385,20 +13384,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>1.32623433710651</v>
+        <v>0.9745476989157914</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.83073112411347283</v>
+        <v>0.83092395718901424</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.44089787132818714</v>
+        <v>0.44100541631120332</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.31662637853017389</v>
+        <v>0.31667912108296437</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13440,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.10251046025104602</v>
+        <v>7.5471698113207544E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.10251046025104602</v>
+        <v>0.10272536687631029</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>9.2050209205020911E-2</v>
+        <v>9.2243186582809236E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.5313807531380741E-2</v>
+        <v>7.5471698113207544E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13577,26 +13576,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.30965452391532777</v>
+        <v>-0.30964378035395745</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.33175826228846328</v>
+        <v>-0.33173466190541689</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.15669528468906435</v>
+        <v>-0.15675997101974881</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.18347109532374484</v>
+        <v>0.18357070894353189</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.10489058396805739</v>
+        <v>0.10463588399861634</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -14188,19 +14187,19 @@
       <c r="E114" s="268"/>
       <c r="G114" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.8565596069482173</v>
+        <v>1.8569905599828904</v>
       </c>
       <c r="H114" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.46246264339748455</v>
+        <v>0.46257544851713722</v>
       </c>
       <c r="I114" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>0.53722082459780562</v>
+        <v>0.53731031302840637</v>
       </c>
       <c r="J114" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>0.35841167645166327</v>
+        <v>0.35851056586362906</v>
       </c>
       <c r="K114" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -14296,24 +14295,24 @@
       </c>
       <c r="C117" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.3055202992623556E-2</v>
+        <v>9.3039179367971361E-2</v>
       </c>
       <c r="E117" s="268"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>0.12805536634261894</v>
+        <v>0.12803132337228806</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.17265253544651632</v>
+        <v>0.17261402292473829</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.1703674363324458</v>
+        <v>0.17034249978466875</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16129446821716184</v>
+        <v>0.1612572865299233</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14461,26 +14460,26 @@
       </c>
       <c r="C120" s="102">
         <f>C13/C105</f>
-        <v>7.0642585231402863E-2</v>
+        <v>7.0630420943605887E-2</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="271"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f>IF(G$4="","",G13/G105)</f>
-        <v>0.10232932303990128</v>
+        <v>0.102310110249777</v>
       </c>
       <c r="H120" s="102">
         <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
-        <v>0.15473615757958106</v>
+        <v>0.15470164155221305</v>
       </c>
       <c r="I120" s="102">
         <f t="shared" si="48"/>
-        <v>0.19890699474394657</v>
+        <v>0.19887788088343192</v>
       </c>
       <c r="J120" s="102">
         <f t="shared" si="48"/>
-        <v>0.17976644049711157</v>
+        <v>0.17972500064092536</v>
       </c>
       <c r="K120" s="102">
         <f t="shared" si="48"/>
@@ -14582,26 +14581,26 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.36946713434448503</v>
+        <v>0.3694021343444851</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.58984187034392244</v>
+        <v>0.58970498534866211</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>0.99796353898130119</v>
+        <v>0.99772017241961986</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>1.1369867591928784</v>
+        <v>1.1367973953220816</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>0.91359036640684455</v>
+        <v>0.9133383670999512</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
@@ -14639,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.7294379569975952E-2</v>
+        <v>7.7442795460059763E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12339788082508837</v>
+        <v>0.12362787952802141</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.2087789830504814</v>
+        <v>0.20916565459530817</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.23786333874327997</v>
+        <v>0.2383223050989689</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.19112769171691307</v>
+        <v>0.19147554865827071</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.17689534692143993</v>
+        <v>0.17726619670534235</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.11883661087550845</v>
+        <v>0.11908574423164162</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.4371849306305919E-2</v>
+        <v>9.4569693854117898E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>8.7048696260438568E-2</v>
+        <v>8.7231188286141806E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10642256009391289</v>
+        <v>0.10664566818635297</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.10069699960295844</v>
+        <v>0.10090810442392903</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14696,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14204978044806488</v>
+        <v>0.14234757872992665</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22957077929288017</v>
+        <v>0.23005205975261367</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2498855045533043</v>
+        <v>0.25040937353559634</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21521431763235868</v>
+        <v>0.21566550068819174</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17809373837666689</v>
+        <v>0.17846710051162845</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12312260412346913</v>
+        <v>0.12338072279039465</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10155352831980678</v>
+        <v>0.10176642879846466</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6316642308437534E-2</v>
+        <v>6.6455670908664874E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11890005744712685</v>
+        <v>0.11914932381494055</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12222055938785108</v>
+        <v>0.12247678697566629</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15482,7 +15481,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>392279.51308745093</v>
+        <v>392210.49972745095</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15503,7 +15502,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15514,7 +15513,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>4903493.9135931367</v>
+        <v>5229473.3296993459</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15548,7 +15547,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>2315838.5793675557</v>
+        <v>2338843.0327008888</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15580,7 +15579,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>7188936.4929606924</v>
+        <v>7537920.3624002347</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15608,7 +15607,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15661,7 +15660,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>7.0202429099639359</v>
+        <v>7.3608683071354024</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15696,7 +15695,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>405281.57135964237</v>
+        <v>405210.2705599512</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -15704,11 +15703,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>375260.71422189102</v>
+        <v>376939.78656739648</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15718,7 +15717,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>418714.5813223336</v>
+        <v>418640.91726603196</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -15726,11 +15725,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>358980.26519404456</v>
+        <v>362263.63852117426</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15740,7 +15739,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>432592.82681856357</v>
+        <v>432516.72117578948</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -15748,11 +15747,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>343406.13316263043</v>
+        <v>348158.90620008967</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15772,7 +15771,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>446931.06512766716</v>
+        <v>446852.43697232439</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -15780,11 +15779,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>328507.67501095124</v>
+        <v>334603.34153674066</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15804,7 +15803,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>461744.54265726497</v>
+        <v>461663.30838097143</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -15812,11 +15811,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>314255.57705456956</v>
+        <v>321575.5626920794</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16456,7 +16455,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>5066019.6419955296</v>
+        <v>5402803.607466016</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16464,11 +16463,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>3447847.8441851065</v>
+        <v>3763369.4916728018</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16479,7 +16478,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>5168258.2088291934</v>
+        <v>5506910.7271902822</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16500,7 +16499,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>5168258.2088291934</v>
+        <v>5506910.7271902822</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16530,19 +16529,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>4903493.9135931358</v>
+        <v>5229473.3296993468</v>
       </c>
       <c r="C56" s="123">
-        <v>4982020.5529871695</v>
+        <v>5311797.0979552846</v>
       </c>
       <c r="D56" s="123">
-        <v>5142576.5374104809</v>
+        <v>5480015.6552283727</v>
       </c>
       <c r="E56" s="123">
-        <v>5307974.0832336675</v>
+        <v>5653170.5093219765</v>
       </c>
       <c r="F56" s="123">
-        <v>5392554.1713279355</v>
+        <v>5741666.1791931614</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16551,19 +16550,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>4903493.9135931348</v>
+        <v>5229473.3296993468</v>
       </c>
       <c r="C57" s="123">
-        <v>5058034.8490198106</v>
+        <v>5390727.6240964383</v>
       </c>
       <c r="D57" s="123">
-        <v>5390020.094280811</v>
+        <v>5736976.0953361988</v>
       </c>
       <c r="E57" s="123">
-        <v>5755582.3259497788</v>
+        <v>6118038.2918811832</v>
       </c>
       <c r="F57" s="123">
-        <v>5952189.3224694356</v>
+        <v>6322908.5674613891</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16572,19 +16571,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>4903493.9135931339</v>
+        <v>5229473.3296993477</v>
       </c>
       <c r="C58" s="341">
-        <v>5149784.7315246295</v>
+        <v>5488178.5049927346</v>
       </c>
       <c r="D58" s="123">
-        <v>5704265.4891112307</v>
+        <v>6070780.1280872598</v>
       </c>
       <c r="E58" s="123">
-        <v>6354840.6907237992</v>
+        <v>6754659.7660099249</v>
       </c>
       <c r="F58" s="123">
-        <v>6721989.0642282236</v>
+        <v>7140747.7793463282</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16603,19 +16602,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>4903493.9135931339</v>
+        <v>5229473.3296993477</v>
       </c>
       <c r="C59" s="341">
-        <v>5240851.4742050003</v>
+        <v>5587151.4605609588</v>
       </c>
       <c r="D59" s="123">
-        <v>6033200.4060326396</v>
+        <v>6428308.510721324</v>
       </c>
       <c r="E59" s="123">
-        <v>7018600.6750914315</v>
+        <v>7476196.9692272805</v>
       </c>
       <c r="F59" s="123">
-        <v>7600121.3271887824</v>
+        <v>8095371.61425889</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16634,19 +16633,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>4903493.9135931339</v>
+        <v>5229473.3296993477</v>
       </c>
       <c r="C60" s="341">
-        <v>5323304.2195165623</v>
+        <v>5678854.5880803559</v>
       </c>
       <c r="D60" s="123">
-        <v>6347852.0772465961</v>
+        <v>6778297.3364054672</v>
       </c>
       <c r="E60" s="123">
-        <v>7692636.2117226962</v>
+        <v>8226016.0050450303</v>
       </c>
       <c r="F60" s="123">
-        <v>8520377.2392496709</v>
+        <v>9119156.034894228</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16665,19 +16664,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>4903493.9135931339</v>
+        <v>5229473.3296993477</v>
       </c>
       <c r="C61" s="341">
-        <v>5394065.3993567638</v>
+        <v>5759395.5124234725</v>
       </c>
       <c r="D61" s="123">
-        <v>6633625.7748917416</v>
+        <v>7103601.9084206969</v>
       </c>
       <c r="E61" s="123">
-        <v>8344459.503612618</v>
+        <v>8968094.1231267322</v>
       </c>
       <c r="F61" s="123">
-        <v>9440516.2047973126</v>
+        <v>10166768.968136745</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16757,23 +16756,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16784,23 +16783,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.7708755528269444</v>
+        <v>7.0995648314473501</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8448356028898916</v>
+        <v>7.1771011945027929</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.9960547144867657</v>
+        <v>7.3355372744552945</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>7.1518338343340986</v>
+        <v>7.4986225888941824</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.2314953046077877</v>
+        <v>7.581971936638257</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16811,23 +16810,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>6.7708755528269435</v>
+        <v>7.0995648314473501</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>6.9164294108442013</v>
+        <v>7.2514416439342506</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>7.2291085927006575</v>
+        <v>7.5775545969999243</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>7.5734121457878123</v>
+        <v>7.9364567396491736</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>7.7585857813531236</v>
+        <v>8.1294131166856403</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16838,23 +16837,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>6.7708755528269426</v>
+        <v>7.099564831447351</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>7.0028437277650593</v>
+        <v>7.3432254269330679</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>7.5250795563514234</v>
+        <v>7.8919467977103217</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>8.137821612452111</v>
+        <v>8.5360565246526594</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>8.4836190678692596</v>
+        <v>8.8996922158705072</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16865,23 +16864,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>6.7708755528269426</v>
+        <v>7.099564831447351</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>7.0886146317497962</v>
+        <v>7.4364427708203182</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>7.8348857967647527</v>
+        <v>8.2286836972209993</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>8.7629817116545858</v>
+        <v>9.2156339022666192</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>9.3106849735494972</v>
+        <v>9.798801450217546</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16892,23 +16891,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>6.7708755528269426</v>
+        <v>7.099564831447351</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>7.1662724714094157</v>
+        <v>7.5228130517160867</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>8.1312394104550165</v>
+        <v>8.5583194904858004</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>9.3978198050474049</v>
+        <v>9.9218484283837913</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>10.177424895847988</v>
+        <v>10.763049348614276</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16918,23 +16917,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>6.7708755528269426</v>
+        <v>7.099564831447351</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>7.2329186496220554</v>
+        <v>7.5986702492543978</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>8.4003944022846344</v>
+        <v>8.8647065028119645</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>10.01173737075997</v>
+        <v>10.620772197278836</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>11.044054672468004</v>
+        <v>11.749740051121206</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16969,7 +16968,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.7585857813531236</v>
+        <v>8.1294131166856403</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16991,7 +16990,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>7.1518338343340986</v>
+        <v>7.4986225888941824</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17014,7 +17013,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>6.9960547144867657</v>
+        <v>7.3355372744552945</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17037,7 +17036,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>6.8448356028898916</v>
+        <v>7.1771011945027929</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17060,7 +17059,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>6.7708755528269435</v>
+        <v>7.0995648314473501</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17242,7 +17241,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91</f>
-        <v>520254.56</v>
+        <v>382227.84</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17263,7 +17262,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17274,7 +17273,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>6503182</v>
+        <v>5096371.2</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17290,7 +17289,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.125</v>
+        <v>4.8</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17343,7 +17342,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>6.4557195515885795</v>
+        <v>5.0546527009504914</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17378,7 +17377,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>537498.33613364003</v>
+        <v>394896.73675124574</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17386,11 +17385,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>497683.64456818515</v>
+        <v>367345.80162906583</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17400,7 +17399,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>555313.65519685496</v>
+        <v>407985.54259360774</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17408,11 +17407,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>476091.95404394285</v>
+        <v>353043.19532167248</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17422,7 +17421,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>573719.46091274894</v>
+        <v>421508.17536446865</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17430,11 +17429,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>455437.0053732511</v>
+        <v>339297.46089433634</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17444,7 +17443,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>592735.32489189808</v>
+        <v>435479.01420629246</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17452,11 +17451,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>435678.15860254975</v>
+        <v>326086.91654416529</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17466,7 +17465,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>612381.46744360647</v>
+        <v>449912.91485652718</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17474,11 +17473,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>416776.53691699082</v>
+        <v>313390.7246491168</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18038,7 +18037,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>6718729.2016705004</v>
+        <v>5265289.8233499434</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18046,11 +18045,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>4572654.2000769442</v>
+        <v>3667583.0782796214</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18061,7 +18060,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>6854321.4995818641</v>
+        <v>5366747.1773179779</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18082,7 +18081,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>6854321.4995818641</v>
+        <v>5366747.1773179779</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18112,19 +18111,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>6503181.9999999981</v>
+        <v>5096371.2000000011</v>
       </c>
       <c r="C51" s="123">
-        <v>6607326.7255419474</v>
+        <v>5176599.6389199011</v>
       </c>
       <c r="D51" s="123">
-        <v>6820261.58511208</v>
+        <v>5340536.6468253257</v>
       </c>
       <c r="E51" s="123">
-        <v>7039617.4896559399</v>
+        <v>5509284.3114383454</v>
       </c>
       <c r="F51" s="123">
-        <v>7151790.5067220479</v>
+        <v>5595527.5628753211</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18133,19 +18132,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>6503181.9999999981</v>
+        <v>5096371.2000000011</v>
       </c>
       <c r="C52" s="123">
-        <v>6708139.4950514138</v>
+        <v>5253521.2015449768</v>
       </c>
       <c r="D52" s="123">
-        <v>7148429.7267292803</v>
+        <v>5590956.8524447968</v>
       </c>
       <c r="E52" s="123">
-        <v>7633250.9107179493</v>
+        <v>5962320.1392315058</v>
       </c>
       <c r="F52" s="123">
-        <v>7893997.8604176994</v>
+        <v>6161975.9948744401</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18154,19 +18153,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>6503181.9999999972</v>
+        <v>5096371.2000000011</v>
       </c>
       <c r="C53" s="123">
-        <v>6829821.339654793</v>
+        <v>5348491.7332797786</v>
       </c>
       <c r="D53" s="123">
-        <v>7565192.7596309762</v>
+        <v>5916264.8044511545</v>
       </c>
       <c r="E53" s="123">
-        <v>8428007.9308795519</v>
+        <v>6582738.1319240499</v>
       </c>
       <c r="F53" s="123">
-        <v>8914932.7106339298</v>
+        <v>6958999.3169000112</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18175,19 +18174,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>6503181.9999999981</v>
+        <v>5096371.2000000011</v>
       </c>
       <c r="C54" s="123">
-        <v>6950597.1807659445</v>
+        <v>5444945.5993836867</v>
       </c>
       <c r="D54" s="123">
-        <v>8001437.5411254261</v>
+        <v>6264693.2670442667</v>
       </c>
       <c r="E54" s="123">
-        <v>9308309.2137451898</v>
+        <v>7285910.5530016627</v>
       </c>
       <c r="F54" s="123">
-        <v>10079541.870293263</v>
+        <v>7889325.7785442164</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18196,19 +18195,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>6503181.9999999981</v>
+        <v>5096371.2000000011</v>
       </c>
       <c r="C55" s="123">
-        <v>7059948.8427868355</v>
+        <v>5534314.6712910961</v>
       </c>
       <c r="D55" s="123">
-        <v>8418739.3917173222</v>
+        <v>6605774.0717609888</v>
       </c>
       <c r="E55" s="123">
-        <v>10202238.286855584</v>
+        <v>8016644.9689611075</v>
       </c>
       <c r="F55" s="123">
-        <v>11300016.859793685</v>
+        <v>8887052.5298602208</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18217,19 +18216,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>6503181.9999999991</v>
+        <v>5096371.2000000011</v>
       </c>
       <c r="C56" s="123">
-        <v>7153794.7492250791</v>
+        <v>5612805.6437782319</v>
       </c>
       <c r="D56" s="123">
-        <v>8797742.2821762096</v>
+        <v>6922798.8938652175</v>
       </c>
       <c r="E56" s="123">
-        <v>11066708.718285797</v>
+        <v>8739835.4913533926</v>
       </c>
       <c r="F56" s="123">
-        <v>12520336.750812633</v>
+        <v>9908001.30330614</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18279,23 +18278,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>6.125</v>
+        <v>4.8</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>6.125</v>
+        <v>4.8</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>6.125</v>
+        <v>4.8</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>6.125</v>
+        <v>4.8</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>6.125</v>
+        <v>4.8</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18306,23 +18305,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.1249999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>6.2230883579675966</v>
+        <v>4.875562884197981</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>6.4236403361941115</v>
+        <v>5.0299664013409311</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>6.630239953939876</v>
+        <v>5.1889008192543074</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>6.7358897311612287</v>
+        <v>5.2701287343044285</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18333,23 +18332,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>6.1249999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>6.3180385244008095</v>
+        <v>4.9480111981277748</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>6.7327243918772135</v>
+        <v>5.2658238261245618</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>7.1893515863691713</v>
+        <v>5.615591083379333</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>7.4349352201827372</v>
+        <v>5.803636276611349</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18360,23 +18359,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1249999999999973</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>6.4326441587188565</v>
+        <v>5.0374588726470586</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>7.1252512466573634</v>
+        <v>5.5722140218839522</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>7.9378908012473373</v>
+        <v>6.1999296741248831</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>8.3964992603056192</v>
+        <v>6.5543100002448904</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18387,23 +18386,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1249999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>6.5463964767080807</v>
+        <v>5.1283036206314199</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>7.5361269205433947</v>
+        <v>5.9003801924421202</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>8.7669995909985747</v>
+        <v>6.8622102437137977</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>9.4933824634688424</v>
+        <v>7.4305348356517351</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18414,23 +18413,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>6.1249999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>6.6493889702101789</v>
+        <v>5.2124755791331019</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>7.9291612589450207</v>
+        <v>6.2216259962486147</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>9.6089436689593573</v>
+        <v>7.5504499850821931</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>10.642882709762132</v>
+        <v>8.3702404062186577</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18440,23 +18439,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1249999999999991</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>6.7377774201927014</v>
+        <v>5.286402036440264</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>8.2861238511130839</v>
+        <v>6.5202147540887605</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>10.423142224760204</v>
+        <v>8.2315845357764132</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>11.792236877074542</v>
+        <v>9.3318175598883926</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18491,7 +18490,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>7.4349352201827372</v>
+        <v>5.803636276611349</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18513,7 +18512,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.630239953939876</v>
+        <v>5.1889008192543074</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18536,7 +18535,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>6.4236403361941115</v>
+        <v>5.0299664013409311</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18559,7 +18558,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>6.2230883579675966</v>
+        <v>4.875562884197981</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18582,7 +18581,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>6.1249999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18682,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-4.78</v>
+        <v>-4.7699999999999996</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18702,7 +18701,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18711,7 +18710,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18731,7 +18730,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>7.5137431112321744</v>
+        <v>7.724269306623964</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18765,7 +18764,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>626261.06678643764</v>
+        <v>626115.72996402986</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18787,7 +18786,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>392279.51308745093</v>
+        <v>392210.49972745095</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -18871,7 +18870,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.13570627044891626</v>
+        <v>-0.13569365902210184</v>
       </c>
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
@@ -18922,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>4.78</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18937,7 +18936,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>6.7708755528269453</v>
+        <v>7.0995648314473492</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18984,7 +18983,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>6.9960547144867657</v>
+        <v>7.3355372744552945</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19042,7 +19041,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>6.8448356028898916</v>
+        <v>7.1771011945027929</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19100,7 +19099,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>7.1518338343340986</v>
+        <v>7.4986225888941824</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19127,7 +19126,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>6.9969667161368578</v>
+        <v>7.3364671213525714</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19201,7 +19200,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>6.7708755528269435</v>
+        <v>7.0995648314473501</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19259,7 +19258,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>7.7585857813531236</v>
+        <v>8.1294131166856403</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19285,7 +19284,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>7.0237431112321742</v>
+        <v>7.3642693066239637</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19347,7 +19346,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>7.0202429099639359</v>
+        <v>7.3608683071354024</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19410,7 +19409,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.306465703462105</v>
+        <v>0.29523676411886662</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19443,7 +19442,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90</f>
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19461,7 +19460,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19470,7 +19469,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.77857142857142836</v>
+        <v>0.59661335497134915</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19482,7 +19481,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>2.5596731454927757</v>
+        <v>2.8803345595400174</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19492,7 +19491,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>3.3382445740642042</v>
+        <v>3.4769479145113666</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19503,7 +19502,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.52472000738099656</v>
+        <v>0.52786247083822091</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19520,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>4.78</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19533,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22813798282757203</v>
+        <v>0.22187622097249027</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19550,7 +19549,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19559,7 +19558,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.0006982963331732</v>
+        <v>0.73814429659137726</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19571,7 +19570,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>3.8680237064072402</v>
+        <v>4.0815936888806634</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19581,7 +19580,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>4.8687220027404132</v>
+        <v>4.8197379854720408</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19592,7 +19591,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.30681946568426044</v>
+        <v>0.34552393661964331</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19608,7 +19607,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19619,7 +19618,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.2627775237514614</v>
+        <v>0.93618926635390554</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19631,7 +19630,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>5.5756737343394152</v>
+        <v>5.9279464150821148</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19643,7 +19642,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>6.8384512580908767</v>
+        <v>6.8641356814360206</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -19653,7 +19652,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>2.6380784463057028E-2</v>
+        <v>6.7913543674738563E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19670,7 +19669,7 @@
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -19679,7 +19678,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.1768973214285723</v>
+        <v>0.86853712533791372</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19689,7 +19688,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>4.9993616122905742</v>
+        <v>5.27841656248264</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19699,7 +19698,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>6.1762589337191462</v>
+        <v>6.1469536878205542</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -19709,7 +19708,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.12022147767093794</v>
+        <v>0.16491459548843124</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3417AF8-9660-4976-B5BB-E5A33D5AF2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1B86A1-2CD2-458D-8DCC-8A5B0DBEA850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>4.7699999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5064.5188799999996</v>
+        <v>5096.3711999999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22187622097249027</v>
+        <v>0.21916863827977018</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.7442795460059763E-2</v>
+        <v>7.6958777988434396E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.5471698113207544E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.5471698113207544E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.10272536687631029</v>
+        <v>0.10208333333333333</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>9.2243186582809236E-2</v>
+        <v>9.1666666666666674E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.5471698113207544E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.7442795460059763E-2</v>
+        <v>7.6958777988434396E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12362787952802141</v>
+        <v>0.12285520528097128</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.20916565459530817</v>
+        <v>0.20785836925408749</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.2383223050989689</v>
+        <v>0.23683279069210034</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.19147554865827071</v>
+        <v>0.1902788264791565</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.17726619670534235</v>
+        <v>0.17615828297593394</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.11908574423164162</v>
+        <v>0.11834145833019385</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.4569693854117898E-2</v>
+        <v>9.3978633267529657E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>8.7231188286141806E-2</v>
+        <v>8.6685993359353411E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10664566818635297</v>
+        <v>0.10597913276018826</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.10090810442392903</v>
+        <v>0.10027742877127946</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14234757872992665</v>
+        <v>0.14145790636286462</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23005205975261367</v>
+        <v>0.22861423437915981</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25040937353559634</v>
+        <v>0.24884431495099885</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21566550068819174</v>
+        <v>0.21431759130889053</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17846710051162845</v>
+        <v>0.17735168113343078</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12338072279039465</v>
+        <v>0.12260959327295469</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10176642879846466</v>
+        <v>0.10113038861847426</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6455670908664874E-2</v>
+        <v>6.6040322965485718E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11914932381494055</v>
+        <v>0.11840464054109716</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12247678697566629</v>
+        <v>0.12171130705706837</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-4.7699999999999996</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>4.7699999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>4.7699999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22187622097249027</v>
+        <v>0.21916863827977018</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1B86A1-2CD2-458D-8DCC-8A5B0DBEA850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7A4766-0734-4630-9818-4F9B44A898EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5096.3711999999996</v>
+        <v>5075.1363199999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21916863827977018</v>
+        <v>0.22097107464677768</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6958777988434396E-2</v>
+        <v>7.728078124361612E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.5313807531380741E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,6 +5879,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5895,17 +5906,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.5313807531380741E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.10208333333333333</v>
+        <v>0.10251046025104602</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>9.1666666666666674E-2</v>
+        <v>9.2050209205020911E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.5313807531380741E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6958777988434396E-2</v>
+        <v>7.728078124361612E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12285520528097128</v>
+        <v>0.12336924379679123</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.20785836925408749</v>
+        <v>0.20872806954385351</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.23683279069210034</v>
+        <v>0.23782372287072834</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1902788264791565</v>
+        <v>0.19107497219664249</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.17615828297593394</v>
+        <v>0.17689534692143993</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.11834145833019385</v>
+        <v>0.11883661087550845</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.3978633267529657E-2</v>
+        <v>9.4371849306305919E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>8.6685993359353411E-2</v>
+        <v>8.7048696260438568E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10597913276018826</v>
+        <v>0.10642256009391289</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.10027742877127946</v>
+        <v>0.10069699960295844</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14145790636286462</v>
+        <v>0.14204978044806488</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22861423437915981</v>
+        <v>0.22957077929288017</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.24884431495099885</v>
+        <v>0.2498855045533043</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21431759130889053</v>
+        <v>0.21521431763235868</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17735168113343078</v>
+        <v>0.17809373837666689</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12260959327295469</v>
+        <v>0.12312260412346913</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10113038861847426</v>
+        <v>0.10155352831980678</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6040322965485718E-2</v>
+        <v>6.6316642308437534E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11840464054109716</v>
+        <v>0.11890005744712685</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12171130705706837</v>
+        <v>0.12222055938785108</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-4.8</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21916863827977018</v>
+        <v>0.22097107464677768</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7A4766-0734-4630-9818-4F9B44A898EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC847895-F871-41FC-8194-C948875F011D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>4.78</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5075.1363199999996</v>
+        <v>4884.0223999999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22097107464677768</v>
+        <v>0.2376782956740302</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.728078124361612E-2</v>
+        <v>8.0304811814018495E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.5313807531380741E-2</v>
+        <v>7.8260869565217397E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,17 +5879,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5906,6 +5895,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.5313807531380741E-2</v>
+        <v>7.8260869565217397E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.10251046025104602</v>
+        <v>0.10652173913043479</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>9.2050209205020911E-2</v>
+        <v>9.5652173913043481E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.5313807531380741E-2</v>
+        <v>7.8260869565217397E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.728078124361612E-2</v>
+        <v>8.0304811814018495E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12336924379679123</v>
+        <v>0.12819673594536135</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.20872806954385351</v>
+        <v>0.21689568965643913</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.23782372287072834</v>
+        <v>0.24712986854827862</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.19107497219664249</v>
+        <v>0.19855181893477203</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.17689534692143993</v>
+        <v>0.18381733875749631</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.11883661087550845</v>
+        <v>0.12348673912715881</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.4371849306305919E-2</v>
+        <v>9.8064660800900511E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>8.7048696260438568E-2</v>
+        <v>9.0454949592368786E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10642256009391289</v>
+        <v>0.11058692114106602</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.10069699960295844</v>
+        <v>0.1046373169787264</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14204978044806488</v>
+        <v>0.14760825011777179</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22957077929288017</v>
+        <v>0.23855398369999287</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2498855045533043</v>
+        <v>0.25966363299234663</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21521431763235868</v>
+        <v>0.22363574745275533</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17809373837666689</v>
+        <v>0.18506262379140603</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12312260412346913</v>
+        <v>0.12794044515438749</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10155352831980678</v>
+        <v>0.10552736203666879</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6316642308437534E-2</v>
+        <v>6.8911641355289446E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11890005744712685</v>
+        <v>0.12355266839071008</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12222055938785108</v>
+        <v>0.12700310301607134</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-4.78</v>
+        <v>-4.5999999999999996</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>4.78</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>4.78</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22097107464677768</v>
+        <v>0.2376782956740302</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC847895-F871-41FC-8194-C948875F011D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874696A4-65A8-464D-9F64-48ACD261BA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>4.5999999999999996</v>
+        <v>5.23</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4884.0223999999998</v>
+        <v>5552.92112</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2376782956740302</v>
+        <v>0.18276863138905441</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0304811814018495E-2</v>
+        <v>7.0631383239863302E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.8260869565217397E-2</v>
+        <v>6.8833652007648169E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,6 +5879,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5895,17 +5906,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.8260869565217397E-2</v>
+        <v>6.8833652007648169E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.10652173913043479</v>
+        <v>9.369024856596557E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>9.5652173913043481E-2</v>
+        <v>8.4130019120458879E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.8260869565217397E-2</v>
+        <v>6.8833652007648169E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0304811814018495E-2</v>
+        <v>7.0631383239863302E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12819673594536135</v>
+        <v>0.11275429930184744</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.21689568965643913</v>
+        <v>0.19076867541484124</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.24712986854827862</v>
+        <v>0.2173608786466695</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.19855181893477203</v>
+        <v>0.17463448701719908</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.18381733875749631</v>
+        <v>0.16167490598173667</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.12348673912715881</v>
+        <v>0.10861166347704214</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.8064660800900511E-2</v>
+        <v>8.625190051322032E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>9.0454949592368786E-2</v>
+        <v>7.9558846677800443E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.11058692114106602</v>
+        <v>9.7265743259828605E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.1046373169787264</v>
+        <v>9.203282181685303E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14760825011777179</v>
+        <v>0.12982752400415873</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.23855398369999287</v>
+        <v>0.20981803537666677</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.25966363299234663</v>
+        <v>0.22838483972558213</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22363574745275533</v>
+        <v>0.19669683332364715</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18506262379140603</v>
+        <v>0.16277018536146612</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12794044515438749</v>
+        <v>0.11252888101533126</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10552736203666879</v>
+        <v>9.2815653034163753E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8911641355289446E-2</v>
+        <v>6.0610621459719204E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12355266839071008</v>
+        <v>0.10866965097462072</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12700310301607134</v>
+        <v>0.11170445007149678</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-4.5999999999999996</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>4.5999999999999996</v>
+        <v>5.23</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>4.5999999999999996</v>
+        <v>5.23</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2376782956740302</v>
+        <v>0.18276863138905441</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874696A4-65A8-464D-9F64-48ACD261BA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207EAC32-2B7A-46DA-AF95-CD555F8197EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.23</v>
+        <v>5.46</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5552.92112</v>
+        <v>5797.1222399999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18276863138905441</v>
+        <v>0.16495710313199985</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.0631383239863302E-2</v>
+        <v>6.765606856126101E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.8833652007648169E-2</v>
+        <v>6.5934065934065936E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,17 +5879,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5906,6 +5895,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.8833652007648169E-2</v>
+        <v>6.5934065934065936E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.369024856596557E-2</v>
+        <v>8.9743589743589744E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4130019120458879E-2</v>
+        <v>8.0586080586080591E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.8833652007648169E-2</v>
+        <v>6.5934065934065936E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0631383239863302E-2</v>
+        <v>6.765606856126101E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11275429930184744</v>
+        <v>0.10800457607118354</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.19076867541484124</v>
+        <v>0.1827326323112857</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.2173608786466695</v>
+        <v>0.20820465115789039</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17463448701719908</v>
+        <v>0.16727808921244527</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.16167490598173667</v>
+        <v>0.15486442459422764</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10861166347704214</v>
+        <v>0.10403644688368689</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>8.625190051322032E-2</v>
+        <v>8.2618578696729367E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>7.9558846677800443E-2</v>
+        <v>7.6207466689541467E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.7265743259828605E-2</v>
+        <v>9.3168468360605064E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>9.203282181685303E-2</v>
+        <v>8.8155981337388542E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12982752400415873</v>
+        <v>0.12435859900032055</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20981803537666677</v>
+        <v>0.2009795467069537</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22838483972558213</v>
+        <v>0.21876423292395505</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19669683332364715</v>
+        <v>0.18841106928254112</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16277018536146612</v>
+        <v>0.1559135658315875</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11252888101533126</v>
+        <v>0.10778865342677335</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2815653034163753E-2</v>
+        <v>8.8905836148109235E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0610621459719204E-2</v>
+        <v>5.8057426782844583E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10866965097462072</v>
+        <v>0.10409199168448102</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11170445007149678</v>
+        <v>0.10699895125896121</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.23</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.23</v>
+        <v>5.46</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.23</v>
+        <v>5.46</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18276863138905441</v>
+        <v>0.16495710313199985</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207EAC32-2B7A-46DA-AF95-CD555F8197EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F895F-4EB3-4AF9-8814-D80024622D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.46</v>
+        <v>5.38</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5797.1222399999997</v>
+        <v>5712.1827199999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16495710313199985</v>
+        <v>0.17103273835707866</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.765606856126101E-2</v>
+        <v>6.8662106755480498E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.5934065934065936E-2</v>
+        <v>6.6914498141263934E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,6 +5879,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5895,17 +5906,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.5934065934065936E-2</v>
+        <v>6.6914498141263934E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.9743589743589744E-2</v>
+        <v>9.1078066914498143E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.0586080586080591E-2</v>
+        <v>8.1784386617100371E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5934065934065936E-2</v>
+        <v>6.6914498141263934E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.765606856126101E-2</v>
+        <v>6.8662106755480498E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10800457607118354</v>
+        <v>0.10961059207224202</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1827326323112857</v>
+        <v>0.18544984617465055</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.20820465115789039</v>
+        <v>0.21130063110075867</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16727808921244527</v>
+        <v>0.16976549574348535</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.15486442459422764</v>
+        <v>0.15716724131681839</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10403644688368689</v>
+        <v>0.10558345724626961</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>8.2618578696729367E-2</v>
+        <v>8.3847107747981847E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>7.6207466689541467E-2</v>
+        <v>7.7340663220240968E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.3168468360605064E-2</v>
+        <v>9.4553873094591762E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>8.8155981337388542E-2</v>
+        <v>8.9466850948353424E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12435859900032055</v>
+        <v>0.12620779749846658</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2009795467069537</v>
+        <v>0.20396809015241024</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21876423292395505</v>
+        <v>0.22201723267003615</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18841106928254112</v>
+        <v>0.1912127208703856</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1559135658315875</v>
+        <v>0.15823198316737319</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10778865342677335</v>
+        <v>0.10939145868219005</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8905836148109235E-2</v>
+        <v>9.0227856016482616E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8057426782844583E-2</v>
+        <v>5.8920734244299527E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10409199168448102</v>
+        <v>0.10563982799205694</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10699895125896121</v>
+        <v>0.10859001373121342</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.46</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.46</v>
+        <v>5.38</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.46</v>
+        <v>5.38</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16495710313199985</v>
+        <v>0.17103273835707866</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7F895F-4EB3-4AF9-8814-D80024622D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4FF3FA-F54E-44A7-B248-7DF18E5EFC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5712.1827199999998</v>
+        <v>5690.9478399999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17103273835707866</v>
+        <v>0.17257120575125606</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8662106755480498E-2</v>
+        <v>6.8918308646359158E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.6914498141263934E-2</v>
+        <v>6.7164179104477612E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,17 +5879,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5906,6 +5895,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.6914498141263934E-2</v>
+        <v>6.7164179104477612E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.1078066914498143E-2</v>
+        <v>9.141791044776118E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.1784386617100371E-2</v>
+        <v>8.2089552238805971E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6914498141263934E-2</v>
+        <v>6.7164179104477612E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8662106755480498E-2</v>
+        <v>6.8918308646359158E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10961059207224202</v>
+        <v>0.11001958681878024</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.18544984617465055</v>
+        <v>0.18614182321261563</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.21130063110075867</v>
+        <v>0.21208906629143312</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16976549574348535</v>
+        <v>0.17039894908581177</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.15716724131681839</v>
+        <v>0.15775368624710501</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10558345724626961</v>
+        <v>0.10597742537032284</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>8.3847107747981847E-2</v>
+        <v>8.4159970090325054E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>7.7340663220240968E-2</v>
+        <v>7.7629247784495592E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.4553873094591762E-2</v>
+        <v>9.490668605389993E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>8.9466850948353424E-2</v>
+        <v>8.9800682481742791E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12620779749846658</v>
+        <v>0.12667872211599818</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20396809015241024</v>
+        <v>0.20472916511566552</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22201723267003615</v>
+        <v>0.22284565517999899</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1912127208703856</v>
+        <v>0.19192620117214076</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15823198316737319</v>
+        <v>0.15882240101501263</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10939145868219005</v>
+        <v>0.1097996357668251</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0227856016482616E-2</v>
+        <v>9.0564527121021726E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8920734244299527E-2</v>
+        <v>5.9140587730285715E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10563982799205694</v>
+        <v>0.10603400645471388</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10859001373121342</v>
+        <v>0.10899520034961346</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.38</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17103273835707866</v>
+        <v>0.17257120575125606</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4FF3FA-F54E-44A7-B248-7DF18E5EFC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A736589-89DF-4ACD-A556-15B94FDC88FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.36</v>
+        <v>5.49</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5690.9478399999998</v>
+        <v>5828.9745599999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17257120575125606</v>
+        <v>0.16271039755997063</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8918308646359158E-2</v>
+        <v>6.7286363268576524E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.7164179104477612E-2</v>
+        <v>6.5573770491803268E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,6 +5879,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5895,17 +5906,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.7164179104477612E-2</v>
+        <v>6.5573770491803268E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.141791044776118E-2</v>
+        <v>8.9253187613843349E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2089552238805971E-2</v>
+        <v>8.0145719489981782E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.7164179104477612E-2</v>
+        <v>6.5573770491803268E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14638,50 +14638,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8918308646359158E-2</v>
+        <v>6.7286363268576524E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11001958681878024</v>
+        <v>0.10741438713090384</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.18614182321261563</v>
+        <v>0.18173409333690707</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.21208906629143312</v>
+        <v>0.20706692082369427</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.17039894908581177</v>
+        <v>0.16636400129325157</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.15775368624710501</v>
+        <v>0.15401817090792039</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10597742537032284</v>
+        <v>0.1034679417094591</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>8.4159970090325054E-2</v>
+        <v>8.2167111053577838E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>7.7629247784495592E-2</v>
+        <v>7.5791032445336318E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.490668605389993E-2</v>
+        <v>9.2659351047159139E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>8.9800682481742791E-2</v>
+        <v>8.7674254663413734E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14695,43 +14695,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12667872211599818</v>
+        <v>0.12367904381452645</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20472916511566552</v>
+        <v>0.19988129781784467</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22284565517999899</v>
+        <v>0.21756879995715747</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19192620117214076</v>
+        <v>0.18738150059793707</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15882240101501263</v>
+        <v>0.15506157913305424</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1097996357668251</v>
+        <v>0.10719964439165437</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0564527121021726E-2</v>
+        <v>8.8420011906862744E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9140587730285715E-2</v>
+        <v>5.7740173084577677E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10603400645471388</v>
+        <v>0.10352318298675162</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10899520034961346</v>
+        <v>0.10641425753623464</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.36</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.36</v>
+        <v>5.49</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.36</v>
+        <v>5.49</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17257120575125606</v>
+        <v>0.16271039755997063</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A736589-89DF-4ACD-A556-15B94FDC88FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DE1394-EF75-438B-80E5-7280F5742410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1401,10 +1398,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1501,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1550,10 +1535,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1761,10 +1742,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2457,19 +2434,43 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>百富环球</t>
+  </si>
+  <si>
     <t>0327.HK</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>IND_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>DCF</t>
   </si>
   <si>
-    <t>IND_02</t>
-  </si>
-  <si>
     <t>Latest Asset Value</t>
   </si>
   <si>
-    <t>百富环球</t>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3143,7 +3144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3888,29 +3889,33 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4232,18 +4237,18 @@
         <v>45805</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>284</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4257,7 +4262,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4266,10 +4271,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4283,7 +4288,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4293,7 +4298,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4306,19 +4311,21 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>458</v>
       </c>
-      <c r="D11" s="49"/>
+      <c r="D11" s="49" t="s">
+        <v>459</v>
+      </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
@@ -4333,17 +4340,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4357,7 +4364,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4384,34 +4391,34 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,26 +4436,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4469,7 +4476,7 @@
         <v>7.3642693066239637</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4482,7 +4489,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4493,7 +4500,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4501,7 +4508,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4512,7 +4519,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F29" s="302">
         <v>0.3674</v>
@@ -4520,7 +4527,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4531,7 +4538,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F30" s="312">
         <v>0.21740000000000001</v>
@@ -4539,7 +4546,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4550,7 +4557,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4558,7 +4565,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4569,7 +4576,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4581,7 +4588,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4590,26 +4597,26 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
-        <v>341</v>
-      </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4617,17 +4624,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4643,17 +4650,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4666,7 +4673,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4678,17 +4685,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4700,17 +4707,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4725,7 +4732,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4740,7 +4747,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4753,12 +4760,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4770,17 +4777,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4792,17 +4799,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
-        <v>340</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4814,26 +4821,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4846,7 +4853,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4859,24 +4866,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>6.7286363268576524E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>309</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C94</f>
         <v>6.5573770491803268E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4885,73 +4892,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>7.0630420943605887E-2</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.102310110249777</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>9.3039179367971361E-2</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.12803132337228806</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.62627525695225639</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.65923711258132256</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.2121620122817016</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.2121620122817016</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4964,31 +4971,31 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
-        <v>365</v>
-      </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -4997,7 +5004,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5006,7 +5013,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5018,31 +5025,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
-        <v>366</v>
-      </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5050,7 +5057,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5063,7 +5070,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5075,36 +5082,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
-        <v>368</v>
-      </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
-        <v>346</v>
-      </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5117,7 +5124,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5130,7 +5137,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5139,7 +5146,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5148,12 +5155,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5166,7 +5173,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5179,7 +5186,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5192,12 +5199,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5210,7 +5217,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5222,17 +5229,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
-        <v>369</v>
-      </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5245,7 +5252,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5258,7 +5265,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5267,29 +5274,29 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
-        <v>370</v>
-      </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5404,7 +5411,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5416,17 +5423,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
-        <v>373</v>
-      </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5435,31 +5442,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
-        <v>371</v>
-      </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
-        <v>372</v>
-      </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5468,7 +5475,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5477,7 +5484,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5490,7 +5497,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5503,7 +5510,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5532,7 +5539,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5545,7 +5552,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5558,7 +5565,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5567,12 +5574,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5601,7 +5608,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5614,7 +5621,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5627,7 +5634,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5636,12 +5643,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5670,7 +5677,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5683,7 +5690,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5696,7 +5703,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5705,12 +5712,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5739,7 +5746,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5752,7 +5759,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5765,7 +5772,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5774,7 +5781,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5783,113 +5790,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
-        <v>379</v>
-      </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>383</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
-        <v>384</v>
-      </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
-        <v>385</v>
-      </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
-        <v>386</v>
-      </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5906,13 +5902,24 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -6179,7 +6186,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351">
         <v>10638</v>
@@ -6211,7 +6218,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6227,7 +6234,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6453,7 +6460,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>1162691</v>
@@ -6489,7 +6496,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-335753</v>
@@ -6525,7 +6532,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-570451</v>
@@ -6590,7 +6597,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6743,7 +6750,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7144,7 +7151,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7193,7 +7200,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7541,12 +7548,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7595,7 +7602,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7644,7 +7651,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7693,7 +7700,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7895,7 +7902,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8147,7 +8154,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8542,7 +8549,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8553,19 +8560,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8627,7 +8634,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8648,7 +8655,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8659,7 +8666,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8669,7 +8676,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8690,7 +8697,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8754,19 +8761,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8774,7 +8781,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8801,7 +8808,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8821,7 +8828,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>88242</v>
@@ -8832,7 +8839,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8841,7 +8848,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8862,7 +8869,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>44838</v>
@@ -8882,7 +8889,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8902,7 +8909,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8961,16 +8968,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9003,7 +9010,7 @@
         <v>18219</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>34534</v>
@@ -9047,7 +9054,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9097,10 +9104,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9108,10 +9115,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9133,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9149,7 +9156,7 @@
         <v>69606</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9165,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9194,14 +9201,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>69606</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9221,7 +9228,7 @@
         <v>20153</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9240,7 +9247,7 @@
         <v>89759</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9264,13 +9271,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9278,7 +9285,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9310,7 +9317,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9337,7 +9344,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9351,7 +9358,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9363,7 +9370,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9377,7 +9384,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9394,7 +9401,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9431,10 +9438,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9443,7 +9450,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9454,12 +9461,12 @@
         <v>4.586156299298292E-3</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9470,13 +9477,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9484,7 +9491,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9495,12 +9502,12 @@
         <v>2338843.0327008888</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9510,7 +9517,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9520,7 +9527,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9530,7 +9537,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9543,7 +9550,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9555,7 +9562,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9566,12 +9573,12 @@
         <v>-465728.48364955559</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9582,12 +9589,12 @@
         <v>7.0219024921412929</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9595,12 +9602,12 @@
         <v>931456.96729911119</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9608,7 +9615,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9616,10 +9623,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9628,7 +9635,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9642,7 +9649,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9656,7 +9663,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9670,7 +9677,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9684,7 +9691,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9695,15 +9702,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9720,7 +9727,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9737,7 +9744,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9754,7 +9761,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9782,7 +9789,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
+  <dimension ref="A1:Q809"/>
   <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
@@ -10114,7 +10121,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10281,7 +10288,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10393,7 +10400,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10503,7 +10510,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10560,7 +10567,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10625,7 +10632,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10650,7 +10657,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10744,7 +10751,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10963,7 +10970,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10978,7 +10985,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11038,7 +11045,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11155,14 +11162,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-1317994</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11220,7 +11227,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11332,7 +11339,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11514,21 +11521,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11582,7 +11589,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11667,7 +11674,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11722,7 +11729,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11838,11 +11845,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11854,7 +11861,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11881,7 +11888,7 @@
         <v>6.3262169086251069E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11960,17 +11967,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12025,7 +12032,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12080,7 +12087,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12135,7 +12142,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12190,13 +12197,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12246,7 +12253,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12305,17 +12312,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12340,7 +12347,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12365,7 +12372,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12390,7 +12397,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12420,7 +12427,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
@@ -12443,7 +12450,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12635,7 +12642,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12757,7 +12764,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>356</v>
+        <v>464</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12808,7 +12815,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12922,7 +12929,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13094,7 +13101,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13201,7 +13208,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13262,7 +13269,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13380,7 +13387,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13435,1310 +13442,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0</v>
+      </c>
+      <c r="E93" s="268"/>
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
         <v>6.5573770491803268E-2</v>
       </c>
-      <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
         <v>8.9253187613843349E-2</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
         <v>8.0145719489981782E-2</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
         <v>6.5573770491803268E-2</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-5.0000000000000044E-2</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-9.9033226000115659E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.16785663168501086</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.12044499277513476</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.27348561281516237</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.14716307197324752</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.11557796797533371</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.22954904931107079</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.23199816662446882</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>1.5343490337516474E-2</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.30964378035395745</v>
+        <f>C4/G4-1</f>
+        <v>-5.0000000000000044E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-9.9033226000115659E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.16785663168501086</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.12044499277513476</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.27348561281516237</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.14716307197324752</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.11557796797533371</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.22954904931107079</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.23199816662446882</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>1.5343490337516474E-2</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-0.30964378035395745</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>-0.33173466190541689</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>-0.15675997101974881</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.18357070894353189</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>0.10463588399861634</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>0.43135144267977643</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.23078883906261005</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>0.12559697069227838</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>-0.14209230769230774</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>0.12530934617249034</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>9169505</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>9169505</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>9075329</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>9490329</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>8821278</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>7637059</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>6719223</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>5775554</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>5232216</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>4433063</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>4080199</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>2602465</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>2679525</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>2350368</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>2081977</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>1434253</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>1513374</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>1587039</v>
+        <f>BS!C4</f>
+        <v>2602465</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>2679525</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>2350368</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>2081977</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>1434253</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>1513374</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>1587039</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>1826091</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>2527293</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>2071285</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1629901</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1301459</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>1604918</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>1604918</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>1589155</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>2584479</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>2364722</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>2063487</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>1979871</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>1562946</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>1335150</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>931780</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>989600</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>7564587</v>
+        <f>BS!G30</f>
+        <v>1604918</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>1604918</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>1589155</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>2584479</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>2364722</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>2063487</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>1979871</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>1562946</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>1335150</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>931780</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>989600</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>7564587</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>7564587</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>7486174</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>6905850</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>6456556</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>5573572</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>4739352</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>4212608</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>3897066</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>3501283</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>3090599</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.45318314813057653</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.44327197339632002</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.35031368286879572</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.25822323583334716</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.19931303330108385</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.26782446312519037</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.27636080801317292</v>
+        <v>0.45318314813057653</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.30208897516211247</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>0.44327197339632002</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.3766837016665166</v>
+        <f t="shared" si="43"/>
+        <v>0.35031368286879572</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.25689712952308047</v>
+        <f t="shared" si="43"/>
+        <v>0.25822323583334716</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.22650153933125458</v>
+        <f t="shared" si="43"/>
+        <v>0.19931303330108385</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.23032149221173823</v>
+        <f t="shared" si="43"/>
+        <v>0.26782446312519037</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>0.27636080801317292</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.30208897516211247</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.3766837016665166</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.25689712952308047</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.22650153933125458</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.23032149221173823</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.6127833524292503</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>0.42057826647086138</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>0.51137475624959094</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0.31829850893849532</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>0.81324113514410579</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.931445882624059</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>0.38471239702133109</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>0.63723014208208795</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>0.41347852457766715</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>0.51127221958902824</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.6127833524292503</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>0.42057826647086138</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>0.51137475624959094</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0.31829850893849532</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>0.81324113514410579</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.931445882624059</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>0.38471239702133109</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>0.63723014208208795</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>0.41347852457766715</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>0.51127221958902824</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.8569905599828904</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>0.46257544851713722</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.53731031302840637</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.35851056586362906</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.8187505012430828</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.0011059305734258</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.41398893412673554</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.48546348441772452</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.4619567531738964</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.62055450434496751</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>9.3039179367971361E-2</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.12803132337228806</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.17261402292473829</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.17034249978466875</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.1612572865299233</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.18590635822376275</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.14899548960530343</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.13504841793817968</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.14752052307383851</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.21184681708305286</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.191145028169907</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.62627525695225639</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.65923711258132256</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.7392926471315806</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.84957033628655021</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.81575277414451741</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.73989463745140638</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.73308074460395201</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.76449964799913561</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.68634016638456818</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.65752325198175621</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.70359166305368925</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.2121620122817016</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.2121620122817016</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.2122786619707209</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.3742448793414279</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.3662512955823507</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.3702270285554756</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.417751414117373</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.3710162445686853</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.3426038973935777</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.2661253032102804</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.3201968291583606</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>7.0630420943605887E-2</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.102310110249777</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.15470164155221305</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.19887788088343192</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.17972500064092536</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.18847625903101278</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.15485492531468437</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.14154984275774057</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.13593765155632467</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.17636392145393559</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.17755069486529956</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (HKD)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.3694021343444851</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.58970498534866211</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.99772017241961986</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.1367973953220816</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.9133383670999512</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.84555975828448293</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.56803899998493046</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.45109743968414234</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.41609276812489637</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.50869983724890366</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.4813316581021414</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7286363268576524E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (HKD)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.3694021343444851</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.58970498534866211</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.99772017241961986</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.1367973953220816</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.9133383670999512</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.84555975828448293</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.56803899998493046</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.45109743968414234</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.41609276812489637</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.50869983724890366</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.4813316581021414</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>6.7286363268576524E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>0.10741438713090384</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>0.18173409333690707</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>0.20706692082369427</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>0.16636400129325157</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>0.15401817090792039</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>0.1034679417094591</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>8.2167111053577838E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>7.5791032445336318E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>9.2659351047159139E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>8.7674254663413734E-2</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.12367904381452645</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.19988129781784467</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.21756879995715747</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.18738150059793707</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.15506157913305424</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10719964439165437</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.8420011906862744E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.7740173084577677E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10352318298675162</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10641425753623464</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15420,6 +15447,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15464,20 +15492,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15488,7 +15516,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15498,7 +15526,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15509,7 +15537,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15519,15 +15547,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15537,13 +15565,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15553,13 +15581,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15569,13 +15597,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15589,7 +15617,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15620,7 +15648,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15630,23 +15658,23 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="H16" s="120"/>
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15679,7 +15707,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -15699,7 +15727,7 @@
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15721,7 +15749,7 @@
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -15743,7 +15771,7 @@
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -15775,7 +15803,7 @@
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -15807,7 +15835,7 @@
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -16451,7 +16479,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16488,7 +16516,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16709,7 +16737,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16938,19 +16966,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17075,7 +17103,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17212,7 +17240,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17224,23 +17252,23 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
         <v>382227.84</v>
       </c>
       <c r="D4" t="str">
@@ -17248,7 +17276,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17258,7 +17286,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17269,7 +17297,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17279,13 +17307,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17302,7 +17330,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17312,23 +17340,23 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="H11" s="120"/>
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17358,16 +17386,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17381,7 +17409,7 @@
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17403,7 +17431,7 @@
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -17425,7 +17453,7 @@
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -17447,7 +17475,7 @@
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -17469,7 +17497,7 @@
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -18033,7 +18061,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18070,7 +18098,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18241,7 +18269,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18460,19 +18488,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18597,7 +18625,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18661,20 +18689,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18686,14 +18714,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18722,7 +18750,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18735,7 +18763,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18745,11 +18773,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 百富环球(0327.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18770,8 +18798,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18792,8 +18820,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18803,8 +18831,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18815,10 +18843,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>449</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>443</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18829,15 +18857,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-5.6448033822130816E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18848,14 +18876,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.12852816016361679</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18872,12 +18900,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.13569365902210184</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18886,38 +18914,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>332</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>304</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18927,12 +18955,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18942,44 +18970,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -18989,55 +19017,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19047,55 +19075,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19105,24 +19133,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19135,7 +19163,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19144,12 +19172,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19164,39 +19192,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19206,55 +19234,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19264,23 +19292,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19291,7 +19319,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19300,7 +19328,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19309,15 +19337,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19325,19 +19353,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
-        <v>3.3144882254640913E-2</v>
+        <v>3.3144882254640899E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19353,20 +19381,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19376,19 +19404,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19398,14 +19426,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19414,7 +19442,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19423,12 +19451,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19438,10 +19466,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
         <v>0.36</v>
       </c>
       <c r="D77" t="str">
@@ -19451,12 +19479,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19465,7 +19493,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19477,7 +19505,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19498,7 +19526,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19510,12 +19538,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19528,7 +19556,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19540,12 +19568,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19554,7 +19582,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19566,7 +19594,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19587,7 +19615,7 @@
         <v>HKD</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19596,14 +19624,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19614,7 +19642,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19626,7 +19654,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19638,17 +19666,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>6.8641356814360206</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19660,12 +19688,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19674,7 +19702,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19684,7 +19712,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19694,17 +19722,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>6.1469536878205542</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19716,32 +19744,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DE1394-EF75-438B-80E5-7280F5742410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88C5C7C-D5B4-438A-8B30-D9A2E0F52351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.49</v>
+        <v>5.38</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5828.9745599999997</v>
+        <v>5712.1827199999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16271039755997063</v>
+        <v>0.17103273835707866</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.7286363268576524E-2</v>
+        <v>6.8662106755480498E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.5573770491803268E-2</v>
+        <v>6.6914498141263934E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.5573770491803268E-2</v>
+        <v>6.6914498141263934E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.9253187613843349E-2</v>
+        <v>9.1078066914498143E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.0145719489981782E-2</v>
+        <v>8.1784386617100371E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5573770491803268E-2</v>
+        <v>6.6914498141263934E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7286363268576524E-2</v>
+        <v>6.8662106755480498E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10741438713090384</v>
+        <v>0.10961059207224202</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.18173409333690707</v>
+        <v>0.18544984617465055</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20706692082369427</v>
+        <v>0.21130063110075867</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16636400129325157</v>
+        <v>0.16976549574348535</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.15401817090792039</v>
+        <v>0.15716724131681839</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.1034679417094591</v>
+        <v>0.10558345724626961</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>8.2167111053577838E-2</v>
+        <v>8.3847107747981847E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.5791032445336318E-2</v>
+        <v>7.7340663220240968E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.2659351047159139E-2</v>
+        <v>9.4553873094591762E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.7674254663413734E-2</v>
+        <v>8.9466850948353424E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12367904381452645</v>
+        <v>0.12620779749846658</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19988129781784467</v>
+        <v>0.20396809015241024</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21756879995715747</v>
+        <v>0.22201723267003615</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18738150059793707</v>
+        <v>0.1912127208703856</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15506157913305424</v>
+        <v>0.15823198316737319</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10719964439165437</v>
+        <v>0.10939145868219005</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8420011906862744E-2</v>
+        <v>9.0227856016482616E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7740173084577677E-2</v>
+        <v>5.8920734244299527E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10352318298675162</v>
+        <v>0.10563982799205694</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10641425753623464</v>
+        <v>0.10859001373121342</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.49</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.49</v>
+        <v>5.38</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.49</v>
+        <v>5.38</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16271039755997063</v>
+        <v>0.17103273835707866</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88C5C7C-D5B4-438A-8B30-D9A2E0F52351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B86A5-AD97-4A67-B9A1-B4B3CB855999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5712.1827199999998</v>
+        <v>5988.2361600000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17103273835707866</v>
+        <v>0.15172626756600405</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.8662106755480498E-2</v>
+        <v>6.5496832330582455E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.6914498141263934E-2</v>
+        <v>6.3829787234042548E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.6914498141263934E-2</v>
+        <v>6.3829787234042548E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.1078066914498143E-2</v>
+        <v>8.6879432624113476E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>8.1784386617100371E-2</v>
+        <v>7.8014184397163122E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6914498141263934E-2</v>
+        <v>6.3829787234042548E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8662106755480498E-2</v>
+        <v>6.5496832330582455E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10961059207224202</v>
+        <v>0.10455762151572023</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.18544984617465055</v>
+        <v>0.17690073979071275</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.21130063110075867</v>
+        <v>0.2015598218656173</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16976549574348535</v>
+        <v>0.1619394267907715</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.15716724131681839</v>
+        <v>0.14992194295824166</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10558345724626961</v>
+        <v>0.10071613474910115</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>8.3847107747981847E-2</v>
+        <v>7.9981815546833757E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.7340663220240968E-2</v>
+        <v>7.3775313497322054E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.4553873094591762E-2</v>
+        <v>9.0195006604415554E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.9466850948353424E-2</v>
+        <v>8.5342492571301679E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12620779749846658</v>
+        <v>0.1203897075428635</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20396809015241024</v>
+        <v>0.1945653058546041</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.22201723267003615</v>
+        <v>0.21178239570297774</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1912127208703856</v>
+        <v>0.18239795005011961</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15823198316737319</v>
+        <v>0.15093760096462194</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10939145868219005</v>
+        <v>0.10434859001953591</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0227856016482616E-2</v>
+        <v>8.6068415845510005E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8920734244299527E-2</v>
+        <v>5.6204530183392103E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10563982799205694</v>
+        <v>0.10076990684348695</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10859001373121342</v>
+        <v>0.10358409111239861</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.38</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17103273835707866</v>
+        <v>0.15172626756600405</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B86A5-AD97-4A67-B9A1-B4B3CB855999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAB2C69-F5A6-4754-86AE-79DA96BCEC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5988.2361600000004</v>
+        <v>5839.5919999999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15172626756600405</v>
+        <v>0.1619652657876085</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.5496832330582455E-2</v>
+        <v>6.7164024426270008E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3829787234042548E-2</v>
+        <v>6.5454545454545446E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3829787234042548E-2</v>
+        <v>6.5454545454545446E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.6879432624113476E-2</v>
+        <v>8.9090909090909096E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.8014184397163122E-2</v>
+        <v>0.08</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3829787234042548E-2</v>
+        <v>6.5454545454545446E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5496832330582455E-2</v>
+        <v>6.7164024426270008E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10455762151572023</v>
+        <v>0.1072190882452113</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17690073979071275</v>
+        <v>0.18140366771265815</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.2015598218656173</v>
+        <v>0.20669043551310573</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.1619394267907715</v>
+        <v>0.16606152129090021</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.14992194295824166</v>
+        <v>0.15373813786990598</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10071613474910115</v>
+        <v>0.10327981817907826</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.9981815546833757E-2</v>
+        <v>8.2017716306207702E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.3775313497322054E-2</v>
+        <v>7.5653230568162977E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.0195006604415554E-2</v>
+        <v>9.2490879499800671E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.5342492571301679E-2</v>
+        <v>8.7514846927662079E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1203897075428635</v>
+        <v>0.12345417282577276</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1945653058546041</v>
+        <v>0.19951787727635767</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21178239570297774</v>
+        <v>0.21717322032087175</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18239795005011961</v>
+        <v>0.18704080696048628</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15093760096462194</v>
+        <v>0.15477964898917596</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10434859001953591</v>
+        <v>0.1070047359473059</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6068415845510005E-2</v>
+        <v>8.8259248248850258E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6204530183392103E-2</v>
+        <v>5.7635190951696627E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10076990684348695</v>
+        <v>0.1033349590176848</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10358409111239861</v>
+        <v>0.10622077706798694</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.64</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15172626756600405</v>
+        <v>0.1619652657876085</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAB2C69-F5A6-4754-86AE-79DA96BCEC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124D9104-AC9E-4553-907B-A045DCA1E43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5839.5919999999996</v>
+        <v>5924.5315199999995</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1619652657876085</v>
+        <v>0.15607090064212614</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.7164024426270008E-2</v>
+        <v>6.6201099344889797E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.5454545454545446E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.5454545454545446E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.9090909090909096E-2</v>
+        <v>8.7813620071684584E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>0.08</v>
+        <v>7.8853046594982074E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5454545454545446E-2</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7164024426270008E-2</v>
+        <v>6.6201099344889797E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.1072190882452113</v>
+        <v>0.10568189701588927</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.18140366771265815</v>
+        <v>0.17880289828308599</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20669043551310573</v>
+        <v>0.20372713177815083</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16606152129090021</v>
+        <v>0.16368071094981204</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.15373813786990598</v>
+        <v>0.15153400686101845</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10327981817907826</v>
+        <v>0.10179910393995169</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>8.2017716306207702E-2</v>
+        <v>8.084183506884271E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.5653230568162977E-2</v>
+        <v>7.4568596438153473E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.2490879499800671E-2</v>
+        <v>9.1164845385108176E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.7514846927662079E-2</v>
+        <v>8.6260153781745771E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12345417282577276</v>
+        <v>0.12168422052719537</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19951787727635767</v>
+        <v>0.19665740591755684</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21717322032087175</v>
+        <v>0.2140596257643001</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18704080696048628</v>
+        <v>0.18435921833022842</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15477964898917596</v>
+        <v>0.15256058592123078</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1070047359473059</v>
+        <v>0.10547061786920833</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8259248248850258E-2</v>
+        <v>8.6993882682558504E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7635190951696627E-2</v>
+        <v>5.6808879970310297E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1033349590176848</v>
+        <v>0.10185345422890078</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10622077706798694</v>
+        <v>0.10469789854371472</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.5</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1619652657876085</v>
+        <v>0.15607090064212614</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124D9104-AC9E-4553-907B-A045DCA1E43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE0736D-6F2C-443C-A285-0AE5A172FBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5924.5315199999995</v>
+        <v>5882.0617599999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15607090064212614</v>
+        <v>0.15900337065231462</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.6201099344889797E-2</v>
+        <v>6.6679085621748208E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.4516129032258063E-2</v>
+        <v>6.4981949458483748E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4516129032258063E-2</v>
+        <v>6.4981949458483748E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.7813620071684584E-2</v>
+        <v>8.8447653429602882E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.8853046594982074E-2</v>
+        <v>7.9422382671480149E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4516129032258063E-2</v>
+        <v>6.4981949458483748E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6201099344889797E-2</v>
+        <v>6.6679085621748208E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10568189701588927</v>
+        <v>0.10644494320372962</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17880289828308599</v>
+        <v>0.18009389393855954</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20372713177815083</v>
+        <v>0.20519808579820967</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16368071094981204</v>
+        <v>0.16486252113717531</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.15153400686101845</v>
+        <v>0.15262811521380559</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10179910393995169</v>
+        <v>0.10253411552074557</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>8.084183506884271E-2</v>
+        <v>8.1425530628906562E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.4568596438153473E-2</v>
+        <v>7.5106997856479493E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.1164845385108176E-2</v>
+        <v>9.1823075315686578E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.6260153781745771E-2</v>
+        <v>8.688297077655982E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12168422052719537</v>
+        <v>0.12256280695699462</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19665740591755684</v>
+        <v>0.19807731498555364</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2140596257643001</v>
+        <v>0.21560518262902428</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18435921833022842</v>
+        <v>0.18569033181997735</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15256058592123078</v>
+        <v>0.15366210639719635</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10547061786920833</v>
+        <v>0.10623213857584521</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6993882682558504E-2</v>
+        <v>8.7621997358966863E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6808879970310297E-2</v>
+        <v>5.7219052388868492E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10185345422890078</v>
+        <v>0.1025888582305535</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10469789854371472</v>
+        <v>0.10545384004944552</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.58</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15607090064212614</v>
+        <v>0.15900337065231462</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE0736D-6F2C-443C-A285-0AE5A172FBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EC96E1-38E0-416F-B1F4-D73C6D1762EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.54</v>
+        <v>5.68</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>5882.0617599999996</v>
+        <v>6030.7059200000003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15900337065231462</v>
+        <v>0.1488651799509968</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.6679085621748208E-2</v>
+        <v>6.5035587032479761E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.4981949458483748E-2</v>
+        <v>6.3380281690140844E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4981949458483748E-2</v>
+        <v>6.3380281690140844E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.8447653429602882E-2</v>
+        <v>8.6267605633802813E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.9422382671480149E-2</v>
+        <v>7.7464788732394374E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4981949458483748E-2</v>
+        <v>6.3380281690140844E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6679085621748208E-2</v>
+        <v>6.5035587032479761E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10644494320372962</v>
+        <v>0.10382130023744052</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.18009389393855954</v>
+        <v>0.17565495993303168</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20519808579820967</v>
+        <v>0.20014038650036647</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16486252113717531</v>
+        <v>0.16079900829224494</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.15262811521380559</v>
+        <v>0.14886615462754982</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10253411552074557</v>
+        <v>0.10000686619453002</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>8.1425530628906562E-2</v>
+        <v>7.9418563324672953E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.5106997856479493E-2</v>
+        <v>7.3255769036073309E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.1823075315686578E-2</v>
+        <v>8.9559830501567544E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.688297077655982E-2</v>
+        <v>8.4741489102489687E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12256280695699462</v>
+        <v>0.11954189270101236</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19807731498555364</v>
+        <v>0.19319512764436042</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21560518262902428</v>
+        <v>0.21029097038112579</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18569033181997735</v>
+        <v>0.18111345744413285</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15366210639719635</v>
+        <v>0.14987466011275841</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10623213857584521</v>
+        <v>0.10361374079404621</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7621997358966863E-2</v>
+        <v>8.5462300240964156E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7219052388868492E-2</v>
+        <v>5.5808723632804834E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1025888582305535</v>
+        <v>0.10006025961219478</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10545384004944552</v>
+        <v>0.1028546256820296</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.54</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.54</v>
+        <v>5.68</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.54</v>
+        <v>5.68</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15900337065231462</v>
+        <v>0.1488651799509968</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EC96E1-38E0-416F-B1F4-D73C6D1762EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2ED58A7-AA4C-459E-B2DC-9EC574297109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.68</v>
+        <v>5.84</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6030.7059200000003</v>
+        <v>6200.5849600000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1488651799509968</v>
+        <v>0.13769337180705166</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.5035587032479761E-2</v>
+        <v>6.3253790127480322E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3380281690140844E-2</v>
+        <v>6.1643835616438353E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3380281690140844E-2</v>
+        <v>6.1643835616438353E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.6267605633802813E-2</v>
+        <v>8.3904109589041098E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.7464788732394374E-2</v>
+        <v>7.5342465753424653E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3380281690140844E-2</v>
+        <v>6.1643835616438353E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5035587032479761E-2</v>
+        <v>6.3253790127480322E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10382130023744052</v>
+        <v>0.1009768810528531</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17565495993303168</v>
+        <v>0.17084249527733217</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.20014038650036647</v>
+        <v>0.19465708824008246</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.16079900829224494</v>
+        <v>0.15639355601026561</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.14886615462754982</v>
+        <v>0.14478762984323337</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10000686619453002</v>
+        <v>9.7266952052214126E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.9418563324672953E-2</v>
+        <v>7.7242712274681907E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.3255769036073309E-2</v>
+        <v>7.1248761665221982E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.9559830501567544E-2</v>
+        <v>8.7106136515223226E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.4741489102489687E-2</v>
+        <v>8.2419804469544763E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11954189270101236</v>
+        <v>0.11626677235303941</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19319512764436042</v>
+        <v>0.18790211044862451</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21029097038112579</v>
+        <v>0.20452957393232782</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18111345744413285</v>
+        <v>0.17615144491141688</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14987466011275841</v>
+        <v>0.145768505041176</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10361374079404621</v>
+        <v>0.1007750081695518</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5462300240964156E-2</v>
+        <v>8.3120867357650077E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5808723632804834E-2</v>
+        <v>5.427971750587867E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10006025961219478</v>
+        <v>9.7318882636518222E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1028546256820296</v>
+        <v>0.10003669073183702</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.68</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.68</v>
+        <v>5.84</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.68</v>
+        <v>5.84</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1488651799509968</v>
+        <v>0.13769337180705166</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2ED58A7-AA4C-459E-B2DC-9EC574297109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339CE20D-87F9-484C-8951-0196D8D9D998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.84</v>
+        <v>5.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6200.5849600000001</v>
+        <v>6253.6721600000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13769337180705166</v>
+        <v>0.13428855707897047</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.3253790127480322E-2</v>
+        <v>6.2716830958316649E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.1643835616438353E-2</v>
+        <v>6.1120543293718167E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1643835616438353E-2</v>
+        <v>6.1120543293718167E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.3904109589041098E-2</v>
+        <v>8.3191850594227512E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.5342465753424653E-2</v>
+        <v>7.470288624787777E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1643835616438353E-2</v>
+        <v>6.1120543293718167E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.3253790127480322E-2</v>
+        <v>6.2716830958316649E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.1009768810528531</v>
+        <v>0.10011969190978984</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17084249527733217</v>
+        <v>0.16939221942608149</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19465708824008246</v>
+        <v>0.19300465115824816</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15639355601026561</v>
+        <v>0.15506593668929564</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.14478762984323337</v>
+        <v>0.14355853281570169</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.7266952052214126E-2</v>
+        <v>9.6441256364164771E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.7242712274681907E-2</v>
+        <v>7.6587001644166791E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.1248761665221982E-2</v>
+        <v>7.0643933467724351E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.7106136515223226E-2</v>
+        <v>8.6366695627997231E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.2419804469544763E-2</v>
+        <v>8.1720145687969675E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11626677235303941</v>
+        <v>0.1152797878678693</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18790211044862451</v>
+        <v>0.18630701613242226</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20452957393232782</v>
+        <v>0.2027933296714422</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17615144491141688</v>
+        <v>0.17465610157600586</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.145768505041176</v>
+        <v>0.14453108139906073</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1007750081695518</v>
+        <v>9.9919532718197368E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3120867357650077E-2</v>
+        <v>8.2415257278213319E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.427971750587867E-2</v>
+        <v>5.3818938919241333E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7318882636518222E-2</v>
+        <v>9.6492746111590214E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10003669073183702</v>
+        <v>9.918748283088763E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.84</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.84</v>
+        <v>5.89</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.84</v>
+        <v>5.89</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13769337180705166</v>
+        <v>0.13428855707897047</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339CE20D-87F9-484C-8951-0196D8D9D998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D9C6EC-E0CE-44F6-AC40-2784728F1778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6253.6721600000001</v>
+        <v>6306.75936</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13428855707897047</v>
+        <v>0.13092342716051064</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.2716830958316649E-2</v>
+        <v>6.2188911505805571E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.1120543293718167E-2</v>
+        <v>6.0606060606060601E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1120543293718167E-2</v>
+        <v>6.0606060606060601E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.3191850594227512E-2</v>
+        <v>8.2491582491582491E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.470288624787777E-2</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1120543293718167E-2</v>
+        <v>6.0606060606060601E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2716830958316649E-2</v>
+        <v>6.2188911505805571E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10011969190978984</v>
+        <v>9.9276933560380823E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16939221942608149</v>
+        <v>0.16796635899320198</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.19300465115824816</v>
+        <v>0.1913800328825053</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15506593668929564</v>
+        <v>0.15376066786194464</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.14355853281570169</v>
+        <v>0.14235012765732036</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.6441256364164771E-2</v>
+        <v>9.5629461276924316E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.6587001644166791E-2</v>
+        <v>7.5942329913155276E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.0643933467724351E-2</v>
+        <v>7.0049287563113863E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.6366695627997231E-2</v>
+        <v>8.563970324055617E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.1720145687969675E-2</v>
+        <v>8.1032265673761178E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1152797878678693</v>
+        <v>0.11430941928312292</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18630701613242226</v>
+        <v>0.18473877525588672</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.2027933296714422</v>
+        <v>0.20108631511191827</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17465610157600586</v>
+        <v>0.17318593237082064</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14453108139906073</v>
+        <v>0.14331448980479256</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9919532718197368E-2</v>
+        <v>9.9078459210468428E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2415257278213319E-2</v>
+        <v>8.172152615634283E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3818938919241333E-2</v>
+        <v>5.3365917547867243E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6492746111590214E-2</v>
+        <v>9.5680517608967411E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.918748283088763E-2</v>
+        <v>9.8352571359247173E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.89</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13428855707897047</v>
+        <v>0.13092342716051064</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D9C6EC-E0CE-44F6-AC40-2784728F1778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D387A93E-A03F-4C62-8D77-449BDBDF4D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.94</v>
+        <v>6.2</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6306.75936</v>
+        <v>6582.8127999999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13092342716051064</v>
+        <v>0.11403451889514371</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>3.4769479145113666</v>
+        <v>3.6036658259915511</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4522,7 +4522,7 @@
         <v>420</v>
       </c>
       <c r="F29" s="302">
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>4.8197379854720408</v>
+        <v>4.4732258849914697</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4541,7 +4541,7 @@
         <v>433</v>
       </c>
       <c r="F30" s="312">
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.2188911505805571E-2</v>
+        <v>5.9580989410400818E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.0606060606060601E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.59661335497134915</v>
+        <v>0.61051668952903526</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>2.8803345595400174</v>
+        <v>2.9931491364625158</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>3.4769479145113666</v>
+        <v>3.6036658259915511</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52786247083822091</v>
+        <v>0.51065534461780882</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.73814429659137726</v>
+        <v>0.70272000000000001</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>4.0815936888806634</v>
+        <v>3.7705058849914694</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>4.8197379854720408</v>
+        <v>4.4732258849914697</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34552393661964331</v>
+        <v>0.39257709098607751</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0606060606060601E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2491582491582491E-2</v>
+        <v>7.9032258064516123E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.407407407407407E-2</v>
+        <v>7.0967741935483872E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0606060606060601E-2</v>
+        <v>5.8064516129032254E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2188911505805571E-2</v>
+        <v>5.9580989410400818E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.9276933560380823E-2</v>
+        <v>9.5113707314300341E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16796635899320198</v>
+        <v>0.1609226084547774</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.1913800328825053</v>
+        <v>0.18335441860033574</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15376066786194464</v>
+        <v>0.14731263985483084</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.14235012765732036</v>
+        <v>0.1363806061749166</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.5629461276924316E-2</v>
+        <v>9.1619193545956518E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.5942329913155276E-2</v>
+        <v>7.2757651561958445E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>7.0049287563113863E-2</v>
+        <v>6.7111736794338128E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.563970324055617E-2</v>
+        <v>8.2048360846597362E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>8.1032265673761178E-2</v>
+        <v>7.7634138403571196E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11430941928312292</v>
+        <v>0.10951579847447583</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18473877525588672</v>
+        <v>0.17699166532580116</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20108631511191827</v>
+        <v>0.19265366318787008</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17318593237082064</v>
+        <v>0.16592329649720558</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14331448980479256</v>
+        <v>0.1373045273291077</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9078459210468428E-2</v>
+        <v>9.4923556082287502E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.172152615634283E-2</v>
+        <v>7.8294494414302654E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3365917547867243E-2</v>
+        <v>5.1127991973279267E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5680517608967411E-2</v>
+        <v>9.1668108806010701E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8352571359247173E-2</v>
+        <v>9.4228108689343254E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.94</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.94</v>
+        <v>6.2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.59661335497134915</v>
+        <v>0.61051668952903526</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>2.8803345595400174</v>
+        <v>2.9931491364625158</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>3.4769479145113666</v>
+        <v>3.6036658259915511</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.52786247083822091</v>
+        <v>0.51065534461780882</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.94</v>
+        <v>6.2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13092342716051064</v>
+        <v>0.11403451889514371</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.73814429659137726</v>
+        <v>0.70272000000000001</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>4.0815936888806634</v>
+        <v>3.7705058849914694</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>4.8197379854720408</v>
+        <v>4.4732258849914697</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.34552393661964331</v>
+        <v>0.39257709098607751</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D387A93E-A03F-4C62-8D77-449BDBDF4D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8369312F-03A6-40BC-B242-E3708F91CFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>6.2</v>
+        <v>6.13</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6582.8127999999997</v>
+        <v>6508.4907199999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11403451889514371</v>
+        <v>0.11848407485522605</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.9580989410400818E-2</v>
+        <v>6.0261359599426606E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.8064516129032254E-2</v>
+        <v>5.872756933115824E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8064516129032254E-2</v>
+        <v>5.872756933115824E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.9032258064516123E-2</v>
+        <v>7.9934747145187598E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.0967741935483872E-2</v>
+        <v>7.1778140293637854E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.8064516129032254E-2</v>
+        <v>5.872756933115824E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9580989410400818E-2</v>
+        <v>6.0261359599426606E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.5113707314300341E-2</v>
+        <v>9.6199834477758914E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1609226084547774</v>
+        <v>0.16276022388574549</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18335441860033574</v>
+        <v>0.18544818847016012</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14731263985483084</v>
+        <v>0.14899483965741456</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.1363806061749166</v>
+        <v>0.13793797035635938</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.1619193545956518E-2</v>
+        <v>9.2665415984491101E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.2757651561958445E-2</v>
+        <v>7.3588489344884558E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7111736794338128E-2</v>
+        <v>6.7878102467356663E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.2048360846597362E-2</v>
+        <v>8.2985291557733057E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.7634138403571196E-2</v>
+        <v>7.8520662006874617E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10951579847447583</v>
+        <v>0.11076638671154163</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17699166532580116</v>
+        <v>0.17901277732789023</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19265366318787008</v>
+        <v>0.19485362345265816</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16592329649720558</v>
+        <v>0.16781801603306273</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1373045273291077</v>
+        <v>0.13887244199681367</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4923556082287502E-2</v>
+        <v>9.6007511861367453E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8294494414302654E-2</v>
+        <v>7.9188558787712304E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1127991973279267E-2</v>
+        <v>5.1711835274768587E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1668108806010701E-2</v>
+        <v>9.2714889820108712E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4228108689343254E-2</v>
+        <v>9.5304122981064956E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.2</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.2</v>
+        <v>6.13</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.2</v>
+        <v>6.13</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11403451889514371</v>
+        <v>0.11848407485522605</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8369312F-03A6-40BC-B242-E3708F91CFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50810EB-4598-4CA0-8104-702A805FEB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6508.4907199999998</v>
+        <v>6466.0209599999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11848407485522605</v>
+        <v>0.12105828462833323</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0261359599426606E-2</v>
+        <v>6.0657164916992627E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.872756933115824E-2</v>
+        <v>5.9113300492610835E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,20 +13467,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.872756933115824E-2</v>
+        <v>5.9113300492610835E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.9934747145187598E-2</v>
+        <v>8.0459770114942528E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.1778140293637854E-2</v>
+        <v>7.224958949096881E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.872756933115824E-2</v>
+        <v>5.9113300492610835E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0261359599426606E-2</v>
+        <v>6.0657164916992627E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.6199834477758914E-2</v>
+        <v>9.6831688891405934E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16276022388574549</v>
+        <v>0.16382925655494579</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18544818847016012</v>
+        <v>0.18666623896914311</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14899483965741456</v>
+        <v>0.14997345929391645</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13793797035635938</v>
+        <v>0.13884396687758341</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.2665415984491101E-2</v>
+        <v>9.3274055826753771E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.3588489344884558E-2</v>
+        <v>7.4071829176378057E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7878102467356663E-2</v>
+        <v>6.8323935652692347E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.2985291557733057E-2</v>
+        <v>8.353035094399075E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.8520662006874617E-2</v>
+        <v>7.9036397061106961E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11076638671154163</v>
+        <v>0.11149391634511498</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17901277732789023</v>
+        <v>0.18018855911657916</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19485362345265816</v>
+        <v>0.19613345020768383</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16781801603306273</v>
+        <v>0.16892026901193341</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13887244199681367</v>
+        <v>0.13978457626280258</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6007511861367453E-2</v>
+        <v>9.663810307227956E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9188558787712304E-2</v>
+        <v>7.9708680684511729E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1711835274768587E-2</v>
+        <v>5.2051486081171008E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2714889820108712E-2</v>
+        <v>9.3323854613672638E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5304122981064956E-2</v>
+        <v>9.5930094232172108E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.13</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11848407485522605</v>
+        <v>0.12105828462833323</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50810EB-4598-4CA0-8104-702A805FEB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8121805F-0532-4573-8EB7-C5CDE0F60260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>Y</t>
@@ -4243,7 +4247,7 @@
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4274,7 +4278,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4321,10 +4325,10 @@
         <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4418,7 +4422,7 @@
         <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4426,7 +4430,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4439,7 +4443,7 @@
         <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4447,7 +4451,7 @@
         <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6597,7 +6601,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12764,7 +12768,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19786,4 +19790,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8121805F-0532-4573-8EB7-C5CDE0F60260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE7F847-C1B5-4EBF-B4A2-E04825BB5F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2501,7 +2514,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2941,6 +2954,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3144,11 +3163,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3933,9 +3953,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{00F37BA5-8C88-4ABE-B544-13B3F4130A2D}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4020,6 +4046,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>1061744000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>6.09</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>7.4999999999999997E-2</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19793,22 +19902,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D578CBAA-219F-41EA-A9BF-E2ADF6C97C9D}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE7F847-C1B5-4EBF-B4A2-E04825BB5F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1C2D24-5515-4120-BEB1-0F74A52726B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3917,47 +3917,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4504,13 +4504,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4710,13 +4710,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4763,13 +4763,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4798,13 +4798,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4820,13 +4820,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4890,13 +4890,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4912,13 +4912,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4934,22 +4934,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5084,13 +5084,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5143,22 +5143,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5195,13 +5195,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5214,13 +5214,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5342,13 +5342,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5387,13 +5387,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5536,13 +5536,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5555,22 +5555,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5903,13 +5903,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5917,13 +5917,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5946,13 +5946,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5960,22 +5960,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5999,6 +5999,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6015,17 +6026,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -15660,10 +15660,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15678,8 +15678,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15694,8 +15694,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15710,8 +15710,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -17420,8 +17420,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18886,11 +18886,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 百富环球(0327.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18911,8 +18911,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18933,8 +18933,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18944,8 +18944,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18958,8 +18958,8 @@
       <c r="B11" s="159" t="s">
         <v>443</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18977,8 +18977,8 @@
         <v>-5.6448033822130816E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18995,8 +18995,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.12852816016361679</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19013,8 +19013,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.13569365902210184</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19040,21 +19040,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19068,8 +19068,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19083,8 +19083,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19104,8 +19104,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19115,8 +19115,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19130,8 +19130,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19141,8 +19141,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19162,8 +19162,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19173,8 +19173,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19188,8 +19188,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19199,8 +19199,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19220,8 +19220,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19231,8 +19231,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19246,8 +19246,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19258,8 +19258,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19321,8 +19321,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19332,8 +19332,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19347,8 +19347,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19358,8 +19358,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19379,8 +19379,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19390,8 +19390,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19405,8 +19405,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19416,8 +19416,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19906,19 +19906,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1C2D24-5515-4120-BEB1-0F74A52726B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A2DDC6-A3C2-4E0F-B702-46366AC68A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="466">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="560">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2331,136 +2123,1151 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>Y</t>
@@ -3168,7 +3975,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3917,33 +4724,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3958,10 +4787,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{00F37BA5-8C88-4ABE-B544-13B3F4130A2D}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{0500429E-0EED-4D3B-B90D-D3AAA0ED5EAD}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4328,6 +5162,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45805</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>INT</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>百富环球</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>1061744000</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>0327.HK</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>6.09</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>6466.0209599999998</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>IND_02</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (HKD) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>7.3642693066239637</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>0.12105828462833323</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0327.HK (HKD)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>3.6036658259915511</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>4.4732258849914697</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>6.8641356814360206</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>6.1469536878205542</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>536120.13620533235</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>3725.8278691964447</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-5556</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-1830.1721308035553</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-8506.973328445607</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-133572.49101863219</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>626115.72996402986</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>392210.49972745095</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>6.0657164916992627E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>5.9113300492610835E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.9745476989157914</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>7.0630420943605887E-2</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.102310110249777</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>9.3039179367971361E-2</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.12803132337228806</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.62627525695225639</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.65923711258132256</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.2121620122817016</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.2121620122817016</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>4.9253617912598004</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>87825</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>8.2717679591313917E-2</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>1.1610019159010268E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.16381589511191816</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>3270300</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>2338843.0327008888</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.2028314101147628</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>57429</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.4089309664099819E-2</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>7.0995648314473492</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>3.7980767021052162</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.06</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>8.13 HKD</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.05</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>7.5 HKD</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.03</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>7.34 HKD</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>7.18 HKD</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>7.1 HKD</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>7.3642693066239637</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.36</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>0327.HK</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.61051668952903526</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>2.9931491364625158</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>3.6036658259915511</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.51065534461780882</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.70272000000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>3.7705058849914694</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>4.4732258849914697</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.39257709098607751</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.93618926635390554</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>5.9279464150821148</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>6.8641356814360206</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>6.7913543674738563E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.86853712533791372</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>5.27841656248264</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>6.1469536878205542</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.16491459548843124</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4344,24 +6921,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45805</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4375,7 +6952,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4384,15 +6961,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>1061744000</v>
@@ -4401,7 +6978,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4411,7 +6988,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4424,26 +7001,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>6.09</v>
@@ -4453,17 +7030,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4477,7 +7054,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4491,7 +7068,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4504,71 +7081,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4589,7 +7166,7 @@
         <v>7.3642693066239637</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4602,7 +7179,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4613,7 +7190,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4621,7 +7198,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4632,7 +7209,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="F29" s="302">
         <v>0.35</v>
@@ -4640,7 +7217,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4651,7 +7228,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F30" s="312">
         <v>0.25</v>
@@ -4659,7 +7236,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4670,7 +7247,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4678,7 +7255,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4689,7 +7266,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4701,7 +7278,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4709,27 +7286,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4737,17 +7314,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4763,17 +7340,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4786,7 +7363,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4798,17 +7375,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4820,17 +7397,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4845,7 +7422,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4860,7 +7437,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4873,12 +7450,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4890,17 +7467,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4912,17 +7489,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4934,26 +7511,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4966,7 +7543,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4979,7 +7556,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4989,14 +7566,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>5.9113300492610835E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5005,18 +7582,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5071,7 +7648,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5082,33 +7659,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5117,7 +7694,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5126,7 +7703,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5138,31 +7715,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5170,7 +7747,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5183,7 +7760,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5195,36 +7772,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5237,7 +7814,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5250,7 +7827,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5259,7 +7836,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5268,12 +7845,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5286,7 +7863,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5299,7 +7876,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5312,12 +7889,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5330,7 +7907,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5342,17 +7919,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5365,7 +7942,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5378,7 +7955,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5386,30 +7963,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5524,7 +8101,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5536,17 +8113,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5555,31 +8132,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5588,7 +8165,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5597,7 +8174,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5610,7 +8187,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5623,7 +8200,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5652,7 +8229,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5665,7 +8242,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5678,7 +8255,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5687,12 +8264,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5721,7 +8298,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5734,7 +8311,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5747,7 +8324,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5756,12 +8333,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5790,7 +8367,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5803,7 +8380,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5816,7 +8393,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5825,12 +8402,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5859,7 +8436,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5872,7 +8449,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5885,7 +8462,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5894,7 +8471,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5903,113 +8480,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6026,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6050,7 +8627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6115,7 +8692,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6131,7 +8708,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1000</v>
@@ -6139,7 +8716,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>6044878</v>
@@ -6175,7 +8752,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>3191489</v>
@@ -6211,7 +8788,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>2090422</v>
@@ -6247,7 +8824,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>772428</v>
@@ -6283,7 +8860,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351"/>
       <c r="D8" s="351"/>
@@ -6299,7 +8876,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351">
         <v>10638</v>
@@ -6331,7 +8908,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6347,7 +8924,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6363,7 +8940,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>5556</v>
@@ -6387,7 +8964,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>20661</v>
@@ -6411,7 +8988,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>140323</v>
@@ -6447,7 +9024,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>720922</v>
@@ -6483,7 +9060,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>7495</v>
@@ -6519,13 +9096,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351"/>
       <c r="D19" s="351"/>
@@ -6541,7 +9118,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6557,7 +9134,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6573,7 +9150,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>1162691</v>
@@ -6609,7 +9186,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-335753</v>
@@ -6645,7 +9222,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-570451</v>
@@ -6707,15 +9284,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6752,7 +9329,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6789,7 +9366,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6826,7 +9403,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6863,7 +9440,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6900,7 +9477,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6916,12 +9493,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -6970,7 +9547,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7019,7 +9596,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7068,7 +9645,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7117,7 +9694,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7166,7 +9743,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7215,7 +9792,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7264,7 +9841,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7313,7 +9890,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7362,7 +9939,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7411,7 +9988,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7460,7 +10037,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7509,7 +10086,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7558,12 +10135,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7612,7 +10189,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7661,12 +10238,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7715,7 +10292,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7764,7 +10341,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7813,7 +10390,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7862,13 +10439,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7917,7 +10494,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7966,7 +10543,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8015,7 +10592,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8064,7 +10641,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8113,7 +10690,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8168,7 +10745,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8267,7 +10844,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8366,7 +10943,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8382,13 +10959,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8437,7 +11014,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8471,7 +11048,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8505,7 +11082,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8554,7 +11131,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8626,7 +11203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8646,7 +11223,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8662,7 +11239,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8673,27 +11250,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>58581+2543884</f>
@@ -8704,7 +11281,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <f>162490+3083598</f>
@@ -8716,7 +11293,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8726,7 +11303,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>24212</v>
@@ -8737,7 +11314,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>1587039</v>
@@ -8747,7 +11324,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8758,7 +11335,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8768,7 +11345,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8779,7 +11356,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8789,7 +11366,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8800,7 +11377,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
@@ -8810,7 +11387,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8821,7 +11398,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>96042</v>
@@ -8833,7 +11410,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>90273</v>
@@ -8845,7 +11422,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8856,7 +11433,7 @@
         <v>2445949.9499999997</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8874,27 +11451,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8903,7 +11480,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="261">
@@ -8912,7 +11489,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8921,7 +11498,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8932,7 +11509,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8941,7 +11518,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>88242</v>
@@ -8952,7 +11529,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8961,7 +11538,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8972,7 +11549,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>939396+207281</f>
@@ -8982,7 +11559,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>44838</v>
@@ -8993,7 +11570,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9002,7 +11579,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9013,7 +11590,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>117832</v>
@@ -9022,7 +11599,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9033,7 +11610,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>121857</v>
@@ -9045,7 +11622,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <v>3940</v>
@@ -9057,7 +11634,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9068,7 +11645,7 @@
         <v>230230.60000000003</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9081,30 +11658,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9117,13 +11694,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>18219</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>34534</v>
@@ -9132,13 +11709,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9151,13 +11728,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9167,14 +11744,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>18219</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9184,14 +11761,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>1496940</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9204,7 +11781,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>1515159</v>
@@ -9217,24 +11794,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9247,13 +11824,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9263,13 +11840,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>69606</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9279,13 +11856,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9295,13 +11872,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9314,14 +11891,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>69606</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9334,14 +11911,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>20153</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9354,13 +11931,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>89759</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9373,7 +11950,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9384,21 +11961,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9430,20 +12007,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9457,7 +12034,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9471,19 +12048,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9497,7 +12074,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9514,19 +12091,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9537,7 +12114,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9551,19 +12128,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9574,12 +12151,12 @@
         <v>4.586156299298292E-3</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9590,21 +12167,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9615,12 +12192,12 @@
         <v>2338843.0327008888</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9630,7 +12207,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9640,7 +12217,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9650,7 +12227,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9663,19 +12240,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9686,12 +12263,12 @@
         <v>-465728.48364955559</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9702,12 +12279,12 @@
         <v>7.0219024921412929</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9715,12 +12292,12 @@
         <v>931456.96729911119</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9728,7 +12305,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9736,19 +12313,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9762,7 +12339,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9776,7 +12353,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9790,7 +12367,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9804,7 +12381,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9815,15 +12392,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9840,7 +12417,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9857,7 +12434,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9874,7 +12451,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9896,7 +12473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9922,7 +12499,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9975,12 +12552,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9998,7 +12575,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10012,7 +12589,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>G4*0.95</f>
@@ -10069,7 +12646,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10124,7 +12701,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10179,7 +12756,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10234,7 +12811,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10291,7 +12868,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10346,7 +12923,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10401,7 +12978,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10458,7 +13035,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10513,7 +13090,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10568,7 +13145,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10623,7 +13200,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10680,7 +13257,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10737,7 +13314,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10745,7 +13322,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10763,14 +13340,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10788,7 +13365,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10864,12 +13441,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10887,7 +13464,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10908,7 +13485,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -10965,7 +13542,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11022,7 +13599,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11083,14 +13660,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -11098,7 +13675,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11158,7 +13735,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11209,7 +13786,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11268,21 +13845,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-1317994</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11332,7 +13909,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -11340,7 +13917,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11391,7 +13968,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11452,7 +14029,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11575,7 +14152,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11634,21 +14211,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11702,12 +14279,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11725,14 +14302,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11787,7 +14364,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11842,7 +14419,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11899,7 +14476,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -11958,23 +14535,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11994,14 +14571,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>6.3262169086251069E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12021,7 +14598,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12080,17 +14657,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12145,7 +14722,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12200,7 +14777,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12255,7 +14832,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12310,13 +14887,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12366,7 +14943,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12425,17 +15002,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12460,7 +15037,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12485,7 +15062,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12510,7 +15087,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12540,12 +15117,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12563,7 +15140,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12584,7 +15161,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12641,7 +15218,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12698,7 +15275,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12755,7 +15332,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12812,7 +15389,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12869,7 +15446,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12877,7 +15454,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12928,7 +15505,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12985,7 +15562,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13042,7 +15619,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13099,7 +15676,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13214,7 +15791,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13271,7 +15848,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13297,7 +15874,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13321,7 +15898,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13382,7 +15959,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13500,7 +16077,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13555,7 +16132,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0</v>
@@ -13576,7 +16153,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13635,7 +16212,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13656,7 +16233,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13713,7 +16290,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13773,12 +16350,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13796,17 +16373,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13863,7 +16440,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13920,7 +16497,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -13977,7 +16554,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14034,7 +16611,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14095,14 +16672,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14118,7 +16695,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14175,7 +16752,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14232,7 +16809,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14263,14 +16840,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14322,7 +16899,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14378,7 +16955,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14432,7 +17009,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14486,7 +17063,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14540,7 +17117,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14597,7 +17174,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14673,12 +17250,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14696,7 +17273,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14775,7 +17352,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14831,7 +17408,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15576,7 +18153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15593,32 +18170,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15629,7 +18206,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15639,7 +18216,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15650,7 +18227,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15660,15 +18237,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15678,13 +18255,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15694,13 +18271,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15710,13 +18287,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15730,7 +18307,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15744,7 +18321,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15761,7 +18338,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15771,13 +18348,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15787,7 +18364,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15797,7 +18374,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15814,19 +18391,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16592,7 +19169,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16615,7 +19192,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16629,7 +19206,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16850,7 +19427,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17079,19 +19656,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17216,20 +19793,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17336,7 +19913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17353,32 +19930,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17389,7 +19966,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17399,7 +19976,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17410,7 +19987,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17420,13 +19997,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17443,7 +20020,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17453,13 +20030,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17469,7 +20046,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17479,7 +20056,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17496,19 +20073,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18174,7 +20751,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18197,7 +20774,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18211,7 +20788,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18382,7 +20959,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18601,19 +21178,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18738,20 +21315,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18787,7 +21364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18802,20 +21379,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18827,14 +21404,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18856,14 +21433,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18876,7 +21453,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18886,11 +21463,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 百富环球(0327.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18901,7 +21478,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18911,8 +21488,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18923,7 +21500,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18933,8 +21510,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18944,8 +21521,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18956,10 +21533,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>443</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>423</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18970,15 +21547,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-5.6448033822130816E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18989,14 +21566,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.12852816016361679</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19007,18 +21584,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.13569365902210184</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19027,38 +21604,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19068,12 +21645,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19083,44 +21660,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19130,55 +21707,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19188,55 +21765,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19246,24 +21823,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19276,7 +21853,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19285,12 +21862,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19305,39 +21882,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19347,55 +21924,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19405,23 +21982,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19432,7 +22009,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19441,7 +22018,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19450,15 +22027,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19466,24 +22043,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>3.3144882254640899E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19494,20 +22071,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19517,19 +22094,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19539,14 +22116,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19555,7 +22132,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19564,12 +22141,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19579,7 +22156,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19592,12 +22169,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19606,7 +22183,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19618,7 +22195,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19628,7 +22205,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19639,7 +22216,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19651,12 +22228,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19669,7 +22246,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19681,12 +22258,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19695,7 +22272,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19707,7 +22284,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19717,7 +22294,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19728,7 +22305,7 @@
         <v>HKD</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19737,14 +22314,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19755,7 +22332,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19767,7 +22344,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19779,17 +22356,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>6.8641356814360206</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19801,12 +22378,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19815,7 +22392,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19825,7 +22402,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19835,17 +22412,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>6.1469536878205542</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19857,32 +22434,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19901,24 +22478,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D578CBAA-219F-41EA-A9BF-E2ADF6C97C9D}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E784C3C-F869-43BB-AE4C-7AB89FABDE7B}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A2DDC6-A3C2-4E0F-B702-46366AC68A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67022103-ABB4-4EA1-8AF5-245E93286E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4751,8 +4751,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4763,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4787,11 +4792,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5574,13 +5574,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5592,13 +5592,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5618,13 +5618,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5653,13 +5653,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5675,13 +5675,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5745,13 +5745,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5767,7 +5767,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5948,13 +5948,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6242,13 +6242,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,13 +6410,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6758,7 +6758,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6801,13 +6801,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7296,13 +7296,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7314,13 +7314,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7340,13 +7340,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7375,13 +7375,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7397,13 +7397,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7467,13 +7467,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7489,7 +7489,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7670,13 +7670,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7964,13 +7964,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,13 +8132,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8480,7 +8480,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8523,13 +8523,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -18237,10 +18237,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18255,8 +18255,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18271,8 +18271,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18287,8 +18287,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -19997,8 +19997,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21463,11 +21463,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 百富环球(0327.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21488,8 +21488,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21510,8 +21510,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21521,8 +21521,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21535,8 +21535,8 @@
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21554,8 +21554,8 @@
         <v>-5.6448033822130816E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21572,8 +21572,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.12852816016361679</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21590,8 +21590,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.13569365902210184</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21617,21 +21617,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21645,8 +21645,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21660,8 +21660,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21681,8 +21681,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21692,8 +21692,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21707,8 +21707,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21718,8 +21718,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21739,8 +21739,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21750,8 +21750,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21765,8 +21765,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21776,8 +21776,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21797,8 +21797,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21808,8 +21808,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21823,8 +21823,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21835,8 +21835,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21898,8 +21898,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21909,8 +21909,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21924,8 +21924,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21935,8 +21935,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21956,8 +21956,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -21967,8 +21967,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -21982,8 +21982,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -21993,8 +21993,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22483,19 +22483,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67022103-ABB4-4EA1-8AF5-245E93286E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406A883F-54E1-4984-83BC-D4E43643CB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.09</v>
+        <v>6.21</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6466.0209599999998</v>
+        <v>6593.4302399999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12105828462833323</v>
+        <v>0.11340452568604564</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0657164916992627E-2</v>
+        <v>5.9485045788161849E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.9113300492610835E-2</v>
+        <v>5.7971014492753624E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.09</v>
+        <v>6.21</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6466.0209599999998</v>
+        <v>6593.4302399999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12105828462833323</v>
+        <v>0.11340452568604564</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0657164916992627E-2</v>
+        <v>5.9485045788161849E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.9113300492610835E-2</v>
+        <v>5.7971014492753624E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.9113300492610835E-2</v>
+        <v>5.7971014492753624E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.0459770114942528E-2</v>
+        <v>7.8904991948470213E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.224958949096881E-2</v>
+        <v>7.0853462157809979E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9113300492610835E-2</v>
+        <v>5.7971014492753624E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0657164916992627E-2</v>
+        <v>5.9485045788161849E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.6831688891405934E-2</v>
+        <v>9.4960545144712097E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16382925655494579</v>
+        <v>0.16066347381958451</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18666623896914311</v>
+        <v>0.18305916188761379</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14997345929391645</v>
+        <v>0.14707542143316443</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13884396687758341</v>
+        <v>0.13616099167221948</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.3274055826753771E-2</v>
+        <v>9.1471658612710213E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.4071829176378057E-2</v>
+        <v>7.2640489482148532E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.8323935652692347E-2</v>
+        <v>6.7003666364717607E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.353035094399075E-2</v>
+        <v>8.191623788227112E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.9036397061106961E-2</v>
+        <v>7.7509123687945478E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11149391634511498</v>
+        <v>0.1093394445316828</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18018855911657916</v>
+        <v>0.1767066545925873</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19613345020768383</v>
+        <v>0.19234343184618269</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16892026901193341</v>
+        <v>0.16565610922426321</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13978457626280258</v>
+        <v>0.13708342503067114</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.663810307227956E-2</v>
+        <v>9.4770700114361103E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9708680684511729E-2</v>
+        <v>7.8168416323458362E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2051486081171008E-2</v>
+        <v>5.1045660263177368E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3323854613672638E-2</v>
+        <v>9.1520495104229688E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5930094232172108E-2</v>
+        <v>9.4076372604497291E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.09</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.09</v>
+        <v>6.21</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.09</v>
+        <v>6.21</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12105828462833323</v>
+        <v>0.11340452568604564</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406A883F-54E1-4984-83BC-D4E43643CB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFED3B0-8210-4FD4-ACE6-A6D533A1CF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.21</v>
+        <v>6.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6593.4302399999997</v>
+        <v>6487.2558399999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11340452568604564</v>
+        <v>0.11976827260606249</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.9485045788161849E-2</v>
+        <v>6.0458614458999194E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.7971014492753624E-2</v>
+        <v>5.8919803600654658E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.21</v>
+        <v>6.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6593.4302399999997</v>
+        <v>6487.2558399999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11340452568604564</v>
+        <v>0.11976827260606249</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.9485045788161849E-2</v>
+        <v>6.0458614458999194E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.7971014492753624E-2</v>
+        <v>5.8919803600654658E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7971014492753624E-2</v>
+        <v>5.8919803600654658E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.8904991948470213E-2</v>
+        <v>8.0196399345335512E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.0853462157809979E-2</v>
+        <v>7.2013093289689037E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.7971014492753624E-2</v>
+        <v>5.8919803600654658E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.9485045788161849E-2</v>
+        <v>6.0458614458999194E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.4960545144712097E-2</v>
+        <v>9.6514727552972523E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16066347381958451</v>
+        <v>0.16329299057604252</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18305916188761379</v>
+        <v>0.18605522018364673</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14707542143316443</v>
+        <v>0.14948254780686598</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13616099167221948</v>
+        <v>0.13838948580760768</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.1471658612710213E-2</v>
+        <v>9.2968739768401046E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.2640489482148532E-2</v>
+        <v>7.3829368197077305E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.7003666364717607E-2</v>
+        <v>6.8100289382143422E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.191623788227112E-2</v>
+        <v>8.3256929173306654E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.7509123687945478E-2</v>
+        <v>7.8777685450432303E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1093394445316828</v>
+        <v>0.11112896080879708</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1767066545925873</v>
+        <v>0.17959874386578839</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19234343184618269</v>
+        <v>0.19549144218736408</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16565610922426321</v>
+        <v>0.16836733850780269</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13708342503067114</v>
+        <v>0.13932701627503563</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4770700114361103E-2</v>
+        <v>9.6321775402648524E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8168416323458362E-2</v>
+        <v>7.9447768472778471E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1045660263177368E-2</v>
+        <v>5.1881104784669632E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1520495104229688E-2</v>
+        <v>9.3018375547834112E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4076372604497291E-2</v>
+        <v>9.5616084103752566E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.21</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.21</v>
+        <v>6.11</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.21</v>
+        <v>6.11</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11340452568604564</v>
+        <v>0.11976827260606249</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFED3B0-8210-4FD4-ACE6-A6D533A1CF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F14A96-EAB6-4B4D-9F5F-AA2FE91C789E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.11</v>
+        <v>6.56</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6487.2558399999998</v>
+        <v>6965.0406400000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11976827260606249</v>
+        <v>9.219872358301795E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0458614458999194E-2</v>
+        <v>5.6311300967147114E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.8919803600654658E-2</v>
+        <v>5.4878048780487805E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.11</v>
+        <v>6.56</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6487.2558399999998</v>
+        <v>6965.0406400000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11976827260606249</v>
+        <v>9.219872358301795E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>6.0458614458999194E-2</v>
+        <v>5.6311300967147114E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.8919803600654658E-2</v>
+        <v>5.4878048780487805E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8919803600654658E-2</v>
+        <v>5.4878048780487805E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.0196399345335512E-2</v>
+        <v>7.4695121951219509E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.2013093289689037E-2</v>
+        <v>6.7073170731707321E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.8919803600654658E-2</v>
+        <v>5.4878048780487805E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0458614458999194E-2</v>
+        <v>5.6311300967147114E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.6514727552972523E-2</v>
+        <v>8.9894052644613129E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16329299057604252</v>
+        <v>0.15209148969811279</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18605522018364673</v>
+        <v>0.17329228587226855</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14948254780686598</v>
+        <v>0.13922840961889502</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13838948580760768</v>
+        <v>0.12889630461653703</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.2968739768401046E-2</v>
+        <v>8.6591310973312574E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.3829368197077305E-2</v>
+        <v>6.8764853610387561E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.8100289382143422E-2</v>
+        <v>6.3428775628795189E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.3256929173306654E-2</v>
+        <v>7.7545706897698741E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.8777685450432303E-2</v>
+        <v>7.3373728369228883E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11112896080879708</v>
+        <v>0.10350578514355947</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17959874386578839</v>
+        <v>0.16727870808231207</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19549144218736408</v>
+        <v>0.1820812060617065</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16836733850780269</v>
+        <v>0.15681774973821258</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13932701627503563</v>
+        <v>0.12976952278055912</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6321775402648524E-2</v>
+        <v>8.9714336541186351E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9447768472778471E-2</v>
+        <v>7.3997845330590922E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1881104784669632E-2</v>
+        <v>4.8322187535721255E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3018375547834112E-2</v>
+        <v>8.663754185933939E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5616084103752566E-2</v>
+        <v>8.9057053944196371E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.11</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.11</v>
+        <v>6.56</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.11</v>
+        <v>6.56</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11976827260606249</v>
+        <v>9.219872358301795E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F14A96-EAB6-4B4D-9F5F-AA2FE91C789E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E14789-B134-440E-8695-5427BE5A1E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.56</v>
+        <v>6.51</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6965.0406400000002</v>
+        <v>6911.9534400000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.219872358301795E-2</v>
+        <v>9.513149400081744E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6311300967147114E-2</v>
+        <v>5.6743799438476968E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.4878048780487805E-2</v>
+        <v>5.5299539170506909E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.56</v>
+        <v>6.51</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6965.0406400000002</v>
+        <v>6911.9534400000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.219872358301795E-2</v>
+        <v>9.513149400081744E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6311300967147114E-2</v>
+        <v>5.6743799438476968E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.4878048780487805E-2</v>
+        <v>5.5299539170506909E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4878048780487805E-2</v>
+        <v>5.5299539170506909E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.4695121951219509E-2</v>
+        <v>7.5268817204301078E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.7073170731707321E-2</v>
+        <v>6.7588325652841785E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.4878048780487805E-2</v>
+        <v>5.5299539170506909E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6311300967147114E-2</v>
+        <v>5.6743799438476968E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.9894052644613129E-2</v>
+        <v>9.058448315647652E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15209148969811279</v>
+        <v>0.15325962709978799</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17329228587226855</v>
+        <v>0.17462325580984356</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.13922840961889502</v>
+        <v>0.14029775224269603</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12889630461653703</v>
+        <v>0.12988629159515866</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.6591310973312574E-2</v>
+        <v>8.7256374805672887E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.8764853610387561E-2</v>
+        <v>6.929300148757947E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.3428775628795189E-2</v>
+        <v>6.3915939804131544E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.7545706897698741E-2</v>
+        <v>7.8141296044378444E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.3373728369228883E-2</v>
+        <v>7.3937274670067804E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10350578514355947</v>
+        <v>0.10430076045188175</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16727870808231207</v>
+        <v>0.16856349078647728</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1820812060617065</v>
+        <v>0.18347967922654293</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15681774973821258</v>
+        <v>0.15802218714019578</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12976952278055912</v>
+        <v>0.1307662165039121</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9714336541186351E-2</v>
+        <v>9.0403386745035716E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3997845330590922E-2</v>
+        <v>7.4566185156478712E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8322187535721255E-2</v>
+        <v>4.8693325688837392E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.663754185933939E-2</v>
+        <v>8.7302960767629251E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9057053944196371E-2</v>
+        <v>8.974105589461262E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.56</v>
+        <v>-6.51</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.56</v>
+        <v>6.51</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.56</v>
+        <v>6.51</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.219872358301795E-2</v>
+        <v>9.513149400081744E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E14789-B134-440E-8695-5427BE5A1E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5D1B2D-6095-4D46-8B59-6E61E04F022E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.33</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6911.9534400000002</v>
+        <v>6720.8395200000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.513149400081744E-2</v>
+        <v>0.10595213359196998</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6743799438476968E-2</v>
+        <v>5.835736719502134E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5299539170506909E-2</v>
+        <v>5.6872037914691941E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.51</v>
+        <v>6.33</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6911.9534400000002</v>
+        <v>6720.8395200000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.513149400081744E-2</v>
+        <v>0.10595213359196998</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6743799438476968E-2</v>
+        <v>5.835736719502134E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5299539170506909E-2</v>
+        <v>5.6872037914691941E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5299539170506909E-2</v>
+        <v>5.6872037914691941E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.5268817204301078E-2</v>
+        <v>7.7409162717219593E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.7588325652841785E-2</v>
+        <v>6.9510268562401265E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.5299539170506909E-2</v>
+        <v>5.6872037914691941E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6743799438476968E-2</v>
+        <v>5.835736719502134E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.058448315647652E-2</v>
+        <v>9.3160345236755468E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15325962709978799</v>
+        <v>0.15761772076139335</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17462325580984356</v>
+        <v>0.17958884602244574</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14029775224269603</v>
+        <v>0.14428726178514237</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12988629159515866</v>
+        <v>0.13357974064525796</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.7256374805672887E-2</v>
+        <v>8.9737598733796275E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.929300148757947E-2</v>
+        <v>7.1263418591491684E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.3915939804131544E-2</v>
+        <v>6.5733454680078421E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.8141296044378444E-2</v>
+        <v>8.0363323420047969E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.3937274670067804E-2</v>
+        <v>7.603975641424035E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10430076045188175</v>
+        <v>0.10726665885335705</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16856349078647728</v>
+        <v>0.17335676540599798</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18347967922654293</v>
+        <v>0.18869711086331667</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15802218714019578</v>
+        <v>0.16251570904939566</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1307662165039121</v>
+        <v>0.13448468711539774</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0403386745035716E-2</v>
+        <v>9.2974099164325821E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4566185156478712E-2</v>
+        <v>7.6686550611165319E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8693325688837392E-2</v>
+        <v>5.0077970021221399E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7302960767629251E-2</v>
+        <v>8.978550941504998E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.974105589461262E-2</v>
+        <v>9.2292934261284071E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.51</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.33</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.51</v>
+        <v>6.33</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.513149400081744E-2</v>
+        <v>0.10595213359196998</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5D1B2D-6095-4D46-8B59-6E61E04F022E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53956B12-922C-41ED-AB05-2AE83B69205B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6720.8395200000004</v>
+        <v>6688.9871999999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10595213359196998</v>
+        <v>0.10779685778901893</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.835736719502134E-2</v>
+        <v>5.8635259419759535E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.6872037914691941E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6720.8395200000004</v>
+        <v>6688.9871999999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10595213359196998</v>
+        <v>0.10779685778901893</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.835736719502134E-2</v>
+        <v>5.8635259419759535E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.6872037914691941E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6872037914691941E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.7409162717219593E-2</v>
+        <v>7.7777777777777779E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9510268562401265E-2</v>
+        <v>6.9841269841269843E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6872037914691941E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.835736719502134E-2</v>
+        <v>5.8635259419759535E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.3160345236755468E-2</v>
+        <v>9.3603965928359067E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15761772076139335</v>
+        <v>0.15836828133644759</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17958884602244574</v>
+        <v>0.18044403100350501</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14428726178514237</v>
+        <v>0.14497434398411924</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13357974064525796</v>
+        <v>0.13421583464833062</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.9737598733796275E-2</v>
+        <v>9.016492063252865E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.1263418591491684E-2</v>
+        <v>7.1602768203832115E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.5733454680078421E-2</v>
+        <v>6.6046471130935938E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.0363323420047969E-2</v>
+        <v>8.0746005912524399E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.603975641424035E-2</v>
+        <v>7.6401850492403403E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10726665885335705</v>
+        <v>0.10777745246694448</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17335676540599798</v>
+        <v>0.17418227381269319</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18869711086331667</v>
+        <v>0.18959566853409437</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16251570904939566</v>
+        <v>0.16328959337820231</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13448468711539774</v>
+        <v>0.13512509038737583</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2974099164325821E-2</v>
+        <v>9.3416832969870231E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6686550611165319E-2</v>
+        <v>7.7051724661694673E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0077970021221399E-2</v>
+        <v>5.0316436545131973E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.978550941504998E-2</v>
+        <v>9.021305945988356E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2292934261284071E-2</v>
+        <v>9.2732424424433038E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.33</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10595213359196998</v>
+        <v>0.10779685778901893</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53956B12-922C-41ED-AB05-2AE83B69205B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FD1AF3-FF63-4463-88BC-388DBBF0EDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.3</v>
+        <v>6.36</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6688.9871999999996</v>
+        <v>6752.6918400000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10779685778901893</v>
+        <v>0.1041194271854049</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.8635259419759535E-2</v>
+        <v>5.8082096595044826E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.7142857142857141E-2</v>
+        <v>5.6603773584905655E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.3</v>
+        <v>6.36</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6688.9871999999996</v>
+        <v>6752.6918400000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10779685778901893</v>
+        <v>0.1041194271854049</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.8635259419759535E-2</v>
+        <v>5.8082096595044826E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.7142857142857141E-2</v>
+        <v>5.6603773584905655E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7142857142857141E-2</v>
+        <v>5.6603773584905655E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.7777777777777779E-2</v>
+        <v>7.7044025157232701E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9841269841269843E-2</v>
+        <v>6.9182389937106917E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.7142857142857141E-2</v>
+        <v>5.6603773584905655E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.8635259419759535E-2</v>
+        <v>5.8082096595044826E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.3603965928359067E-2</v>
+        <v>9.272090964601605E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15836828133644759</v>
+        <v>0.15687424094648111</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18044403100350501</v>
+        <v>0.17874172882422665</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14497434398411924</v>
+        <v>0.14360666149370302</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13421583464833062</v>
+        <v>0.13294964752900673</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.016492063252865E-2</v>
+        <v>8.9314308173731205E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.1602768203832115E-2</v>
+        <v>7.0927270390588409E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.6046471130935938E-2</v>
+        <v>6.5423391214606344E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.0746005912524399E-2</v>
+        <v>7.998425113976472E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6401850492403403E-2</v>
+        <v>7.5681078317946751E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10777745246694448</v>
+        <v>0.106760684047445</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17418227381269319</v>
+        <v>0.17253904481446025</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18959566853409437</v>
+        <v>0.18780703015169725</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16328959337820231</v>
+        <v>0.16174912551614379</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13512509038737583</v>
+        <v>0.13385032538372135</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3416832969870231E-2</v>
+        <v>9.2535542092795992E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7051724661694673E-2</v>
+        <v>7.63248215988485E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0316436545131973E-2</v>
+        <v>4.9841753181498652E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.021305945988356E-2</v>
+        <v>8.93619928612054E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2732424424433038E-2</v>
+        <v>9.1857590231749719E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.3</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.3</v>
+        <v>6.36</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.3</v>
+        <v>6.36</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10779685778901893</v>
+        <v>0.1041194271854049</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FD1AF3-FF63-4463-88BC-388DBBF0EDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAC5F62-18E9-45BE-98B2-672CD35DDA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.36</v>
+        <v>6.44</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6752.6918400000004</v>
+        <v>6837.6313600000003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1041194271854049</v>
+        <v>9.9289940045246272E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.8082096595044826E-2</v>
+        <v>5.7360579867156071E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.6603773584905655E-2</v>
+        <v>5.5900621118012417E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.36</v>
+        <v>6.44</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6752.6918400000004</v>
+        <v>6837.6313600000003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1041194271854049</v>
+        <v>9.9289940045246272E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.8082096595044826E-2</v>
+        <v>5.7360579867156071E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.6603773584905655E-2</v>
+        <v>5.5900621118012417E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6603773584905655E-2</v>
+        <v>5.5900621118012417E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.7044025157232701E-2</v>
+        <v>7.6086956521739121E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9182389937106917E-2</v>
+        <v>6.8322981366459618E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6603773584905655E-2</v>
+        <v>5.5900621118012417E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.8082096595044826E-2</v>
+        <v>5.7360579867156071E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.272090964601605E-2</v>
+        <v>9.1569097103829517E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15687424094648111</v>
+        <v>0.15492549261174221</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17874172882422665</v>
+        <v>0.17652133467734185</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14360666149370302</v>
+        <v>0.14182272781055141</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13294964752900673</v>
+        <v>0.13129809911249735</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.9314308173731205E-2</v>
+        <v>8.8204813662256271E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.0927270390588409E-2</v>
+        <v>7.0046186286357504E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.5423391214606344E-2</v>
+        <v>6.4610678280263414E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.998425113976472E-2</v>
+        <v>7.8990657957904289E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.5681078317946751E-2</v>
+        <v>7.4740940699090277E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.106760684047445</v>
+        <v>0.10543446436983699</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17253904481446025</v>
+        <v>0.17039570264285203</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18780703015169725</v>
+        <v>0.18547402356596188</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16174912551614379</v>
+        <v>0.15973981960911096</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13385032538372135</v>
+        <v>0.13218758842243289</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2535542092795992E-2</v>
+        <v>9.1386032253133923E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.63248215988485E-2</v>
+        <v>7.5376687169049134E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9841753181498652E-2</v>
+        <v>4.9222600968063891E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.93619928612054E-2</v>
+        <v>8.8251905993364341E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1857590231749719E-2</v>
+        <v>9.0716502154336673E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.36</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.36</v>
+        <v>6.44</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.36</v>
+        <v>6.44</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1041194271854049</v>
+        <v>9.9289940045246272E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAC5F62-18E9-45BE-98B2-672CD35DDA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD4DA0-DCD9-4D23-BE9C-F1FD085090F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD4DA0-DCD9-4D23-BE9C-F1FD085090F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA1B19A-B951-48A1-8D24-594342EEAEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6837.6313600000003</v>
+        <v>6933.1883200000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.9289940045246272E-2</v>
+        <v>9.3954672396520111E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.7360579867156071E-2</v>
+        <v>5.6570005259492358E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5900621118012417E-2</v>
+        <v>5.5130168453292494E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6837.6313600000003</v>
+        <v>6933.1883200000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.9289940045246272E-2</v>
+        <v>9.3954672396520111E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.7360579867156071E-2</v>
+        <v>5.6570005259492358E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5900621118012417E-2</v>
+        <v>5.5130168453292494E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5900621118012417E-2</v>
+        <v>5.5130168453292494E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.6086956521739121E-2</v>
+        <v>7.5038284839203676E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8322981366459618E-2</v>
+        <v>6.738131699846861E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.5900621118012417E-2</v>
+        <v>5.5130168453292494E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7360579867156071E-2</v>
+        <v>5.6570005259492358E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.1569097103829517E-2</v>
+        <v>9.0307042166717019E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15492549261174221</v>
+        <v>0.15279022548539353</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17652133467734185</v>
+        <v>0.17408842194825139</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14182272781055141</v>
+        <v>0.13986805009187614</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13129809911249735</v>
+        <v>0.12948847753208007</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.8204813662256271E-2</v>
+        <v>8.6989127103358418E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>7.0046186286357504E-2</v>
+        <v>6.9080771773988109E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.4610678280263414E-2</v>
+        <v>6.3720178885895304E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.8990657957904289E-2</v>
+        <v>7.7901965888040381E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.4740940699090277E-2</v>
+        <v>7.3710820536315683E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10543446436983699</v>
+        <v>0.10398130942446404</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17039570264285203</v>
+        <v>0.16804721669524764</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18547402356596188</v>
+        <v>0.18291772002523654</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15973981960911096</v>
+        <v>0.15753819881817374</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13218758842243289</v>
+        <v>0.13036570741814207</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1386032253133923E-2</v>
+        <v>9.0126500415035601E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5376687169049134E-2</v>
+        <v>7.433780480377894E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9222600968063891E-2</v>
+        <v>4.8544188397294248E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8251905993364341E-2</v>
+        <v>8.7035570382429761E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0716502154336673E-2</v>
+        <v>8.9466198143021161E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.44</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.44</v>
+        <v>6.53</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.9289940045246272E-2</v>
+        <v>9.3954672396520111E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA1B19A-B951-48A1-8D24-594342EEAEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7946B2E7-7CE0-4D7E-9258-035C49072462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.53</v>
+        <v>6.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6933.1883200000002</v>
+        <v>6975.6580800000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.3954672396520111E-2</v>
+        <v>9.1615864855765006E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6570005259492358E-2</v>
+        <v>5.6225591224426955E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5130168453292494E-2</v>
+        <v>5.4794520547945202E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.53</v>
+        <v>6.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6933.1883200000002</v>
+        <v>6975.6580800000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.3954672396520111E-2</v>
+        <v>9.1615864855765006E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6570005259492358E-2</v>
+        <v>5.6225591224426955E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5130168453292494E-2</v>
+        <v>5.4794520547945202E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5130168453292494E-2</v>
+        <v>5.4794520547945202E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.5038284839203676E-2</v>
+        <v>7.4581430745814303E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.738131699846861E-2</v>
+        <v>6.6971080669710803E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.5130168453292494E-2</v>
+        <v>5.4794520547945202E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6570005259492358E-2</v>
+        <v>5.6225591224426955E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.0307042166717019E-2</v>
+        <v>8.9757227602536085E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15279022548539353</v>
+        <v>0.15185999580207304</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17408842194825139</v>
+        <v>0.17302852288007328</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.13986805009187614</v>
+        <v>0.13901649423134721</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12948847753208007</v>
+        <v>0.12870011541620743</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.6989127103358418E-2</v>
+        <v>8.6459512935301436E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.9080771773988109E-2</v>
+        <v>6.8660188688606141E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.3720178885895304E-2</v>
+        <v>6.3332232591308421E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.7901965888040381E-2</v>
+        <v>7.7427676902420639E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.3710820536315683E-2</v>
+        <v>7.3262048417373118E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10398130942446404</v>
+        <v>0.10334824209159059</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16804721669524764</v>
+        <v>0.16702409817655511</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18291772002523654</v>
+        <v>0.18180406571762472</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15753819881817374</v>
+        <v>0.15657906214348166</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13036570741814207</v>
+        <v>0.12957200448104533</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0126500415035601E-2</v>
+        <v>8.9577785039601593E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.433780480377894E-2</v>
+        <v>7.3885215429022294E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8544188397294248E-2</v>
+        <v>4.8248637783003263E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7035570382429761E-2</v>
+        <v>8.6505673454682866E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9466198143021161E-2</v>
+        <v>8.8921502872744015E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.53</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.53</v>
+        <v>6.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.53</v>
+        <v>6.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.3954672396520111E-2</v>
+        <v>9.1615864855765006E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7946B2E7-7CE0-4D7E-9258-035C49072462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C532B0-D2F8-4CDA-8C4A-7E9A56401948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C532B0-D2F8-4CDA-8C4A-7E9A56401948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA404D7C-AD39-4FBC-B136-BE80CAD5DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6975.6580800000002</v>
+        <v>6901.3360000000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.1615864855765006E-2</v>
+        <v>9.572177520852998E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6225591224426955E-2</v>
+        <v>5.683109759145924E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.4794520547945202E-2</v>
+        <v>5.5384615384615379E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6975.6580800000002</v>
+        <v>6901.3360000000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.1615864855765006E-2</v>
+        <v>9.572177520852998E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.6225591224426955E-2</v>
+        <v>5.683109759145924E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.4794520547945202E-2</v>
+        <v>5.5384615384615379E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16157,20 +16157,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4794520547945202E-2</v>
+        <v>5.5384615384615379E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.4581430745814303E-2</v>
+        <v>7.5384615384615383E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6971080669710803E-2</v>
+        <v>6.7692307692307691E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.4794520547945202E-2</v>
+        <v>5.5384615384615379E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17356,50 +17356,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6225591224426955E-2</v>
+        <v>5.683109759145924E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.9757227602536085E-2</v>
+        <v>9.0723843899794168E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15185999580207304</v>
+        <v>0.15349541114147996</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17302852288007328</v>
+        <v>0.17489190697262794</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.13901649423134721</v>
+        <v>0.14051359493845403</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12870011541620743</v>
+        <v>0.13008611665915121</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.6459512935301436E-2</v>
+        <v>8.7390615382296991E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.8660188688606141E-2</v>
+        <v>6.939960610525267E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.3332232591308421E-2</v>
+        <v>6.4014272019214821E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.7427676902420639E-2</v>
+        <v>7.8261513422908255E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.3262048417373118E-2</v>
+        <v>7.4051024323406364E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17413,43 +17413,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10334824209159059</v>
+        <v>0.10446122316026926</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16702409817655511</v>
+        <v>0.1688228192338411</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18180406571762472</v>
+        <v>0.18376195565612224</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15657906214348166</v>
+        <v>0.15826529819733454</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12957200448104533</v>
+        <v>0.13096739529853349</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9577785039601593E-2</v>
+        <v>9.0542468878489615E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3885215429022294E-2</v>
+        <v>7.4680902364411758E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8248637783003263E-2</v>
+        <v>4.8768238497589454E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6505673454682866E-2</v>
+        <v>8.7437273014964054E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8921502872744015E-2</v>
+        <v>8.9879119057527407E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.57</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.1615864855765006E-2</v>
+        <v>9.572177520852998E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA404D7C-AD39-4FBC-B136-BE80CAD5DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998A3D68-69E2-492B-AD97-F1AF1F21D1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,27 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998A3D68-69E2-492B-AD97-F1AF1F21D1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB37CAB-758D-4933-AEF2-67E77E880314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
-    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
-    <sheet name="Data" sheetId="4" r:id="rId3"/>
-    <sheet name="BS" sheetId="3" r:id="rId4"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
-    <sheet name="DCF" sheetId="8" r:id="rId6"/>
-    <sheet name="DDM" sheetId="10" r:id="rId7"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
+    <sheet name="Data" sheetId="4" r:id="rId2"/>
+    <sheet name="BS" sheetId="3" r:id="rId3"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId8"/>
     <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
@@ -4751,31 +4751,26 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4792,10 +4787,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{0500429E-0EED-4D3B-B90D-D3AAA0ED5EAD}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{C0164295-F4D5-499D-8E1E-F301B48E18DB}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4889,6 +4889,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="投资主题"/>
       <sheetName val="Thesis"/>
       <sheetName val="Data"/>
       <sheetName val="BS"/>
@@ -4899,7 +4900,8 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
         <row r="6">
           <cell r="C6">
             <v>1061744000</v>
@@ -4907,7 +4909,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>6.09</v>
+            <v>6.5</v>
           </cell>
         </row>
         <row r="13">
@@ -4941,25 +4943,25 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1">
+      <sheetData sheetId="2">
         <row r="3">
           <cell r="C3">
             <v>1000</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
         <row r="93">
           <cell r="C93">
             <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5162,1749 +5164,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
-  <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="B1" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C1" s="33">
-        <f>Thesis!C1</f>
-        <v>45805</v>
-      </c>
-      <c r="D1" s="358" t="str">
-        <f>Thesis!D1</f>
-        <v>INT</v>
-      </c>
-      <c r="E1" s="292" t="s">
-        <v>344</v>
-      </c>
-      <c r="F1" s="307" t="str">
-        <f>Thesis!F1</f>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="222" t="s">
-        <v>438</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="45" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.4">
-      <c r="B5" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="C5" s="359" t="str">
-        <f>Thesis!C5</f>
-        <v>百富环球</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C6" s="34">
-        <f>Common_Shares</f>
-        <v>1061744000</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C7" s="360">
-        <f>Thesis!C7</f>
-        <v>6</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="C8" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="E9" s="34"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="45" t="s">
-        <v>440</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C11" s="365" t="str">
-        <f>Thesis!C11</f>
-        <v>0327.HK</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="C12" s="366">
-        <f>Market_Price</f>
-        <v>6.5</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="48"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C13" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="C14" s="35">
-        <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6901.3360000000002</v>
-      </c>
-      <c r="D14" s="35" t="str">
-        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
-        <v/>
-      </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C15" s="32" t="str">
-        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
-        <v>HKD</v>
-      </c>
-      <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
-        <v/>
-      </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="C16" s="366">
-        <f>Exchange_Rate</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
-        <v>489</v>
-      </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="45" t="s">
-        <v>490</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C21" s="32" t="str">
-        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Low Growth </v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E21" s="363" t="str">
-        <f>valuation_method</f>
-        <v>DCF</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C22" s="32" t="str">
-        <f>Thesis!C22</f>
-        <v>IND_02</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","终值贴现率","")</f>
-        <v/>
-      </c>
-      <c r="E22" s="364">
-        <f>Thesis!E22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C23" s="253" t="str">
-        <f>Thesis!C23</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C24" s="253" t="str">
-        <f>Thesis!C24</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C25" s="32" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D25" s="32" t="str">
-        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
-        <v/>
-      </c>
-      <c r="E25" s="299" t="str">
-        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="1" t="str">
-        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
-        <v>预期股权价值 (HKD) :</v>
-      </c>
-      <c r="C26" s="304">
-        <f>C132</f>
-        <v>7.3642693066239637</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E26" s="301">
-        <f ca="1">Scenarios!C87</f>
-        <v>9.572177520852998E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="45" t="s">
-        <v>448</v>
-      </c>
-      <c r="C28" s="309" t="str">
-        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
-        <v>0327.HK (HKD)</v>
-      </c>
-      <c r="D28" s="309" t="str">
-        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
-        <v/>
-      </c>
-      <c r="E28" s="305" t="s">
-        <v>453</v>
-      </c>
-      <c r="F28" s="361">
-        <f>Thesis!F28</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C29" s="310">
-        <f>C149</f>
-        <v>3.6036658259915511</v>
-      </c>
-      <c r="D29" s="310" t="str">
-        <f>D149</f>
-        <v/>
-      </c>
-      <c r="E29" s="306" t="s">
-        <v>455</v>
-      </c>
-      <c r="F29" s="362">
-        <f>Thesis!F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C30" s="311">
-        <f>C157</f>
-        <v>4.4732258849914697</v>
-      </c>
-      <c r="D30" s="311" t="str">
-        <f>D157</f>
-        <v/>
-      </c>
-      <c r="E30" s="307" t="s">
-        <v>454</v>
-      </c>
-      <c r="F30" s="224">
-        <f>Thesis!F30</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C31" s="311">
-        <f>C165</f>
-        <v>6.8641356814360206</v>
-      </c>
-      <c r="D31" s="311" t="str">
-        <f>D165</f>
-        <v/>
-      </c>
-      <c r="E31" s="307" t="s">
-        <v>491</v>
-      </c>
-      <c r="F31" s="224">
-        <f>Thesis!F31</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" s="311">
-        <f>C173</f>
-        <v>6.1469536878205542</v>
-      </c>
-      <c r="D32" s="311" t="str">
-        <f>D173</f>
-        <v/>
-      </c>
-      <c r="E32" s="307" t="s">
-        <v>456</v>
-      </c>
-      <c r="F32" s="224">
-        <f>Thesis!F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="222" t="s">
-        <v>457</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-    </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
-        <v>492</v>
-      </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
-        <v>330</v>
-      </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39" s="210" t="s">
-        <v>493</v>
-      </c>
-      <c r="C39" s="108">
-        <f>scaling_factor</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" s="370" t="s">
-        <v>494</v>
-      </c>
-      <c r="C40" s="370"/>
-      <c r="D40" s="370"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="B41" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C41" s="349">
-        <f>Normalized_FCF!C8</f>
-        <v>536120.13620533235</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="B42" s="47"/>
-      <c r="C42" s="76"/>
-    </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="370" t="s">
-        <v>495</v>
-      </c>
-      <c r="C43" s="370"/>
-      <c r="D43" s="370"/>
-      <c r="E43" s="370"/>
-      <c r="F43" s="370"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="B44" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="C44" s="349">
-        <f>Normalized_FCF!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="B45" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="C45" s="349">
-        <f>Normalized_FCF!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="370" t="s">
-        <v>496</v>
-      </c>
-      <c r="C47" s="370"/>
-      <c r="D47" s="370"/>
-      <c r="E47" s="370"/>
-      <c r="F47" s="370"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="B48" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="C48" s="349">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="370" t="s">
-        <v>497</v>
-      </c>
-      <c r="C50" s="370"/>
-      <c r="D50" s="370"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="47" t="s">
-        <v>331</v>
-      </c>
-      <c r="C51" s="350">
-        <f>Normalized_FCF!C48</f>
-        <v>3725.8278691964447</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E51" s="286"/>
-      <c r="F51" s="286"/>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="47" t="s">
-        <v>332</v>
-      </c>
-      <c r="C52" s="350">
-        <f>Normalized_FCF!C47</f>
-        <v>-5556</v>
-      </c>
-      <c r="D52" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E52" s="286"/>
-      <c r="F52" s="286"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C53" s="349">
-        <f>Normalized_FCF!C12</f>
-        <v>-1830.1721308035553</v>
-      </c>
-      <c r="D53" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="349">
-        <f>Normalized_FCF!C15</f>
-        <v>-8506.973328445607</v>
-      </c>
-      <c r="D56" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="370" t="s">
-        <v>237</v>
-      </c>
-      <c r="C58" s="370"/>
-      <c r="D58" s="370"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="C59" s="349">
-        <f>Normalized_FCF!C14</f>
-        <v>-133572.49101863219</v>
-      </c>
-      <c r="D59" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="370" t="s">
-        <v>499</v>
-      </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C62" s="349">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
-        <v>500</v>
-      </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
-        <v>501</v>
-      </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="47" t="s">
-        <v>502</v>
-      </c>
-      <c r="C67" s="349">
-        <f>Normalized_FCF!G19</f>
-        <v>626115.72996402986</v>
-      </c>
-      <c r="D67" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="C68" s="349">
-        <f>Normalized_FCF!C19</f>
-        <v>392210.49972745095</v>
-      </c>
-      <c r="D68" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="227" t="s">
-        <v>371</v>
-      </c>
-      <c r="C69" s="92">
-        <f>Normalized_FCF!C126</f>
-        <v>5.683109759145924E-2</v>
-      </c>
-      <c r="F69" s="314"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="227" t="s">
-        <v>434</v>
-      </c>
-      <c r="C70" s="92">
-        <f>Normalized_FCF!C94</f>
-        <v>5.5384615384615379E-2</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>503</v>
-      </c>
-      <c r="F70" s="315">
-        <f>Normalized_FCF!C92</f>
-        <v>0.9745476989157914</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="210" t="s">
-        <v>513</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>429</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="C73" s="92">
-        <f>Normalized_FCF!C121</f>
-        <v>7.0630420943605887E-2</v>
-      </c>
-      <c r="D73" s="92">
-        <f>Normalized_FCF!G121</f>
-        <v>0.102310110249777</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
-        <v>Pre-tax Profit/Sales</v>
-      </c>
-      <c r="C74" s="322">
-        <f>Normalized_FCF!C118</f>
-        <v>9.3039179367971361E-2</v>
-      </c>
-      <c r="D74" s="322">
-        <f>Normalized_FCF!G118</f>
-        <v>0.12803132337228806</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
-        <v>Sales/Total Assets</v>
-      </c>
-      <c r="C75" s="324">
-        <f>Normalized_FCF!C119</f>
-        <v>0.62627525695225639</v>
-      </c>
-      <c r="D75" s="324">
-        <f>Normalized_FCF!G119</f>
-        <v>0.65923711258132256</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B120</f>
-        <v>Total Assets/Equity</v>
-      </c>
-      <c r="C76" s="324">
-        <f>Normalized_FCF!C120</f>
-        <v>1.2121620122817016</v>
-      </c>
-      <c r="D76" s="324">
-        <f>Normalized_FCF!G120</f>
-        <v>1.2121620122817016</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="13.9">
-      <c r="A78" s="222" t="s">
-        <v>505</v>
-      </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="209"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
-        <v>506</v>
-      </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="B83" s="210" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="B84" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C84" s="92">
-        <f>F31</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="B85" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C85" s="92">
-        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="C86" s="236">
-        <f>F31+C85</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="C87" s="121"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="B88" s="293" t="s">
-        <v>512</v>
-      </c>
-      <c r="C88" s="121"/>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
-        <v>507</v>
-      </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
-        <v>508</v>
-      </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="C92" s="236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="C93" s="223">
-        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.9253617912598004</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="13.9">
-      <c r="A95" s="222" t="s">
-        <v>509</v>
-      </c>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="209"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
-        <v>510</v>
-      </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6">
-      <c r="B100" s="210" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
-        <v>511</v>
-      </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
-    </row>
-    <row r="102" spans="2:6">
-      <c r="B102" s="47" t="s">
-        <v>251</v>
-      </c>
-      <c r="C102" s="349">
-        <f>DCF!C7</f>
-        <v>87825</v>
-      </c>
-      <c r="D102" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="103" spans="2:6">
-      <c r="B103" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="C103" s="223">
-        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.2717679591313917E-2</v>
-      </c>
-      <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6">
-      <c r="B104" s="296" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" s="325">
-        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
-        <v>1.1610019159010268E-2</v>
-      </c>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="B105" s="296" t="s">
-        <v>386</v>
-      </c>
-      <c r="C105" s="326">
-        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0.16381589511191816</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="47" t="s">
-        <v>260</v>
-      </c>
-      <c r="C108" s="349">
-        <f>BS!C66</f>
-        <v>3270300</v>
-      </c>
-      <c r="D108" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="B109" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="C109" s="349">
-        <f>DCF!C8</f>
-        <v>2338843.0327008888</v>
-      </c>
-      <c r="D109" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="B110" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C110" s="223">
-        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.2028314101147628</v>
-      </c>
-      <c r="D110" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="B112" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="C113" s="349">
-        <f>DCF!C9</f>
-        <v>57429</v>
-      </c>
-      <c r="D113" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="C114" s="223">
-        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.4089309664099819E-2</v>
-      </c>
-      <c r="D114" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
-        <v>516</v>
-      </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="47" t="s">
-        <v>517</v>
-      </c>
-      <c r="C118" s="223">
-        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>7.0995648314473492</v>
-      </c>
-      <c r="D118" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="296" t="s">
-        <v>550</v>
-      </c>
-      <c r="C119" s="223">
-        <f>BS!D47</f>
-        <v>3.7980767021052162</v>
-      </c>
-      <c r="D119" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="222" t="s">
-        <v>518</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="370" t="s">
-        <v>519</v>
-      </c>
-      <c r="C123" s="370"/>
-      <c r="D123" s="370"/>
-      <c r="E123" s="370"/>
-      <c r="F123" s="370"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
-      <c r="B125" s="233" t="s">
-        <v>520</v>
-      </c>
-      <c r="C125" s="233" t="s">
-        <v>521</v>
-      </c>
-      <c r="D125" s="233" t="s">
-        <v>108</v>
-      </c>
-      <c r="E125" s="233" t="s">
-        <v>522</v>
-      </c>
-      <c r="F125" s="233" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="228" t="str">
-        <f>DCF!B74</f>
-        <v>Snowball Scenario</v>
-      </c>
-      <c r="C126" s="229">
-        <f>DCF!C74</f>
-        <v>0.06</v>
-      </c>
-      <c r="D126" s="230">
-        <f>DCF!D74</f>
-        <v>10</v>
-      </c>
-      <c r="E126" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>8.13 HKD</v>
-      </c>
-      <c r="F126" s="232">
-        <f>DCF!F74</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="218" t="str">
-        <f>DCF!B75</f>
-        <v>Optimistic</v>
-      </c>
-      <c r="C127" s="219">
-        <f>DCF!C75</f>
-        <v>0.05</v>
-      </c>
-      <c r="D127" s="220">
-        <f>DCF!D75</f>
-        <v>5</v>
-      </c>
-      <c r="E127" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>7.5 HKD</v>
-      </c>
-      <c r="F127" s="221">
-        <f>DCF!F75</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="218" t="str">
-        <f>DCF!B76</f>
-        <v>Base</v>
-      </c>
-      <c r="C128" s="219">
-        <f>DCF!C76</f>
-        <v>0.03</v>
-      </c>
-      <c r="D128" s="220">
-        <f>DCF!D76</f>
-        <v>5</v>
-      </c>
-      <c r="E128" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>7.34 HKD</v>
-      </c>
-      <c r="F128" s="221">
-        <f>DCF!F76</f>
-        <v>0.53999999999999992</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="B129" s="218" t="str">
-        <f>DCF!B77</f>
-        <v>Pessimistic</v>
-      </c>
-      <c r="C129" s="219">
-        <f>DCF!C77</f>
-        <v>0.01</v>
-      </c>
-      <c r="D129" s="220">
-        <f>DCF!D77</f>
-        <v>5</v>
-      </c>
-      <c r="E129" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>7.18 HKD</v>
-      </c>
-      <c r="F129" s="221">
-        <f>DCF!F77</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="B130" s="218" t="str">
-        <f>DCF!B78</f>
-        <v>Devil's advocate</v>
-      </c>
-      <c r="C130" s="219">
-        <f>DCF!C78</f>
-        <v>0</v>
-      </c>
-      <c r="D130" s="220">
-        <f>DCF!D78</f>
-        <v>10</v>
-      </c>
-      <c r="E130" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>7.1 HKD</v>
-      </c>
-      <c r="F130" s="221">
-        <f>DCF!F78</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="211" t="s">
-        <v>254</v>
-      </c>
-      <c r="C132" s="217">
-        <f>Scenarios!C60</f>
-        <v>7.3642693066239637</v>
-      </c>
-      <c r="D132" s="212" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
-        <v>524</v>
-      </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
-      <c r="A136" s="222" t="s">
-        <v>525</v>
-      </c>
-      <c r="B136" s="36"/>
-      <c r="C136" s="36"/>
-      <c r="D136" s="36"/>
-      <c r="E136" s="36"/>
-      <c r="F136" s="36"/>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
-        <v>526</v>
-      </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
-        <v>527</v>
-      </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="210" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="B141" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C141" s="225">
-        <f>F28</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="B142" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C142" s="224">
-        <f>F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="B143" s="212" t="s">
-        <v>530</v>
-      </c>
-      <c r="C143" s="213">
-        <f>Scenarios!C77</f>
-        <v>0.36</v>
-      </c>
-      <c r="D143" s="212" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="210" t="s">
-        <v>531</v>
-      </c>
-      <c r="C145" s="241" t="str">
-        <f>C11</f>
-        <v>0327.HK</v>
-      </c>
-      <c r="D145" s="241" t="str">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C146" s="297">
-        <f>F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C147" s="216">
-        <f>Scenarios!C81</f>
-        <v>0.61051668952903526</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C148" s="216">
-        <f>Scenarios!C82</f>
-        <v>2.9931491364625158</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C149" s="215">
-        <f>Scenarios!C83</f>
-        <v>3.6036658259915511</v>
-      </c>
-      <c r="D149" s="300" t="str">
-        <f>IF($D$11="","",C149*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C150" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D150" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C151" s="92">
-        <f>Scenarios!F83</f>
-        <v>0.51065534461780882</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="210" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C154" s="297">
-        <f>Scenarios!C90</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C155" s="216">
-        <f>Scenarios!C91</f>
-        <v>0.70272000000000001</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C156" s="216">
-        <f>Scenarios!C92</f>
-        <v>3.7705058849914694</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C157" s="215">
-        <f>Scenarios!C93</f>
-        <v>4.4732258849914697</v>
-      </c>
-      <c r="D157" s="300" t="str">
-        <f>IF($D$11="","",C157*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C158" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D158" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C159" s="92">
-        <f>Scenarios!F93</f>
-        <v>0.39257709098607751</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" s="210" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C162" s="92">
-        <f>Scenarios!C96</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C163" s="216">
-        <f>Scenarios!C97</f>
-        <v>0.93618926635390554</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C164" s="216">
-        <f>Scenarios!C98</f>
-        <v>5.9279464150821148</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
-      <c r="B165" s="80" t="s">
-        <v>382</v>
-      </c>
-      <c r="C165" s="215">
-        <f>Scenarios!C99</f>
-        <v>6.8641356814360206</v>
-      </c>
-      <c r="D165" s="300" t="str">
-        <f>IF($D$11="","",C165*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
-      <c r="B166" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C166" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D166" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C167" s="92">
-        <f>Scenarios!F99</f>
-        <v>6.7913543674738563E-2</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" s="210" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C170" s="92">
-        <f>F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C171" s="216">
-        <f>Scenarios!C103</f>
-        <v>0.86853712533791372</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C172" s="216">
-        <f>Scenarios!C104</f>
-        <v>5.27841656248264</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" s="80" t="s">
-        <v>382</v>
-      </c>
-      <c r="C173" s="215">
-        <f>Scenarios!C105</f>
-        <v>6.1469536878205542</v>
-      </c>
-      <c r="D173" s="300" t="str">
-        <f>IF($D$11="","",C173*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
-      <c r="B174" s="259" t="s">
-        <v>532</v>
-      </c>
-      <c r="C174" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D174" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" s="214" t="s">
-        <v>533</v>
-      </c>
-      <c r="C175" s="92">
-        <f>Scenarios!F105</f>
-        <v>0.16491459548843124</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="13.9">
-      <c r="A177" s="222" t="s">
-        <v>357</v>
-      </c>
-      <c r="B177" s="36"/>
-      <c r="C177" s="36"/>
-      <c r="D177" s="36"/>
-      <c r="E177" s="36"/>
-      <c r="F177" s="36"/>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
-        <v>534</v>
-      </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="B181" s="210" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
-        <v>536</v>
-      </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="B183" s="214" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="B184" s="214" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="B185" s="214" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="B187" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="370" t="s">
-        <v>541</v>
-      </c>
-      <c r="C188" s="370"/>
-      <c r="D188" s="370"/>
-      <c r="E188" s="370"/>
-      <c r="F188" s="370"/>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="B190" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
-        <v>543</v>
-      </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
-        <v>544</v>
-      </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="214" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="214" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="214" t="s">
-        <v>548</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B116:F116"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
-  </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
-      <formula1>"INT,CN"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
-      <formula1>"DCF,DDM"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
-      <formula1>"Y, N"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7081,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="367" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367"/>
+      <c r="E18" s="367"/>
+      <c r="F18" s="367"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7287,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="367" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="367"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="369" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7314,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="370" t="s">
+      <c r="B40" s="368" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="370"/>
-      <c r="D40" s="370"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="C40" s="368"/>
+      <c r="D40" s="368"/>
+      <c r="E40" s="368"/>
+      <c r="F40" s="368"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7340,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="370" t="s">
+      <c r="B43" s="368" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="370"/>
-      <c r="D43" s="370"/>
-      <c r="E43" s="370"/>
-      <c r="F43" s="370"/>
+      <c r="C43" s="368"/>
+      <c r="D43" s="368"/>
+      <c r="E43" s="368"/>
+      <c r="F43" s="368"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7375,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="370" t="s">
+      <c r="B47" s="368" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="370"/>
-      <c r="D47" s="370"/>
-      <c r="E47" s="370"/>
-      <c r="F47" s="370"/>
+      <c r="C47" s="368"/>
+      <c r="D47" s="368"/>
+      <c r="E47" s="368"/>
+      <c r="F47" s="368"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7397,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="370" t="s">
+      <c r="B50" s="368" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="370"/>
-      <c r="D50" s="370"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="C50" s="368"/>
+      <c r="D50" s="368"/>
+      <c r="E50" s="368"/>
+      <c r="F50" s="368"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7467,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="370" t="s">
+      <c r="B58" s="368" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="370"/>
-      <c r="D58" s="370"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="C58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7489,13 +5748,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="370" t="s">
+      <c r="B61" s="368" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="371"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="367" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="367"/>
+      <c r="D64" s="367"/>
+      <c r="E64" s="367"/>
+      <c r="F64" s="367"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="367" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="367"/>
+      <c r="D65" s="367"/>
+      <c r="E65" s="367"/>
+      <c r="F65" s="367"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7661,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="367" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="367"/>
+      <c r="D80" s="367"/>
+      <c r="E80" s="367"/>
+      <c r="F80" s="367"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="367" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="367" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="367" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="367"/>
+      <c r="D97" s="367"/>
+      <c r="E97" s="367"/>
+      <c r="F97" s="367"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="367" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="367"/>
+      <c r="D101" s="367"/>
+      <c r="E101" s="367"/>
+      <c r="F101" s="367"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="367" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="367"/>
+      <c r="D116" s="367"/>
+      <c r="E116" s="367"/>
+      <c r="F116" s="367"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -7964,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="370" t="s">
+      <c r="B123" s="368" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="370"/>
-      <c r="D123" s="370"/>
-      <c r="E123" s="370"/>
-      <c r="F123" s="370"/>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8113,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="370" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="367" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="367"/>
+      <c r="D139" s="367"/>
+      <c r="E139" s="367"/>
+      <c r="F139" s="367"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="374" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="367"/>
+      <c r="D179" s="367"/>
+      <c r="E179" s="367"/>
+      <c r="F179" s="367"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +6753,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="371" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="371"/>
+      <c r="D182" s="371"/>
+      <c r="E182" s="371"/>
+      <c r="F182" s="371"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8523,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="370" t="s">
+      <c r="B188" s="368" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="370"/>
-      <c r="D188" s="370"/>
-      <c r="E188" s="370"/>
-      <c r="F188" s="370"/>
+      <c r="C188" s="368"/>
+      <c r="D188" s="368"/>
+      <c r="E188" s="368"/>
+      <c r="F188" s="368"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8537,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="373" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="373"/>
+      <c r="D191" s="373"/>
+      <c r="E191" s="373"/>
+      <c r="F191" s="373"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="373" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="373"/>
+      <c r="D192" s="373"/>
+      <c r="E192" s="373"/>
+      <c r="F192" s="373"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8627,7 +6886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -11203,7 +9462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -12473,7 +10732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -18153,7 +16412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -18237,10 +16496,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="378" t="s">
+      <c r="E6" s="375" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="378"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18255,8 +16514,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="378"/>
-      <c r="F7" s="378"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18271,8 +16530,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="378"/>
-      <c r="F8" s="378"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18287,8 +16546,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="378"/>
-      <c r="F9" s="378"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -19913,7 +18172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -19997,8 +18256,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="378"/>
-      <c r="F6" s="378"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21364,7 +19623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -21463,11 +19722,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="380" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 百富环球(0327.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="380"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21488,8 +19747,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="380"/>
-      <c r="F8" s="380"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21510,8 +19769,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="380"/>
-      <c r="F9" s="380"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21521,8 +19780,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="380"/>
-      <c r="F10" s="380"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21535,8 +19794,8 @@
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
-      <c r="E11" s="380"/>
-      <c r="F11" s="380"/>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21554,8 +19813,8 @@
         <v>-5.6448033822130816E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="380"/>
-      <c r="F12" s="380"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21572,8 +19831,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.12852816016361679</v>
       </c>
-      <c r="E13" s="380"/>
-      <c r="F13" s="380"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21590,8 +19849,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.13569365902210184</v>
       </c>
-      <c r="E14" s="380"/>
-      <c r="F14" s="380"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21617,21 +19876,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="380" t="s">
+      <c r="E18" s="377" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="381"/>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="381"/>
-      <c r="F19" s="381"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="381"/>
-      <c r="F20" s="381"/>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21645,8 +19904,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="381"/>
-      <c r="F21" s="381"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21660,8 +19919,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="381"/>
-      <c r="F22" s="381"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21681,8 +19940,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="379"/>
-      <c r="F25" s="379"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21692,8 +19951,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="379"/>
-      <c r="F26" s="379"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21707,8 +19966,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="379"/>
-      <c r="F27" s="379"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21718,8 +19977,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="379"/>
-      <c r="F28" s="379"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21739,8 +19998,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="379"/>
-      <c r="F31" s="379"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21750,8 +20009,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="379"/>
-      <c r="F32" s="379"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21765,8 +20024,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="379"/>
-      <c r="F33" s="379"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21776,8 +20035,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="379"/>
-      <c r="F34" s="379"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21797,8 +20056,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="379"/>
-      <c r="F37" s="379"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21808,8 +20067,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="379"/>
-      <c r="F38" s="379"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21823,8 +20082,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="379"/>
-      <c r="F39" s="379"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21835,8 +20094,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="379"/>
-      <c r="F40" s="379"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21898,8 +20157,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="379"/>
-      <c r="F49" s="379"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21909,8 +20168,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="379"/>
-      <c r="F50" s="379"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21924,8 +20183,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="379"/>
-      <c r="F51" s="379"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21935,8 +20194,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="379"/>
-      <c r="F52" s="379"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21956,8 +20215,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="379"/>
-      <c r="F55" s="379"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -21967,8 +20226,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="379"/>
-      <c r="F56" s="379"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -21982,8 +20241,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="379"/>
-      <c r="F57" s="379"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -21993,8 +20252,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="379"/>
-      <c r="F58" s="379"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22478,24 +20737,1767 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45805</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>INT</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>百富环球</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>1061744000</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>0327.HK</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>6.5</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>6901.3360000000002</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="367" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367"/>
+      <c r="E18" s="367"/>
+      <c r="F18" s="367"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>IND_02</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (HKD) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>7.3642693066239637</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>9.572177520852998E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0327.HK (HKD)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>3.6036658259915511</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>4.4732258849914697</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>6.8641356814360206</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>6.1469536878205542</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="367" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="367"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="369" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="368" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="368"/>
+      <c r="D40" s="368"/>
+      <c r="E40" s="368"/>
+      <c r="F40" s="368"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>536120.13620533235</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="368" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="368"/>
+      <c r="D43" s="368"/>
+      <c r="E43" s="368"/>
+      <c r="F43" s="368"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="368" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="368"/>
+      <c r="D47" s="368"/>
+      <c r="E47" s="368"/>
+      <c r="F47" s="368"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="368" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="368"/>
+      <c r="D50" s="368"/>
+      <c r="E50" s="368"/>
+      <c r="F50" s="368"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>3725.8278691964447</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-5556</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-1830.1721308035553</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-8506.973328445607</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="368" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-133572.49101863219</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="368" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="371"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="367" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="367"/>
+      <c r="D64" s="367"/>
+      <c r="E64" s="367"/>
+      <c r="F64" s="367"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="367" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="367"/>
+      <c r="D65" s="367"/>
+      <c r="E65" s="367"/>
+      <c r="F65" s="367"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>626115.72996402986</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>392210.49972745095</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>5.683109759145924E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>5.5384615384615379E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.9745476989157914</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>7.0630420943605887E-2</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.102310110249777</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>9.3039179367971361E-2</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.12803132337228806</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.62627525695225639</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.65923711258132256</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.2121620122817016</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.2121620122817016</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="367" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="367"/>
+      <c r="D80" s="367"/>
+      <c r="E80" s="367"/>
+      <c r="F80" s="367"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="369" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="367" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="367" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>4.9253617912598004</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="367" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="367"/>
+      <c r="D97" s="367"/>
+      <c r="E97" s="367"/>
+      <c r="F97" s="367"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="367" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="367"/>
+      <c r="D101" s="367"/>
+      <c r="E101" s="367"/>
+      <c r="F101" s="367"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>87825</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>8.2717679591313917E-2</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>1.1610019159010268E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.16381589511191816</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>3270300</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>2338843.0327008888</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.2028314101147628</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>57429</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.4089309664099819E-2</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="367" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="367"/>
+      <c r="D116" s="367"/>
+      <c r="E116" s="367"/>
+      <c r="F116" s="367"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>7.0995648314473492</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>3.7980767021052162</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="368" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.06</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>8.13 HKD</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.05</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>7.5 HKD</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.03</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>7.34 HKD</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>7.18 HKD</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>7.1 HKD</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>7.3642693066239637</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="372" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="367" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="367"/>
+      <c r="D139" s="367"/>
+      <c r="E139" s="367"/>
+      <c r="F139" s="367"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.36</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>0327.HK</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.61051668952903526</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>2.9931491364625158</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>3.6036658259915511</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.51065534461780882</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.70272000000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>3.7705058849914694</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>4.4732258849914697</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.39257709098607751</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.93618926635390554</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>5.9279464150821148</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>6.8641356814360206</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>6.7913543674738563E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.86853712533791372</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>5.27841656248264</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>6.1469536878205542</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.16491459548843124</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="374" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="367"/>
+      <c r="D179" s="367"/>
+      <c r="E179" s="367"/>
+      <c r="F179" s="367"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="371" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="371"/>
+      <c r="D182" s="371"/>
+      <c r="E182" s="371"/>
+      <c r="F182" s="371"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="368" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="368"/>
+      <c r="D188" s="368"/>
+      <c r="E188" s="368"/>
+      <c r="F188" s="368"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="373" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="373"/>
+      <c r="D191" s="373"/>
+      <c r="E191" s="373"/>
+      <c r="F191" s="373"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="373" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="373"/>
+      <c r="D192" s="373"/>
+      <c r="E192" s="373"/>
+      <c r="F192" s="373"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E784C3C-F869-43BB-AE4C-7AB89FABDE7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFB4D25-B9F8-4B13-9963-A000A2E02EB6}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="369"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="367" t="s">
+      <c r="B2" s="379" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="368"/>
-      <c r="D2" s="368"/>
-      <c r="E2" s="368"/>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB37CAB-758D-4933-AEF2-67E77E880314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF50C80B-1068-46F8-B68A-62BA5D87FFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4751,29 +4751,34 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4787,11 +4792,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5282,7 +5282,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>6901.3360000000002</v>
+        <v>7060.5976000000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5340,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="372" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.572177520852998E-2</v>
+        <v>8.6996591630523978E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5546,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="367" t="s">
+      <c r="B36" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="367"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5573,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="368" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="368"/>
-      <c r="D40" s="368"/>
-      <c r="E40" s="368"/>
-      <c r="F40" s="368"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5599,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="368" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="368"/>
-      <c r="D43" s="368"/>
-      <c r="E43" s="368"/>
-      <c r="F43" s="368"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="368" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="368"/>
-      <c r="D47" s="368"/>
-      <c r="E47" s="368"/>
-      <c r="F47" s="368"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="368" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="368"/>
-      <c r="D50" s="368"/>
-      <c r="E50" s="368"/>
-      <c r="F50" s="368"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5726,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="368" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="368"/>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="368" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="371"/>
-      <c r="D61" s="371"/>
-      <c r="E61" s="371"/>
-      <c r="F61" s="371"/>
+      <c r="C61" s="374"/>
+      <c r="D61" s="374"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="374"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="367" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="367"/>
-      <c r="D64" s="367"/>
-      <c r="E64" s="367"/>
-      <c r="F64" s="367"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="367" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="367"/>
-      <c r="D65" s="367"/>
-      <c r="E65" s="367"/>
-      <c r="F65" s="367"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.683109759145924E-2</v>
+        <v>5.5549193134509033E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5384615384615379E-2</v>
+        <v>5.4135338345864654E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="367" t="s">
+      <c r="B80" s="372" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="367"/>
-      <c r="D80" s="367"/>
-      <c r="E80" s="367"/>
-      <c r="F80" s="367"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5979,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="367" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="367"/>
-      <c r="D89" s="367"/>
-      <c r="E89" s="367"/>
-      <c r="F89" s="367"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="367" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="367"/>
-      <c r="D90" s="367"/>
-      <c r="E90" s="367"/>
-      <c r="F90" s="367"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6031,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="367" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="367"/>
-      <c r="D97" s="367"/>
-      <c r="E97" s="367"/>
-      <c r="F97" s="367"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6050,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="367" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="367"/>
-      <c r="D101" s="367"/>
-      <c r="E101" s="367"/>
-      <c r="F101" s="367"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6178,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="367" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="367"/>
-      <c r="D116" s="367"/>
-      <c r="E116" s="367"/>
-      <c r="F116" s="367"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6223,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="368" t="s">
+      <c r="B123" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6372,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="376" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6391,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="367" t="s">
+      <c r="B139" s="372" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="367"/>
-      <c r="D139" s="367"/>
-      <c r="E139" s="367"/>
-      <c r="F139" s="367"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6739,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="371" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="367"/>
-      <c r="D179" s="367"/>
-      <c r="E179" s="367"/>
-      <c r="F179" s="367"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6753,13 +6753,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="371" t="s">
+      <c r="B182" s="374" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="371"/>
-      <c r="D182" s="371"/>
-      <c r="E182" s="371"/>
-      <c r="F182" s="371"/>
+      <c r="C182" s="374"/>
+      <c r="D182" s="374"/>
+      <c r="E182" s="374"/>
+      <c r="F182" s="374"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6782,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="368" t="s">
+      <c r="B188" s="373" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="368"/>
-      <c r="D188" s="368"/>
-      <c r="E188" s="368"/>
-      <c r="F188" s="368"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6796,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="373" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="373"/>
-      <c r="D191" s="373"/>
-      <c r="E191" s="373"/>
-      <c r="F191" s="373"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="373" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="373"/>
-      <c r="D192" s="373"/>
-      <c r="E192" s="373"/>
-      <c r="F192" s="373"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6835,17 +6835,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6862,6 +6851,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14416,20 +14416,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5384615384615379E-2</v>
+        <v>5.4135338345864654E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.5384615384615383E-2</v>
+        <v>7.3684210526315783E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.7692307692307691E-2</v>
+        <v>6.616541353383458E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.5384615384615379E-2</v>
+        <v>5.4135338345864654E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -15615,50 +15615,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.683109759145924E-2</v>
+        <v>5.5549193134509033E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.0723843899794168E-2</v>
+        <v>8.867744140581385E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15349541114147996</v>
+        <v>0.15003310863452929</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17489190697262794</v>
+        <v>0.17094697674016263</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14051359493845403</v>
+        <v>0.13734411535337612</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.13008611665915121</v>
+        <v>0.12715184335105006</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.7390615382296991E-2</v>
+        <v>8.5419398493974494E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.939960610525267E-2</v>
+        <v>6.7834201456261997E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.4014272019214821E-2</v>
+        <v>6.2570341071412988E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.8261513422908255E-2</v>
+        <v>7.6496216127654684E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.4051024323406364E-2</v>
+        <v>7.2380700466487424E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15672,43 +15672,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10446122316026926</v>
+        <v>0.10210495496868424</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1688228192338411</v>
+        <v>0.16501478571728828</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18376195565612224</v>
+        <v>0.1796169491375631</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15826529819733454</v>
+        <v>0.15469540425303377</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13096739529853349</v>
+        <v>0.12801324352488236</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0542468878489615E-2</v>
+        <v>8.8500157550403385E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4680902364411758E-2</v>
+        <v>7.2996370732131791E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8768238497589454E-2</v>
+        <v>4.766820304275661E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7437273014964054E-2</v>
+        <v>8.5465003698837055E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9879119057527407E-2</v>
+        <v>8.7851770507357624E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16496,10 +16496,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -16514,8 +16514,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -16530,8 +16530,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -16546,8 +16546,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -18256,8 +18256,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.5</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19722,11 +19722,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 百富环球(0327.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -19747,8 +19747,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -19769,8 +19769,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -19780,8 +19780,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19794,8 +19794,8 @@
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19813,8 +19813,8 @@
         <v>-5.6448033822130816E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19831,8 +19831,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.12852816016361679</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19849,8 +19849,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.13569365902210184</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19876,21 +19876,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19898,14 +19898,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19919,8 +19919,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19940,8 +19940,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19951,8 +19951,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19966,8 +19966,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19977,8 +19977,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19998,8 +19998,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -20009,8 +20009,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -20024,8 +20024,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -20035,8 +20035,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -20056,8 +20056,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -20067,8 +20067,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -20082,8 +20082,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -20094,8 +20094,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -20157,8 +20157,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -20168,8 +20168,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -20183,8 +20183,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -20194,8 +20194,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -20215,8 +20215,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -20226,8 +20226,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -20241,8 +20241,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -20252,8 +20252,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.572177520852998E-2</v>
+        <v>8.6996591630523978E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>6901.3360000000002</v>
+        <v>7060.5976000000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20922,13 +20922,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="372" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.572177520852998E-2</v>
+        <v>8.6996591630523978E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21141,22 +21141,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="367" t="s">
+      <c r="B36" s="372" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="367"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21168,13 +21168,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="368" t="s">
+      <c r="B40" s="373" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="368"/>
-      <c r="D40" s="368"/>
-      <c r="E40" s="368"/>
-      <c r="F40" s="368"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21194,13 +21194,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="368" t="s">
+      <c r="B43" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="368"/>
-      <c r="D43" s="368"/>
-      <c r="E43" s="368"/>
-      <c r="F43" s="368"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21229,13 +21229,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="368" t="s">
+      <c r="B47" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="368"/>
-      <c r="D47" s="368"/>
-      <c r="E47" s="368"/>
-      <c r="F47" s="368"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21251,13 +21251,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="368" t="s">
+      <c r="B50" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="368"/>
-      <c r="D50" s="368"/>
-      <c r="E50" s="368"/>
-      <c r="F50" s="368"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21321,13 +21321,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="368" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="368"/>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21343,13 +21343,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="368" t="s">
+      <c r="B61" s="373" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="371"/>
-      <c r="D61" s="371"/>
-      <c r="E61" s="371"/>
-      <c r="F61" s="371"/>
+      <c r="C61" s="374"/>
+      <c r="D61" s="374"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="374"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -21365,22 +21365,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="367" t="s">
+      <c r="B64" s="372" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="367"/>
-      <c r="D64" s="367"/>
-      <c r="E64" s="367"/>
-      <c r="F64" s="367"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="367" t="s">
+      <c r="B65" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="367"/>
-      <c r="D65" s="367"/>
-      <c r="E65" s="367"/>
-      <c r="F65" s="367"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.683109759145924E-2</v>
+        <v>5.5549193134509033E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.5384615384615379E-2</v>
+        <v>5.4135338345864654E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -21515,22 +21515,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="367" t="s">
+      <c r="B80" s="372" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="367"/>
-      <c r="D80" s="367"/>
-      <c r="E80" s="367"/>
-      <c r="F80" s="367"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21574,22 +21574,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="367" t="s">
+      <c r="B89" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="367"/>
-      <c r="D89" s="367"/>
-      <c r="E89" s="367"/>
-      <c r="F89" s="367"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="367" t="s">
+      <c r="B90" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="367"/>
-      <c r="D90" s="367"/>
-      <c r="E90" s="367"/>
-      <c r="F90" s="367"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21626,13 +21626,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="367" t="s">
+      <c r="B97" s="372" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="367"/>
-      <c r="D97" s="367"/>
-      <c r="E97" s="367"/>
-      <c r="F97" s="367"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21645,13 +21645,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="367" t="s">
+      <c r="B101" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="367"/>
-      <c r="D101" s="367"/>
-      <c r="E101" s="367"/>
-      <c r="F101" s="367"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21773,13 +21773,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="367" t="s">
+      <c r="B116" s="372" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="367"/>
-      <c r="D116" s="367"/>
-      <c r="E116" s="367"/>
-      <c r="F116" s="367"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21818,13 +21818,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="368" t="s">
+      <c r="B123" s="373" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21967,13 +21967,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="376" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -21986,22 +21986,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="377" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="367" t="s">
+      <c r="B139" s="372" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="367"/>
-      <c r="D139" s="367"/>
-      <c r="E139" s="367"/>
-      <c r="F139" s="367"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22334,13 +22334,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="371" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="367"/>
-      <c r="D179" s="367"/>
-      <c r="E179" s="367"/>
-      <c r="F179" s="367"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22348,13 +22348,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="371" t="s">
+      <c r="B182" s="374" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="371"/>
-      <c r="D182" s="371"/>
-      <c r="E182" s="371"/>
-      <c r="F182" s="371"/>
+      <c r="C182" s="374"/>
+      <c r="D182" s="374"/>
+      <c r="E182" s="374"/>
+      <c r="F182" s="374"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -22377,13 +22377,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="368" t="s">
+      <c r="B188" s="373" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="368"/>
-      <c r="D188" s="368"/>
-      <c r="E188" s="368"/>
-      <c r="F188" s="368"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22391,22 +22391,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="373" t="s">
+      <c r="B191" s="370" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="373"/>
-      <c r="D191" s="373"/>
-      <c r="E191" s="373"/>
-      <c r="F191" s="373"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="373" t="s">
+      <c r="B192" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="373"/>
-      <c r="D192" s="373"/>
-      <c r="E192" s="373"/>
-      <c r="F192" s="373"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22430,15 +22430,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22451,12 +22448,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -22485,19 +22485,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF50C80B-1068-46F8-B68A-62BA5D87FFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D14DE-1D8C-46C6-941F-ACE9852D1916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4756,29 +4756,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5282,7 +5282,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.65</v>
+        <v>6.78</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7060.5976000000001</v>
+        <v>7198.6243199999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5340,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.6996591630523978E-2</v>
+        <v>7.9651273337934203E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5546,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5573,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5599,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5726,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5748,7 +5748,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.5549193134509033E-2</v>
+        <v>5.4484090611280983E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.4135338345864654E-2</v>
+        <v>5.3097345132743362E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5979,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6031,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6050,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6178,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6223,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6372,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6391,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6739,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6782,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6796,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6835,6 +6835,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6851,17 +6862,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14416,20 +14416,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4135338345864654E-2</v>
+        <v>5.3097345132743362E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.3684210526315783E-2</v>
+        <v>7.2271386430678458E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.616541353383458E-2</v>
+        <v>6.4896755162241887E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.4135338345864654E-2</v>
+        <v>5.3097345132743362E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -15615,50 +15615,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5549193134509033E-2</v>
+        <v>5.4484090611280983E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.867744140581385E-2</v>
+        <v>8.6977136482103548E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.15003310863452929</v>
+        <v>0.14715636761351325</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17094697674016263</v>
+        <v>0.1676692323483896</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.13734411535337612</v>
+        <v>0.13471067361356212</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12715184335105006</v>
+        <v>0.12471382865552845</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.5419398493974494E-2</v>
+        <v>8.3781563419606256E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.7834201456261997E-2</v>
+        <v>6.6533545676127182E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.2570341071412988E-2</v>
+        <v>6.137061476768383E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.6496216127654684E-2</v>
+        <v>7.5029474520487263E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.2380700466487424E-2</v>
+        <v>7.099286992656953E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15672,43 +15672,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10210495496868424</v>
+        <v>0.10014719034539088</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16501478571728828</v>
+        <v>0.16185078540117509</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1796169491375631</v>
+        <v>0.17617296633699034</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15469540425303377</v>
+        <v>0.15172926818328533</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12801324352488236</v>
+        <v>0.12555871230685364</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8500157550403385E-2</v>
+        <v>8.6803251874658191E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2996370732131791E-2</v>
+        <v>7.1596735305114526E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.766820304275661E-2</v>
+        <v>4.6754210949016439E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5465003698837055E-2</v>
+        <v>8.3826294188387371E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7851770507357624E-2</v>
+        <v>8.6167297031552834E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.65</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.65</v>
+        <v>6.78</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.65</v>
+        <v>6.78</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.6996591630523978E-2</v>
+        <v>7.9651273337934203E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.65</v>
+        <v>6.78</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>7060.5976000000001</v>
+        <v>7198.6243199999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20922,13 +20922,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.6996591630523978E-2</v>
+        <v>7.9651273337934203E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21141,22 +21141,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21168,13 +21168,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21194,13 +21194,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21229,13 +21229,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21251,13 +21251,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21321,13 +21321,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21343,7 +21343,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="374"/>
@@ -21365,22 +21365,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.5549193134509033E-2</v>
+        <v>5.4484090611280983E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.4135338345864654E-2</v>
+        <v>5.3097345132743362E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -21515,22 +21515,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21574,22 +21574,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21626,13 +21626,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21645,13 +21645,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21773,13 +21773,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21818,13 +21818,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21967,13 +21967,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -21986,22 +21986,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22334,13 +22334,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22377,13 +22377,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22391,22 +22391,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22430,12 +22430,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22448,15 +22451,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109D14DE-1D8C-46C6-941F-ACE9852D1916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D7734C-EBBC-4C3E-9B5A-04C3C69E0553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4756,29 +4756,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5282,7 +5282,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>6.78</v>
+        <v>6.99</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>7198.6243199999999</v>
+        <v>7421.5905599999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5340,13 +5340,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.9651273337934203E-2</v>
+        <v>6.8186486812982006E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5546,22 +5546,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5573,13 +5573,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5599,13 +5599,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5726,13 +5726,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5748,7 +5748,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.4484090611280983E-2</v>
+        <v>5.284722951995495E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.3097345132743362E-2</v>
+        <v>5.1502145922746781E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>424</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5979,22 +5979,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6031,13 +6031,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6050,13 +6050,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6178,13 +6178,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6223,13 +6223,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6372,13 +6372,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6391,22 +6391,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6739,13 +6739,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6782,13 +6782,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6796,22 +6796,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6835,17 +6835,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6862,6 +6851,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14416,20 +14416,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.3097345132743362E-2</v>
+        <v>5.1502145922746781E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.2271386430678458E-2</v>
+        <v>7.0100143061516448E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4896755162241887E-2</v>
+        <v>6.2947067238912732E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.3097345132743362E-2</v>
+        <v>5.1502145922746781E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -15615,50 +15615,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.4484090611280983E-2</v>
+        <v>5.284722951995495E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>8.6977136482103548E-2</v>
+        <v>8.4364089463327907E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.14715636761351325</v>
+        <v>0.14273536086117594</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.1676692323483896</v>
+        <v>0.16263195927354529</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.13471067361356212</v>
+        <v>0.13066357183118044</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12471382865552845</v>
+        <v>0.1209670612710276</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>8.3781563419606256E-2</v>
+        <v>8.1264520741764018E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>6.6533545676127182E-2</v>
+        <v>6.4534683788861569E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>6.137061476768383E-2</v>
+        <v>5.9526862392689034E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>7.5029474520487263E-2</v>
+        <v>7.2775370135751596E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.099286992656953E-2</v>
+        <v>6.8860036924483753E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15672,43 +15672,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10014719034539088</v>
+        <v>9.7138476472353394E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16185078540117509</v>
+        <v>0.15698831545350031</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17617296633699034</v>
+        <v>0.17088021627536401</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15172926818328533</v>
+        <v>0.14717087815202784</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12555871230685364</v>
+        <v>0.12178656215171213</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6803251874658191E-2</v>
+        <v>8.4195428856964585E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1596735305114526E-2</v>
+        <v>6.9445760424703351E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6754210949016439E-2</v>
+        <v>4.5349578002050278E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3826294188387371E-2</v>
+        <v>8.1307907667706208E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6167297031552834E-2</v>
+        <v>8.3578579953351675E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-6.78</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>6.78</v>
+        <v>6.99</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>6.78</v>
+        <v>6.99</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.9651273337934203E-2</v>
+        <v>6.8186486812982006E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>6.78</v>
+        <v>6.99</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>7198.6243199999999</v>
+        <v>7421.5905599999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20922,13 +20922,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.9651273337934203E-2</v>
+        <v>6.8186486812982006E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21141,22 +21141,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21168,13 +21168,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21194,13 +21194,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21229,13 +21229,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21251,13 +21251,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21321,13 +21321,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21343,7 +21343,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="374"/>
@@ -21365,22 +21365,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.4484090611280983E-2</v>
+        <v>5.284722951995495E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.3097345132743362E-2</v>
+        <v>5.1502145922746781E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -21515,22 +21515,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21574,22 +21574,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21626,13 +21626,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21645,13 +21645,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21773,13 +21773,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21818,13 +21818,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21967,13 +21967,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -21986,22 +21986,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22334,13 +22334,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22377,13 +22377,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22391,22 +22391,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22430,15 +22430,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22451,12 +22448,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0327.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0327.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D7734C-EBBC-4C3E-9B5A-04C3C69E0553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57130E07-8E91-DB44-8A17-5B40345CD4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -54,6 +54,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3321,7 +3332,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3765,6 +3776,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4756,29 +4768,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4794,7 +4806,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{C0164295-F4D5-499D-8E1E-F301B48E18DB}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
@@ -5169,16 +5181,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
@@ -5195,7 +5207,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>263</v>
       </c>
@@ -5209,7 +5221,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>394</v>
       </c>
@@ -5218,7 +5230,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>458</v>
       </c>
@@ -5226,7 +5238,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>459</v>
       </c>
@@ -5235,7 +5247,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>460</v>
       </c>
@@ -5245,7 +5257,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>461</v>
       </c>
@@ -5255,17 +5267,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>396</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>462</v>
       </c>
@@ -5277,7 +5289,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>463</v>
       </c>
@@ -5287,7 +5299,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>464</v>
       </c>
@@ -5297,7 +5309,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>465</v>
       </c>
@@ -5311,7 +5323,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>466</v>
       </c>
@@ -5325,7 +5337,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>467</v>
       </c>
@@ -5335,27 +5347,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="370" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>339</v>
       </c>
@@ -5370,7 +5382,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
@@ -5383,7 +5395,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>410</v>
       </c>
@@ -5391,7 +5403,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>411</v>
       </c>
@@ -5399,7 +5411,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>338</v>
       </c>
@@ -5415,7 +5427,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -5432,11 +5444,11 @@
         <v>6.8186486812982006E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>409</v>
       </c>
@@ -5455,7 +5467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>401</v>
       </c>
@@ -5474,7 +5486,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>402</v>
       </c>
@@ -5493,7 +5505,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>403</v>
       </c>
@@ -5512,7 +5524,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>404</v>
       </c>
@@ -5531,11 +5543,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>345</v>
       </c>
@@ -5545,25 +5557,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B36" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>226</v>
       </c>
@@ -5572,16 +5584,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>228</v>
       </c>
@@ -5594,20 +5606,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>230</v>
       </c>
@@ -5620,7 +5632,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>231</v>
       </c>
@@ -5633,16 +5645,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>233</v>
       </c>
@@ -5655,16 +5667,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>331</v>
       </c>
@@ -5679,7 +5691,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>332</v>
       </c>
@@ -5694,7 +5706,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>234</v>
       </c>
@@ -5707,12 +5719,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>261</v>
       </c>
@@ -5725,16 +5737,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>235</v>
       </c>
@@ -5747,8 +5759,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5756,7 +5768,7 @@
       <c r="E61" s="374"/>
       <c r="F61" s="374"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>238</v>
       </c>
@@ -5769,25 +5781,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>265</v>
       </c>
@@ -5800,7 +5812,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>244</v>
       </c>
@@ -5813,7 +5825,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>371</v>
       </c>
@@ -5823,7 +5835,7 @@
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>434</v>
       </c>
@@ -5839,7 +5851,7 @@
         <v>0.9745476989157914</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>427</v>
       </c>
@@ -5850,7 +5862,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>428</v>
       </c>
@@ -5863,7 +5875,7 @@
         <v>0.102310110249777</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5877,7 +5889,7 @@
         <v>0.12803132337228806</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
@@ -5891,7 +5903,7 @@
         <v>0.65923711258132256</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
@@ -5905,7 +5917,7 @@
         <v>1.2121620122817016</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>470</v>
       </c>
@@ -5915,34 +5927,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>407</v>
       </c>
@@ -5951,7 +5963,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>406</v>
       </c>
@@ -5960,7 +5972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>243</v>
       </c>
@@ -5969,34 +5981,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>247</v>
       </c>
@@ -6004,7 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>275</v>
       </c>
@@ -6017,7 +6029,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>347</v>
       </c>
@@ -6027,38 +6039,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>251</v>
       </c>
@@ -6071,7 +6083,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>276</v>
       </c>
@@ -6084,7 +6096,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>384</v>
       </c>
@@ -6093,7 +6105,7 @@
         <v>1.1610019159010268E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>386</v>
       </c>
@@ -6102,12 +6114,12 @@
         <v>0.16381589511191816</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>260</v>
       </c>
@@ -6120,7 +6132,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>262</v>
       </c>
@@ -6133,7 +6145,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>277</v>
       </c>
@@ -6146,12 +6158,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>253</v>
       </c>
@@ -6164,7 +6176,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>278</v>
       </c>
@@ -6177,16 +6189,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>425</v>
       </c>
@@ -6199,7 +6211,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>549</v>
       </c>
@@ -6212,7 +6224,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>472</v>
       </c>
@@ -6222,16 +6234,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B123" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>113</v>
       </c>
@@ -6248,7 +6260,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -6270,7 +6282,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -6292,7 +6304,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -6314,7 +6326,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -6336,7 +6348,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -6358,7 +6370,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>254</v>
       </c>
@@ -6371,16 +6383,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>475</v>
       </c>
@@ -6390,30 +6402,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B139" s="370" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>259</v>
       </c>
@@ -6422,7 +6434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>271</v>
       </c>
@@ -6431,7 +6443,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>257</v>
       </c>
@@ -6444,7 +6456,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>388</v>
       </c>
@@ -6457,7 +6469,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>387</v>
       </c>
@@ -6466,7 +6478,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6476,7 +6488,7 @@
         <v>0.61051668952903526</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6486,7 +6498,7 @@
         <v>2.9931491364625158</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>256</v>
       </c>
@@ -6499,7 +6511,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>395</v>
       </c>
@@ -6512,7 +6524,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>258</v>
       </c>
@@ -6521,12 +6533,12 @@
         <v>0.51065534461780882</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>390</v>
       </c>
@@ -6535,7 +6547,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6545,7 +6557,7 @@
         <v>0.70272000000000001</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6555,7 +6567,7 @@
         <v>3.7705058849914694</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>256</v>
       </c>
@@ -6568,7 +6580,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>395</v>
       </c>
@@ -6581,7 +6593,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>258</v>
       </c>
@@ -6590,12 +6602,12 @@
         <v>0.39257709098607751</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>389</v>
       </c>
@@ -6604,7 +6616,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6614,7 +6626,7 @@
         <v>0.93618926635390554</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6624,7 +6636,7 @@
         <v>5.9279464150821148</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>382</v>
       </c>
@@ -6637,7 +6649,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>395</v>
       </c>
@@ -6650,7 +6662,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>258</v>
       </c>
@@ -6659,12 +6671,12 @@
         <v>6.7913543674738563E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>399</v>
       </c>
@@ -6673,7 +6685,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -6683,7 +6695,7 @@
         <v>0.86853712533791372</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -6693,7 +6705,7 @@
         <v>5.27841656248264</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>382</v>
       </c>
@@ -6706,7 +6718,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>395</v>
       </c>
@@ -6719,7 +6731,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>258</v>
       </c>
@@ -6728,7 +6740,7 @@
         <v>0.16491459548843124</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>357</v>
       </c>
@@ -6738,21 +6750,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="374" t="s">
         <v>362</v>
       </c>
@@ -6761,80 +6773,91 @@
       <c r="E182" s="374"/>
       <c r="F182" s="374"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+    <row r="188" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6851,17 +6874,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6892,15 +6904,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -6949,7 +6961,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>94</v>
       </c>
@@ -6965,7 +6977,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6973,7 +6985,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>0</v>
       </c>
@@ -7009,7 +7021,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>41</v>
       </c>
@@ -7045,7 +7057,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>52</v>
       </c>
@@ -7081,7 +7093,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>59</v>
       </c>
@@ -7117,7 +7129,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>47</v>
       </c>
@@ -7133,7 +7145,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>155</v>
       </c>
@@ -7165,7 +7177,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>163</v>
       </c>
@@ -7181,7 +7193,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>154</v>
       </c>
@@ -7197,7 +7209,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>37</v>
       </c>
@@ -7221,7 +7233,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>65</v>
       </c>
@@ -7245,7 +7257,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>48</v>
       </c>
@@ -7281,7 +7293,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>40</v>
       </c>
@@ -7317,7 +7329,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>42</v>
       </c>
@@ -7353,13 +7365,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>45</v>
       </c>
@@ -7375,7 +7387,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>51</v>
       </c>
@@ -7391,7 +7403,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>50</v>
       </c>
@@ -7407,7 +7419,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>354</v>
       </c>
@@ -7443,7 +7455,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>356</v>
       </c>
@@ -7479,7 +7491,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>355</v>
       </c>
@@ -7515,7 +7527,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7541,7 +7553,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7549,7 +7561,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>22</v>
       </c>
@@ -7586,7 +7598,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>30</v>
       </c>
@@ -7623,7 +7635,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>38</v>
       </c>
@@ -7660,7 +7672,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>28</v>
       </c>
@@ -7697,7 +7709,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>168</v>
       </c>
@@ -7734,7 +7746,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>79</v>
       </c>
@@ -7750,12 +7762,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>0</v>
       </c>
@@ -7804,7 +7816,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>41</v>
       </c>
@@ -7853,7 +7865,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>56</v>
       </c>
@@ -7902,7 +7914,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>52</v>
       </c>
@@ -7951,7 +7963,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>59</v>
       </c>
@@ -8000,7 +8012,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>62</v>
       </c>
@@ -8049,7 +8061,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>47</v>
       </c>
@@ -8098,7 +8110,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>148</v>
       </c>
@@ -8147,7 +8159,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>164</v>
       </c>
@@ -8196,7 +8208,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>66</v>
       </c>
@@ -8245,7 +8257,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>48</v>
       </c>
@@ -8294,7 +8306,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>40</v>
       </c>
@@ -8343,7 +8355,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>42</v>
       </c>
@@ -8392,12 +8404,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>37</v>
       </c>
@@ -8446,7 +8458,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>65</v>
       </c>
@@ -8495,12 +8507,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>155</v>
       </c>
@@ -8549,7 +8561,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>163</v>
       </c>
@@ -8598,7 +8610,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>154</v>
       </c>
@@ -8647,7 +8659,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>156</v>
       </c>
@@ -8696,13 +8708,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>45</v>
       </c>
@@ -8751,7 +8763,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>51</v>
       </c>
@@ -8800,7 +8812,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>50</v>
       </c>
@@ -8849,7 +8861,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>374</v>
       </c>
@@ -8898,7 +8910,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>34</v>
       </c>
@@ -8947,12 +8959,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -9002,7 +9014,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>56</v>
       </c>
@@ -9051,7 +9063,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -9101,7 +9113,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>164</v>
       </c>
@@ -9150,7 +9162,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9200,7 +9212,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>80</v>
       </c>
@@ -9216,13 +9228,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>1</v>
       </c>
@@ -9271,7 +9283,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>83</v>
       </c>
@@ -9305,7 +9317,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>84</v>
       </c>
@@ -9339,7 +9351,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>38</v>
       </c>
@@ -9388,7 +9400,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>28</v>
       </c>
@@ -9469,18 +9481,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>35</v>
       </c>
@@ -9496,7 +9508,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>152</v>
       </c>
@@ -9507,7 +9519,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>180</v>
       </c>
@@ -9527,7 +9539,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9550,7 +9562,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9571,7 +9583,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9592,7 +9604,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>67</v>
       </c>
@@ -9613,7 +9625,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>169</v>
       </c>
@@ -9634,7 +9646,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9655,7 +9667,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9667,7 +9679,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9679,7 +9691,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>70</v>
       </c>
@@ -9703,12 +9715,12 @@
         <v>2938427.6</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>179</v>
       </c>
@@ -9728,7 +9740,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>431</v>
       </c>
@@ -9746,7 +9758,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9766,7 +9778,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>67</v>
       </c>
@@ -9786,7 +9798,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>169</v>
       </c>
@@ -9806,7 +9818,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9827,7 +9839,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9847,7 +9859,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9867,7 +9879,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9879,7 +9891,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9891,7 +9903,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>71</v>
       </c>
@@ -9915,7 +9927,7 @@
         <v>57429</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>196</v>
       </c>
@@ -9932,7 +9944,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9951,7 +9963,7 @@
         <v>4067119.1500000004</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9966,7 +9978,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9985,7 +9997,7 @@
         <v>4032585.1500000004</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -10001,7 +10013,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>199</v>
       </c>
@@ -10018,7 +10030,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -10038,7 +10050,7 @@
         <v>5672037.1500000004</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>2</v>
       </c>
@@ -10049,7 +10061,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -10062,7 +10074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>197</v>
       </c>
@@ -10081,7 +10093,7 @@
         <v>2676180.5499999998</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -10097,7 +10109,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -10113,7 +10125,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -10129,7 +10141,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -10148,7 +10160,7 @@
         <v>114667.70000000001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>200</v>
       </c>
@@ -10168,7 +10180,7 @@
         <v>2995856.6</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10188,7 +10200,7 @@
         <v>2938427.6</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>20</v>
       </c>
@@ -10207,7 +10219,7 @@
         <v>57429</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>93</v>
       </c>
@@ -10218,7 +10230,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>266</v>
       </c>
@@ -10232,7 +10244,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>268</v>
       </c>
@@ -10246,7 +10258,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -10261,10 +10273,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>139</v>
       </c>
@@ -10277,7 +10289,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>91</v>
       </c>
@@ -10291,7 +10303,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>172</v>
       </c>
@@ -10302,10 +10314,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>138</v>
       </c>
@@ -10317,7 +10329,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>135</v>
       </c>
@@ -10331,7 +10343,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>137</v>
       </c>
@@ -10345,10 +10357,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>171</v>
       </c>
@@ -10360,7 +10372,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>87</v>
       </c>
@@ -10371,7 +10383,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>90</v>
       </c>
@@ -10382,10 +10394,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>269</v>
       </c>
@@ -10397,7 +10409,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>241</v>
       </c>
@@ -10413,7 +10425,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>189</v>
       </c>
@@ -10424,7 +10436,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>184</v>
       </c>
@@ -10438,7 +10450,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>183</v>
       </c>
@@ -10454,7 +10466,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>173</v>
       </c>
@@ -10464,7 +10476,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>177</v>
       </c>
@@ -10474,7 +10486,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>175</v>
       </c>
@@ -10484,7 +10496,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>184</v>
       </c>
@@ -10494,10 +10506,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>309</v>
       </c>
@@ -10509,7 +10521,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>308</v>
       </c>
@@ -10525,7 +10537,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>312</v>
       </c>
@@ -10541,7 +10553,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>311</v>
       </c>
@@ -10554,7 +10566,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>313</v>
       </c>
@@ -10567,10 +10579,10 @@
         <v>314</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>185</v>
       </c>
@@ -10582,7 +10594,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>174</v>
       </c>
@@ -10596,7 +10608,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>178</v>
       </c>
@@ -10610,7 +10622,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>176</v>
       </c>
@@ -10624,7 +10636,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>185</v>
       </c>
@@ -10638,7 +10650,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>283</v>
       </c>
@@ -10649,7 +10661,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>284</v>
       </c>
@@ -10657,7 +10669,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>281</v>
       </c>
@@ -10674,7 +10686,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>282</v>
       </c>
@@ -10691,7 +10703,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>185</v>
       </c>
@@ -10708,7 +10720,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>286</v>
       </c>
@@ -10739,19 +10751,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q809"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -10808,7 +10820,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>96</v>
@@ -10831,7 +10843,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>64</v>
@@ -10845,7 +10857,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>0</v>
@@ -10902,7 +10914,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>44</v>
@@ -10957,7 +10969,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>46</v>
@@ -11012,7 +11024,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>43</v>
@@ -11067,7 +11079,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>148</v>
@@ -11124,7 +11136,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>63</v>
@@ -11179,7 +11191,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>78</v>
@@ -11234,7 +11246,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>190</v>
@@ -11291,7 +11303,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>66</v>
@@ -11346,7 +11358,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>160</v>
@@ -11401,7 +11413,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>61</v>
@@ -11456,7 +11468,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>239</v>
@@ -11513,7 +11525,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>150</v>
@@ -11570,7 +11582,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>50</v>
@@ -11596,7 +11608,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>95</v>
@@ -11621,7 +11633,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>64</v>
@@ -11678,7 +11690,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -11697,7 +11709,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>201</v>
@@ -11720,7 +11732,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>44</v>
@@ -11741,7 +11753,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>41</v>
@@ -11798,7 +11810,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>60</v>
@@ -11855,7 +11867,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>44</v>
@@ -11912,18 +11924,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>41</v>
@@ -11982,7 +11994,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -12042,7 +12054,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>44</v>
@@ -12097,18 +12109,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>170</v>
@@ -12165,7 +12177,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>47</v>
@@ -12224,7 +12236,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>43</v>
@@ -12281,18 +12293,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -12350,7 +12362,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -12408,7 +12420,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>43</v>
@@ -12463,18 +12475,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>167</v>
@@ -12532,10 +12544,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>205</v>
@@ -12558,14 +12570,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>37</v>
@@ -12620,7 +12632,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>336</v>
@@ -12675,7 +12687,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>333</v>
@@ -12732,7 +12744,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>66</v>
@@ -12787,11 +12799,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>151</v>
@@ -12801,7 +12813,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>86</v>
@@ -12827,7 +12839,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>85</v>
@@ -12854,7 +12866,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>88</v>
@@ -12909,11 +12921,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>164</v>
@@ -12923,7 +12935,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>163</v>
@@ -12978,7 +12990,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>155</v>
@@ -13033,7 +13045,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>154</v>
@@ -13088,7 +13100,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>190</v>
@@ -13143,7 +13155,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>156</v>
@@ -13199,7 +13211,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>191</v>
@@ -13254,11 +13266,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>165</v>
@@ -13268,7 +13280,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>163</v>
@@ -13293,7 +13305,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>153</v>
@@ -13318,7 +13330,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>154</v>
@@ -13343,7 +13355,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>190</v>
@@ -13370,10 +13382,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>208</v>
@@ -13396,7 +13408,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>212</v>
@@ -13417,7 +13429,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>44</v>
@@ -13474,7 +13486,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>46</v>
@@ -13531,7 +13543,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>43</v>
@@ -13588,7 +13600,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>148</v>
@@ -13645,7 +13657,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>63</v>
@@ -13702,7 +13714,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>78</v>
@@ -13761,7 +13773,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>149</v>
@@ -13818,7 +13830,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>66</v>
@@ -13875,7 +13887,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>160</v>
@@ -13932,7 +13944,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>61</v>
@@ -13989,7 +14001,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -14047,7 +14059,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>150</v>
@@ -14104,7 +14116,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>50</v>
@@ -14130,7 +14142,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>95</v>
@@ -14154,7 +14166,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>136</v>
@@ -14211,18 +14223,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -14277,7 +14289,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14333,7 +14345,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>209</v>
@@ -14388,7 +14400,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>433</v>
@@ -14409,7 +14421,7 @@
       <c r="P93" s="357"/>
       <c r="Q93" s="357"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
         <v>432</v>
@@ -14464,11 +14476,11 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="E95" s="268"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
         <v>82</v>
@@ -14489,7 +14501,7 @@
       <c r="P96" s="12"/>
       <c r="Q96" s="12"/>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
         <v>140</v>
@@ -14546,7 +14558,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
         <v>160</v>
@@ -14603,10 +14615,10 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
         <v>211</v>
@@ -14629,7 +14641,7 @@
       <c r="P100" s="37"/>
       <c r="Q100" s="37"/>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
         <v>26</v>
@@ -14639,7 +14651,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
         <v>1</v>
@@ -14696,7 +14708,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>206</v>
@@ -14753,7 +14765,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
         <v>207</v>
@@ -14810,7 +14822,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>38</v>
@@ -14867,7 +14879,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
         <v>28</v>
@@ -14924,11 +14936,11 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="E107" s="268"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
         <v>216</v>
@@ -14951,7 +14963,7 @@
       <c r="P108" s="12"/>
       <c r="Q108" s="12"/>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>213</v>
@@ -15008,7 +15020,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>214</v>
@@ -15065,7 +15077,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
         <v>67</v>
@@ -15092,18 +15104,18 @@
       <c r="P111" s="204"/>
       <c r="Q111" s="204"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
         <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>372</v>
@@ -15155,7 +15167,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
         <v>373</v>
@@ -15207,11 +15219,11 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="E116" s="268"/>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
         <v>36</v>
@@ -15265,7 +15277,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
         <v>217</v>
@@ -15320,7 +15332,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>81</v>
       </c>
@@ -15374,7 +15386,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B120" s="7" t="s">
         <v>89</v>
       </c>
@@ -15430,7 +15442,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
         <v>218</v>
@@ -15487,7 +15499,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="27"/>
       <c r="C122" s="62"/>
@@ -15506,7 +15518,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
         <v>219</v>
@@ -15529,7 +15541,7 @@
       <c r="P123" s="37"/>
       <c r="Q123" s="37"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
         <v>166</v>
@@ -15550,7 +15562,7 @@
       <c r="P124" s="12"/>
       <c r="Q124" s="12"/>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15608,7 +15620,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
         <v>264</v>
@@ -15665,7 +15677,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="2" t="s">
         <v>375</v>
       </c>
@@ -15715,688 +15727,688 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -16418,16 +16430,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>53</v>
       </c>
@@ -16439,7 +16451,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>159</v>
       </c>
@@ -16452,7 +16464,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>124</v>
       </c>
@@ -16473,7 +16485,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>119</v>
       </c>
@@ -16484,7 +16496,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>224</v>
       </c>
@@ -16502,7 +16514,7 @@
       <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>220</v>
       </c>
@@ -16518,7 +16530,7 @@
       <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>221</v>
       </c>
@@ -16534,7 +16546,7 @@
       <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>186</v>
       </c>
@@ -16550,7 +16562,7 @@
       <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>223</v>
       </c>
@@ -16564,7 +16576,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>162</v>
       </c>
@@ -16578,7 +16590,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>99</v>
       </c>
@@ -16592,10 +16604,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>225</v>
       </c>
@@ -16605,13 +16617,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>129</v>
       </c>
@@ -16621,7 +16633,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>130</v>
       </c>
@@ -16631,7 +16643,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>103</v>
       </c>
@@ -16645,10 +16657,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>104</v>
       </c>
@@ -16666,7 +16678,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -16688,7 +16700,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -16710,7 +16722,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -16742,7 +16754,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -16774,7 +16786,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -16806,7 +16818,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -16828,7 +16840,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -16850,7 +16862,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -16872,7 +16884,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -16894,7 +16906,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -16916,7 +16928,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16938,7 +16950,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16960,7 +16972,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16992,7 +17004,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -17024,7 +17036,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -17056,7 +17068,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -17078,7 +17090,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -17100,7 +17112,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -17122,7 +17134,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -17144,7 +17156,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -17166,7 +17178,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -17188,7 +17200,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -17210,7 +17222,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -17232,7 +17244,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -17254,7 +17266,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -17276,7 +17288,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -17298,7 +17310,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -17330,7 +17342,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -17362,7 +17374,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -17394,7 +17406,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -17426,7 +17438,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>127</v>
       </c>
@@ -17448,7 +17460,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>97</v>
@@ -17459,11 +17471,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>125</v>
       </c>
@@ -17473,7 +17485,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>5506910.7271902822</v>
@@ -17500,7 +17512,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -17522,7 +17534,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -17543,7 +17555,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -17574,7 +17586,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -17605,7 +17617,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -17636,7 +17648,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -17667,7 +17679,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -17684,7 +17696,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>126</v>
       </c>
@@ -17704,7 +17716,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -17727,7 +17739,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -17753,7 +17765,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -17780,7 +17792,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -17807,7 +17819,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -17834,7 +17846,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -17861,7 +17873,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -17887,7 +17899,7 @@
         <v>10.763049348614276</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -17913,7 +17925,7 @@
         <v>11.749740051121206</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>113</v>
       </c>
@@ -17930,7 +17942,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17952,7 +17964,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17975,7 +17987,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17998,7 +18010,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18021,7 +18033,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18043,14 +18055,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>302</v>
       </c>
@@ -18058,26 +18070,26 @@
         <v>102</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -18091,7 +18103,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -18105,7 +18117,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -18119,7 +18131,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -18133,7 +18145,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -18178,16 +18190,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>419</v>
       </c>
@@ -18199,7 +18211,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>418</v>
       </c>
@@ -18212,7 +18224,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>416</v>
       </c>
@@ -18233,7 +18245,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>119</v>
       </c>
@@ -18244,7 +18256,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>417</v>
       </c>
@@ -18260,7 +18272,7 @@
       <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>420</v>
       </c>
@@ -18274,10 +18286,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>225</v>
       </c>
@@ -18287,13 +18299,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>129</v>
       </c>
@@ -18303,7 +18315,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>130</v>
       </c>
@@ -18313,7 +18325,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>103</v>
       </c>
@@ -18327,10 +18339,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>104</v>
       </c>
@@ -18348,7 +18360,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -18370,7 +18382,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -18392,7 +18404,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -18414,7 +18426,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -18436,7 +18448,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -18458,7 +18470,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -18480,7 +18492,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -18502,7 +18514,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -18524,7 +18536,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -18546,7 +18558,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -18568,7 +18580,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -18590,7 +18602,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -18612,7 +18624,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -18634,7 +18646,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -18656,7 +18668,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -18678,7 +18690,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -18700,7 +18712,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -18722,7 +18734,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -18744,7 +18756,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -18766,7 +18778,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -18788,7 +18800,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -18810,7 +18822,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -18832,7 +18844,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -18854,7 +18866,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -18876,7 +18888,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -18898,7 +18910,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -18920,7 +18932,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18942,7 +18954,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18964,7 +18976,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18986,7 +18998,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -19008,7 +19020,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>127</v>
       </c>
@@ -19030,7 +19042,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>97</v>
@@ -19041,11 +19053,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>125</v>
       </c>
@@ -19055,7 +19067,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>5366747.1773179779</v>
@@ -19082,7 +19094,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -19104,7 +19116,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -19125,7 +19137,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -19146,7 +19158,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -19167,7 +19179,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -19188,7 +19200,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -19209,14 +19221,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>126</v>
       </c>
@@ -19226,7 +19238,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -19249,7 +19261,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -19275,7 +19287,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -19302,7 +19314,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -19329,7 +19341,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -19356,7 +19368,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -19383,7 +19395,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -19409,7 +19421,7 @@
         <v>8.3702404062186577</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -19435,7 +19447,7 @@
         <v>9.3318175598883926</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>113</v>
       </c>
@@ -19452,7 +19464,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -19474,7 +19486,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -19497,7 +19509,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -19520,7 +19532,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -19543,7 +19555,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -19565,14 +19577,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>302</v>
       </c>
@@ -19580,23 +19592,23 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -19626,17 +19638,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>141</v>
       </c>
@@ -19649,7 +19661,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>144</v>
       </c>
@@ -19661,7 +19673,7 @@
         <v>-6.99</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>142</v>
       </c>
@@ -19681,7 +19693,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -19690,7 +19702,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>92</v>
       </c>
@@ -19710,7 +19722,7 @@
         <v>7.724269306623964</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>270</v>
       </c>
@@ -19735,7 +19747,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>64</v>
       </c>
@@ -19757,7 +19769,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>55</v>
       </c>
@@ -19779,7 +19791,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="380"/>
       <c r="F10" s="380"/>
       <c r="H10" s="247">
@@ -19790,7 +19802,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>423</v>
       </c>
@@ -19804,7 +19816,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>140</v>
       </c>
@@ -19823,7 +19835,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>148</v>
       </c>
@@ -19841,7 +19853,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>64</v>
       </c>
@@ -19852,7 +19864,7 @@
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>158</v>
       </c>
@@ -19861,7 +19873,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>147</v>
       </c>
@@ -19869,7 +19881,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>129</v>
       </c>
@@ -19881,18 +19893,18 @@
       </c>
       <c r="F18" s="381"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="381"/>
       <c r="F19" s="381"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
       <c r="E20" s="381"/>
       <c r="F20" s="381"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>272</v>
       </c>
@@ -19907,7 +19919,7 @@
       <c r="E21" s="381"/>
       <c r="F21" s="381"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>273</v>
       </c>
@@ -19922,7 +19934,7 @@
       <c r="E22" s="381"/>
       <c r="F22" s="381"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>111</v>
       </c>
@@ -19931,7 +19943,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>129</v>
       </c>
@@ -19943,7 +19955,7 @@
       <c r="E25" s="379"/>
       <c r="F25" s="379"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>130</v>
       </c>
@@ -19954,7 +19966,7 @@
       <c r="E26" s="379"/>
       <c r="F26" s="379"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>109</v>
       </c>
@@ -19969,7 +19981,7 @@
       <c r="E27" s="379"/>
       <c r="F27" s="379"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>143</v>
       </c>
@@ -19980,7 +19992,7 @@
       <c r="E28" s="379"/>
       <c r="F28" s="379"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>112</v>
       </c>
@@ -19989,7 +20001,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>129</v>
       </c>
@@ -20001,7 +20013,7 @@
       <c r="E31" s="379"/>
       <c r="F31" s="379"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>130</v>
       </c>
@@ -20012,7 +20024,7 @@
       <c r="E32" s="379"/>
       <c r="F32" s="379"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>109</v>
       </c>
@@ -20027,7 +20039,7 @@
       <c r="E33" s="379"/>
       <c r="F33" s="379"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>143</v>
       </c>
@@ -20038,7 +20050,7 @@
       <c r="E34" s="379"/>
       <c r="F34" s="379"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>110</v>
       </c>
@@ -20047,7 +20059,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>129</v>
       </c>
@@ -20059,7 +20071,7 @@
       <c r="E37" s="379"/>
       <c r="F37" s="379"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>130</v>
       </c>
@@ -20070,7 +20082,7 @@
       <c r="E38" s="379"/>
       <c r="F38" s="379"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>109</v>
       </c>
@@ -20085,7 +20097,7 @@
       <c r="E39" s="379"/>
       <c r="F39" s="379"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>143</v>
       </c>
@@ -20097,7 +20109,7 @@
       <c r="E40" s="379"/>
       <c r="F40" s="379"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>116</v>
       </c>
@@ -20110,7 +20122,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>157</v>
       </c>
@@ -20119,12 +20131,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>129</v>
       </c>
@@ -20134,12 +20146,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>161</v>
       </c>
@@ -20148,7 +20160,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>129</v>
       </c>
@@ -20160,7 +20172,7 @@
       <c r="E49" s="379"/>
       <c r="F49" s="379"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>130</v>
       </c>
@@ -20171,7 +20183,7 @@
       <c r="E50" s="379"/>
       <c r="F50" s="379"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>109</v>
       </c>
@@ -20186,7 +20198,7 @@
       <c r="E51" s="379"/>
       <c r="F51" s="379"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>143</v>
       </c>
@@ -20197,7 +20209,7 @@
       <c r="E52" s="379"/>
       <c r="F52" s="379"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>307</v>
       </c>
@@ -20206,7 +20218,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>129</v>
       </c>
@@ -20218,7 +20230,7 @@
       <c r="E55" s="379"/>
       <c r="F55" s="379"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>130</v>
       </c>
@@ -20229,7 +20241,7 @@
       <c r="E56" s="379"/>
       <c r="F56" s="379"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>109</v>
       </c>
@@ -20244,7 +20256,7 @@
       <c r="E57" s="379"/>
       <c r="F57" s="379"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>143</v>
       </c>
@@ -20255,7 +20267,7 @@
       <c r="E58" s="379"/>
       <c r="F58" s="379"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>116</v>
       </c>
@@ -20275,7 +20287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>340</v>
       </c>
@@ -20284,7 +20296,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>299</v>
       </c>
@@ -20292,7 +20304,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>129</v>
       </c>
@@ -20305,7 +20317,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>130</v>
       </c>
@@ -20317,7 +20329,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>99</v>
       </c>
@@ -20333,7 +20345,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>341</v>
       </c>
@@ -20341,7 +20353,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>300</v>
       </c>
@@ -20351,7 +20363,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>288</v>
       </c>
@@ -20363,7 +20375,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>287</v>
       </c>
@@ -20373,7 +20385,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>279</v>
       </c>
@@ -20389,7 +20401,7 @@
         <v>0.29523676411886662</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>123</v>
       </c>
@@ -20398,12 +20410,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>292</v>
       </c>
@@ -20413,7 +20425,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>435</v>
       </c>
@@ -20426,12 +20438,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>294</v>
       </c>
@@ -20440,7 +20452,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>117</v>
       </c>
@@ -20452,7 +20464,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>118</v>
       </c>
@@ -20462,7 +20474,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>98</v>
       </c>
@@ -20482,15 +20494,15 @@
         <v>0.51065534461780882</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     